--- a/python/optimization_summary_fast_charging.xlsx
+++ b/python/optimization_summary_fast_charging.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="141">
   <si>
     <t>Charger 1</t>
   </si>
@@ -30,12 +30,6 @@
     <t>Charger 3</t>
   </si>
   <si>
-    <t>Charger 4</t>
-  </si>
-  <si>
-    <t>Charger 5</t>
-  </si>
-  <si>
     <t>Activity</t>
   </si>
   <si>
@@ -439,6 +433,15 @@
   </si>
   <si>
     <t>Bus 20</t>
+  </si>
+  <si>
+    <t>Bus 21</t>
+  </si>
+  <si>
+    <t>Bus 22</t>
+  </si>
+  <si>
+    <t>Bus 23</t>
   </si>
 </sst>
 </file>
@@ -796,7 +799,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y6"/>
+  <dimension ref="A1:Y4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
@@ -878,25 +881,25 @@
         <v>0</v>
       </c>
       <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
         <v>3</v>
       </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>4</v>
-      </c>
-      <c r="E2">
-        <v>4</v>
-      </c>
       <c r="F2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -905,7 +908,7 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -935,13 +938,13 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V2">
         <v>0</v>
       </c>
       <c r="W2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X2">
         <v>0</v>
@@ -955,25 +958,25 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -982,7 +985,7 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -1012,10 +1015,10 @@
         <v>0</v>
       </c>
       <c r="U3">
+        <v>1</v>
+      </c>
+      <c r="V3">
         <v>0</v>
-      </c>
-      <c r="V3">
-        <v>2</v>
       </c>
       <c r="W3">
         <v>0</v>
@@ -1035,22 +1038,22 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1089,7 +1092,7 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V4">
         <v>0</v>
@@ -1098,163 +1101,9 @@
         <v>0</v>
       </c>
       <c r="X4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25">
-      <c r="A5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>4</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-      <c r="F5">
-        <v>4</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>4</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>0</v>
-      </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>0</v>
-      </c>
-      <c r="V5">
-        <v>0</v>
-      </c>
-      <c r="W5">
-        <v>0</v>
-      </c>
-      <c r="X5">
-        <v>0</v>
-      </c>
-      <c r="Y5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25">
-      <c r="A6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-      <c r="D6">
-        <v>4</v>
-      </c>
-      <c r="E6">
-        <v>4</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>4</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
-      <c r="V6">
-        <v>0</v>
-      </c>
-      <c r="W6">
-        <v>0</v>
-      </c>
-      <c r="X6">
-        <v>0</v>
-      </c>
-      <c r="Y6">
         <v>0</v>
       </c>
     </row>
@@ -1270,46 +1119,46 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B2">
-        <v>104.5</v>
+        <v>98</v>
       </c>
       <c r="C2">
-        <v>21.77083333333333</v>
+        <v>17.7536231884058</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B3">
-        <v>33.75</v>
+        <v>7</v>
       </c>
       <c r="C3">
-        <v>7.03125</v>
+        <v>1.268115942028986</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4">
-        <v>341.75</v>
+        <v>447</v>
       </c>
       <c r="C4">
-        <v>71.19791666666667</v>
+        <v>80.97826086956522</v>
       </c>
     </row>
   </sheetData>
@@ -1324,35 +1173,35 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B2">
-        <v>135</v>
+        <v>28</v>
       </c>
       <c r="C2">
-        <v>28.125</v>
+        <v>9.722222222222223</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B3">
-        <v>345</v>
+        <v>260</v>
       </c>
       <c r="C3">
-        <v>71.875</v>
+        <v>90.27777777777779</v>
       </c>
     </row>
   </sheetData>
@@ -1367,10 +1216,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1378,7 +1227,7 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>5340</v>
+        <v>4020</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1386,7 +1235,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>6780</v>
+        <v>6900</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1394,7 +1243,7 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>8220</v>
+        <v>8520</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1402,7 +1251,7 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>9660</v>
+        <v>9960</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1410,7 +1259,7 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>11100</v>
+        <v>11040</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1418,7 +1267,7 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>12403.75891301304</v>
+        <v>10975.75891301308</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1426,7 +1275,7 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>13219.48159247707</v>
+        <v>10495.48159247722</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1434,7 +1283,7 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>12396.22615746515</v>
+        <v>9276.22615746554</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1442,7 +1291,7 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>11117.79775020185</v>
+        <v>7997.797750202427</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1450,7 +1299,7 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>10495.18168846827</v>
+        <v>7735.18168846896</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1458,7 +1307,7 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>10283.26834452723</v>
+        <v>7883.268344528023</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1466,7 +1315,7 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>10089.64616763462</v>
+        <v>7689.646167635491</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1474,7 +1323,7 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>9567.872343978415</v>
+        <v>7167.872343979328</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1482,7 +1331,7 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>8899.172674055033</v>
+        <v>6499.172674055942</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1490,7 +1339,7 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>8165.373241901958</v>
+        <v>5765.373241902876</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1498,7 +1347,7 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>7495.666561516601</v>
+        <v>5095.666561517528</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1506,7 +1355,7 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>6771.632627900689</v>
+        <v>4371.632627901618</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1514,7 +1363,7 @@
         <v>17</v>
       </c>
       <c r="B19">
-        <v>6164.214792295261</v>
+        <v>3764.214792296194</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1522,7 +1371,7 @@
         <v>18</v>
       </c>
       <c r="B20">
-        <v>5666.334638743661</v>
+        <v>3266.334638744621</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1530,7 +1379,7 @@
         <v>19</v>
       </c>
       <c r="B21">
-        <v>5337.576543344397</v>
+        <v>3783.576543345381</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1538,7 +1387,7 @@
         <v>20</v>
       </c>
       <c r="B22">
-        <v>5244.410692096139</v>
+        <v>3726.410692097122</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1546,7 +1395,7 @@
         <v>21</v>
       </c>
       <c r="B23">
-        <v>5097.403926373467</v>
+        <v>3507.403926374453</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1554,7 +1403,7 @@
         <v>22</v>
       </c>
       <c r="B24">
-        <v>4948.082199844096</v>
+        <v>3322.08219984508</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1562,7 +1411,7 @@
         <v>23</v>
       </c>
       <c r="B25">
-        <v>4861.33285541882</v>
+        <v>3181.332855419803</v>
       </c>
     </row>
   </sheetData>
@@ -1577,58 +1426,58 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B2">
-        <v>16400000</v>
+        <v>18860000</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B3">
-        <v>1750000</v>
+        <v>1050000</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B4">
-        <v>1500000</v>
+        <v>900000</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B5">
-        <v>867240.0000000002</v>
+        <v>827820</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B6">
-        <v>584000</v>
+        <v>1752000</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B7">
-        <v>21101240</v>
+        <v>23389820</v>
       </c>
     </row>
   </sheetData>
@@ -1638,595 +1487,595 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CS21"/>
+  <dimension ref="A1:CS24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:97">
       <c r="B1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AW1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AX1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AY1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="AZ1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="BA1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="BB1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BC1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="BD1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="BC1" s="1" t="s">
+      <c r="BE1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="BD1" s="1" t="s">
+      <c r="BF1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="BE1" s="1" t="s">
+      <c r="BG1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="BF1" s="1" t="s">
+      <c r="BH1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="BG1" s="1" t="s">
+      <c r="BI1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="BH1" s="1" t="s">
+      <c r="BJ1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="BI1" s="1" t="s">
+      <c r="BK1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="BJ1" s="1" t="s">
+      <c r="BL1" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="BK1" s="1" t="s">
+      <c r="BM1" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="BL1" s="1" t="s">
+      <c r="BN1" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="BM1" s="1" t="s">
+      <c r="BO1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="BN1" s="1" t="s">
+      <c r="BP1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="BO1" s="1" t="s">
+      <c r="BQ1" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="BP1" s="1" t="s">
+      <c r="BR1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="BQ1" s="1" t="s">
+      <c r="BS1" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="BR1" s="1" t="s">
+      <c r="BT1" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="BS1" s="1" t="s">
+      <c r="BU1" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="BT1" s="1" t="s">
+      <c r="BV1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="BU1" s="1" t="s">
+      <c r="BW1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="BV1" s="1" t="s">
+      <c r="BX1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="BW1" s="1" t="s">
+      <c r="BY1" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="BX1" s="1" t="s">
+      <c r="BZ1" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="BY1" s="1" t="s">
+      <c r="CA1" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="BZ1" s="1" t="s">
+      <c r="CB1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="CA1" s="1" t="s">
+      <c r="CC1" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="CB1" s="1" t="s">
+      <c r="CD1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="CC1" s="1" t="s">
+      <c r="CE1" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="CD1" s="1" t="s">
+      <c r="CF1" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="CE1" s="1" t="s">
+      <c r="CG1" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="CF1" s="1" t="s">
+      <c r="CH1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="CG1" s="1" t="s">
+      <c r="CI1" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="CH1" s="1" t="s">
+      <c r="CJ1" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="CI1" s="1" t="s">
+      <c r="CK1" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="CJ1" s="1" t="s">
+      <c r="CL1" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="CK1" s="1" t="s">
+      <c r="CM1" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="CL1" s="1" t="s">
+      <c r="CN1" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="CM1" s="1" t="s">
+      <c r="CO1" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="CN1" s="1" t="s">
+      <c r="CP1" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="CO1" s="1" t="s">
+      <c r="CQ1" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="CP1" s="1" t="s">
+      <c r="CR1" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="CQ1" s="1" t="s">
+      <c r="CS1" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="CR1" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="CS1" s="1" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:97">
       <c r="A2" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B2">
         <v>0.2</v>
       </c>
       <c r="C2">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="D2">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="E2">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="F2">
-        <v>0.26</v>
+        <v>0.8</v>
       </c>
       <c r="G2">
-        <v>0.26</v>
+        <v>0.8</v>
       </c>
       <c r="H2">
-        <v>0.26</v>
+        <v>0.8</v>
       </c>
       <c r="I2">
-        <v>0.32</v>
+        <v>0.8</v>
       </c>
       <c r="J2">
-        <v>0.32</v>
+        <v>0.8</v>
       </c>
       <c r="K2">
-        <v>0.32</v>
+        <v>0.8</v>
       </c>
       <c r="L2">
-        <v>0.32</v>
+        <v>0.8</v>
       </c>
       <c r="M2">
-        <v>0.32</v>
+        <v>0.8</v>
       </c>
       <c r="N2">
-        <v>0.32</v>
+        <v>0.8</v>
       </c>
       <c r="O2">
-        <v>0.32</v>
+        <v>0.8</v>
       </c>
       <c r="P2">
-        <v>0.32</v>
+        <v>0.8</v>
       </c>
       <c r="Q2">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="R2">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="S2">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="T2">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="U2">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="V2">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="W2">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="X2">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="Y2">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="Z2">
-        <v>0.5600000000000001</v>
+        <v>0.7622757967773173</v>
       </c>
       <c r="AA2">
-        <v>0.5600000000000001</v>
+        <v>0.7245515935546346</v>
       </c>
       <c r="AB2">
-        <v>0.5600000000000001</v>
+        <v>0.6868273903319519</v>
       </c>
       <c r="AC2">
-        <v>0.5600000000000001</v>
+        <v>0.6491031871092692</v>
       </c>
       <c r="AD2">
-        <v>0.5413019258919243</v>
+        <v>0.6491031871092692</v>
       </c>
       <c r="AE2">
-        <v>0.5226038517838997</v>
+        <v>0.6122432982706527</v>
       </c>
       <c r="AF2">
-        <v>0.5039057776758751</v>
+        <v>0.5753834094320363</v>
       </c>
       <c r="AG2">
-        <v>0.4852077035678505</v>
+        <v>0.5385235205934197</v>
       </c>
       <c r="AH2">
-        <v>0.4852077035678505</v>
+        <v>0.5016636317548031</v>
       </c>
       <c r="AI2">
-        <v>0.4669474271051228</v>
+        <v>0.4648037429161866</v>
       </c>
       <c r="AJ2">
-        <v>0.4486871506423951</v>
+        <v>0.4648037429161866</v>
       </c>
       <c r="AK2">
-        <v>0.4304268741796673</v>
+        <v>0.4318020028134815</v>
       </c>
       <c r="AL2">
-        <v>0.4121665977169396</v>
+        <v>0.3988002627107763</v>
       </c>
       <c r="AM2">
-        <v>0.3939063212542119</v>
+        <v>0.3657985226080712</v>
       </c>
       <c r="AN2">
-        <v>0.3939063212542119</v>
+        <v>0.3657985226080712</v>
       </c>
       <c r="AO2">
-        <v>0.3939063212542119</v>
+        <v>0.9657985226080712</v>
       </c>
       <c r="AP2">
-        <v>0.3939063212542119</v>
+        <v>0.9657985226080712</v>
       </c>
       <c r="AQ2">
-        <v>0.3939063212542119</v>
+        <v>0.9543326159071519</v>
       </c>
       <c r="AR2">
-        <v>0.3939063212542119</v>
+        <v>0.9428667092062327</v>
       </c>
       <c r="AS2">
-        <v>0.3939063212542119</v>
+        <v>0.9314008025053135</v>
       </c>
       <c r="AT2">
-        <v>0.3893896687823258</v>
+        <v>0.9199348958043944</v>
       </c>
       <c r="AU2">
-        <v>0.3848730163104397</v>
+        <v>0.9084689891034752</v>
       </c>
       <c r="AV2">
-        <v>0.3803563638385536</v>
+        <v>0.9084689891034752</v>
       </c>
       <c r="AW2">
-        <v>0.3758397113666675</v>
+        <v>0.9084689891034752</v>
       </c>
       <c r="AX2">
-        <v>0.3713230588947814</v>
+        <v>0.8714491926201172</v>
       </c>
       <c r="AY2">
-        <v>0.3713230588947814</v>
+        <v>0.8714491926201172</v>
       </c>
       <c r="AZ2">
-        <v>0.3713230588947814</v>
+        <v>0.8714491926201172</v>
       </c>
       <c r="BA2">
-        <v>0.3713230588947814</v>
+        <v>0.8284576514275677</v>
       </c>
       <c r="BB2">
-        <v>0.3713230588948039</v>
+        <v>0.7854661102350182</v>
       </c>
       <c r="BC2">
-        <v>0.3713230588948039</v>
+        <v>0.7854661102350182</v>
       </c>
       <c r="BD2">
-        <v>0.3713230588948039</v>
+        <v>0.7854661102350182</v>
       </c>
       <c r="BE2">
-        <v>0.3713230588948039</v>
+        <v>0.7854661102350182</v>
       </c>
       <c r="BF2">
-        <v>0.3713230588948039</v>
+        <v>0.7854661102350182</v>
       </c>
       <c r="BG2">
-        <v>0.3713230588948039</v>
+        <v>0.7854661102350182</v>
       </c>
       <c r="BH2">
-        <v>0.3713230588948039</v>
+        <v>0.7294913067099764</v>
       </c>
       <c r="BI2">
-        <v>0.3713230588948039</v>
+        <v>0.6735165031849345</v>
       </c>
       <c r="BJ2">
-        <v>0.3510571743139231</v>
+        <v>0.6175416996598928</v>
       </c>
       <c r="BK2">
-        <v>0.3307912897330423</v>
+        <v>0.6175416996598928</v>
       </c>
       <c r="BL2">
-        <v>0.3307912897330423</v>
+        <v>0.4778335985881731</v>
       </c>
       <c r="BM2">
-        <v>0.3307912897330423</v>
+        <v>0.4778335985881731</v>
       </c>
       <c r="BN2">
-        <v>0.3307912897330424</v>
+        <v>0.4263005724371659</v>
       </c>
       <c r="BO2">
-        <v>0.3178866260540808</v>
+        <v>0.3747675462861586</v>
       </c>
       <c r="BP2">
-        <v>0.3049819623751192</v>
+        <v>0.3184165689485643</v>
       </c>
       <c r="BQ2">
-        <v>0.2920772986961576</v>
+        <v>0.2620655916109699</v>
       </c>
       <c r="BR2">
-        <v>0.2920772986961576</v>
+        <v>0.2057146142733757</v>
       </c>
       <c r="BS2">
-        <v>0.2920772986961576</v>
+        <v>0.2057146142733757</v>
       </c>
       <c r="BT2">
-        <v>0.2920772986961576</v>
+        <v>0.2057146142733757</v>
       </c>
       <c r="BU2">
-        <v>0.2920772986961576</v>
+        <v>0.2057146142733757</v>
       </c>
       <c r="BV2">
-        <v>0.2920772986961576</v>
+        <v>0.2057146142733757</v>
       </c>
       <c r="BW2">
-        <v>0.2920772986961576</v>
+        <v>0.2057146142733757</v>
       </c>
       <c r="BX2">
-        <v>0.2920772986961576</v>
+        <v>0.2057146142733757</v>
       </c>
       <c r="BY2">
-        <v>0.2920772986961576</v>
+        <v>0.2057146142733757</v>
       </c>
       <c r="BZ2">
-        <v>0.2920772986961576</v>
+        <v>0.2057146142733757</v>
       </c>
       <c r="CA2">
-        <v>0.2920772986961576</v>
+        <v>0.2057146142733757</v>
       </c>
       <c r="CB2">
-        <v>0.2920772986961576</v>
+        <v>0.2057146142733757</v>
       </c>
       <c r="CC2">
-        <v>0.2697549364179709</v>
+        <v>0.2057146142733757</v>
       </c>
       <c r="CD2">
-        <v>0.2474325741397844</v>
+        <v>0.2057146142733757</v>
       </c>
       <c r="CE2">
-        <v>0.2249728035812434</v>
+        <v>0.2057146142733757</v>
       </c>
       <c r="CF2">
-        <v>0.2025130330227024</v>
+        <v>0.2057146142733757</v>
       </c>
       <c r="CG2">
-        <v>0.2025130330227024</v>
+        <v>0.2057146142733757</v>
       </c>
       <c r="CH2">
-        <v>0.2025130330227024</v>
+        <v>0.2057146142733757</v>
       </c>
       <c r="CI2">
-        <v>0.2625130330227024</v>
+        <v>0.2057146142733757</v>
       </c>
       <c r="CJ2">
-        <v>0.2314056435999366</v>
+        <v>0.2057146142733757</v>
       </c>
       <c r="CK2">
-        <v>0.2002982541771707</v>
+        <v>0.2057146142733757</v>
       </c>
       <c r="CL2">
-        <v>0.2002982541771707</v>
+        <v>0.2057146142733757</v>
       </c>
       <c r="CM2">
-        <v>0.2002982541771707</v>
+        <v>0.2057146142733757</v>
       </c>
       <c r="CN2">
-        <v>0.2002982541771707</v>
+        <v>0.2057146142733757</v>
       </c>
       <c r="CO2">
-        <v>0.2002982541771707</v>
+        <v>0.2057146142733757</v>
       </c>
       <c r="CP2">
-        <v>0.2002982541771707</v>
+        <v>0.2057146142733757</v>
       </c>
       <c r="CQ2">
-        <v>0.2002982541771707</v>
+        <v>0.2057146142733757</v>
       </c>
       <c r="CR2">
-        <v>0.2002982541771707</v>
+        <v>0.2057146142733757</v>
       </c>
       <c r="CS2">
-        <v>0.2002982541771707</v>
+        <v>0.2057146142733757</v>
       </c>
     </row>
     <row r="3" spans="1:97">
       <c r="A3" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B3">
         <v>0.2</v>
@@ -2235,291 +2084,291 @@
         <v>0.2</v>
       </c>
       <c r="D3">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="E3">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="F3">
-        <v>0.26</v>
+        <v>0.8</v>
       </c>
       <c r="G3">
-        <v>0.26</v>
+        <v>0.8</v>
       </c>
       <c r="H3">
-        <v>0.26</v>
+        <v>0.8</v>
       </c>
       <c r="I3">
-        <v>0.26</v>
+        <v>0.8</v>
       </c>
       <c r="J3">
-        <v>0.26</v>
+        <v>0.8</v>
       </c>
       <c r="K3">
-        <v>0.26</v>
+        <v>0.8</v>
       </c>
       <c r="L3">
-        <v>0.26</v>
+        <v>0.8</v>
       </c>
       <c r="M3">
-        <v>0.26</v>
+        <v>0.8</v>
       </c>
       <c r="N3">
-        <v>0.32</v>
+        <v>0.8</v>
       </c>
       <c r="O3">
-        <v>0.32</v>
+        <v>0.8</v>
       </c>
       <c r="P3">
-        <v>0.32</v>
+        <v>0.8</v>
       </c>
       <c r="Q3">
-        <v>0.32</v>
+        <v>0.8</v>
       </c>
       <c r="R3">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="S3">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="T3">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="U3">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="V3">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="W3">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="X3">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="Y3">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="Z3">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="AA3">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AB3">
-        <v>0.5387768192193378</v>
+        <v>0.8</v>
       </c>
       <c r="AC3">
-        <v>0.5175536384386756</v>
+        <v>0.8</v>
       </c>
       <c r="AD3">
-        <v>0.4963304576580135</v>
+        <v>0.8</v>
       </c>
       <c r="AE3">
-        <v>0.4963304576580135</v>
+        <v>0.7658619989500112</v>
       </c>
       <c r="AF3">
-        <v>0.4780627762534735</v>
+        <v>0.7317239979000227</v>
       </c>
       <c r="AG3">
-        <v>0.4597950948489335</v>
+        <v>0.7317239979000227</v>
       </c>
       <c r="AH3">
-        <v>0.4597950948489335</v>
+        <v>0.7317239979000227</v>
       </c>
       <c r="AI3">
-        <v>0.4597950948489335</v>
+        <v>0.7317239979000227</v>
       </c>
       <c r="AJ3">
-        <v>0.4597950948489335</v>
+        <v>0.7317239979000227</v>
       </c>
       <c r="AK3">
-        <v>0.4597950948489335</v>
+        <v>0.7317239979000227</v>
       </c>
       <c r="AL3">
-        <v>0.4410283028990094</v>
+        <v>0.7317239979000227</v>
       </c>
       <c r="AM3">
-        <v>0.4222615109490851</v>
+        <v>0.7317239979000227</v>
       </c>
       <c r="AN3">
-        <v>0.4034947189991609</v>
+        <v>0.7317239979000227</v>
       </c>
       <c r="AO3">
-        <v>0.3847279270492367</v>
+        <v>0.7317239979000234</v>
       </c>
       <c r="AP3">
-        <v>0.3847279270492367</v>
+        <v>0.7317239979000242</v>
       </c>
       <c r="AQ3">
-        <v>0.3847279270492367</v>
+        <v>0.7317239979000242</v>
       </c>
       <c r="AR3">
-        <v>0.3847279270492367</v>
+        <v>0.7317239979000242</v>
       </c>
       <c r="AS3">
-        <v>0.3847279270492367</v>
+        <v>0.7317239979000242</v>
       </c>
       <c r="AT3">
-        <v>0.3847279270492367</v>
+        <v>0.7317239979000242</v>
       </c>
       <c r="AU3">
-        <v>0.3847279270492367</v>
+        <v>0.7317239979000242</v>
       </c>
       <c r="AV3">
-        <v>0.3847279270492367</v>
+        <v>0.7317239979000242</v>
       </c>
       <c r="AW3">
-        <v>0.3847279270492367</v>
+        <v>0.7317239979000242</v>
       </c>
       <c r="AX3">
-        <v>0.3610944330687617</v>
+        <v>0.7317239979000242</v>
       </c>
       <c r="AY3">
-        <v>0.3374609390882867</v>
+        <v>0.7317239979000242</v>
       </c>
       <c r="AZ3">
-        <v>0.3374609390882867</v>
+        <v>0.7317239979000242</v>
       </c>
       <c r="BA3">
-        <v>0.3374609390882867</v>
+        <v>0.6604889625983212</v>
       </c>
       <c r="BB3">
-        <v>0.31104392171128</v>
+        <v>0.5892539272966184</v>
       </c>
       <c r="BC3">
-        <v>0.31104392171128</v>
+        <v>0.5892539272966184</v>
       </c>
       <c r="BD3">
-        <v>0.3110439217112788</v>
+        <v>0.5892539272966187</v>
       </c>
       <c r="BE3">
-        <v>0.287289948963193</v>
+        <v>0.5892539272966194</v>
       </c>
       <c r="BF3">
-        <v>0.2635359762151073</v>
+        <v>0.5892539272966194</v>
       </c>
       <c r="BG3">
-        <v>0.2635359762151073</v>
+        <v>0.5892539272966194</v>
       </c>
       <c r="BH3">
-        <v>0.2635359762151048</v>
+        <v>0.5892539272966194</v>
       </c>
       <c r="BI3">
-        <v>0.2635359762151048</v>
+        <v>0.5892539272966194</v>
       </c>
       <c r="BJ3">
-        <v>0.2635359762151048</v>
+        <v>0.5892539272966194</v>
       </c>
       <c r="BK3">
-        <v>0.2635359762151048</v>
+        <v>0.5892539272966194</v>
       </c>
       <c r="BL3">
-        <v>0.2635359762151048</v>
+        <v>0.5268014544108384</v>
       </c>
       <c r="BM3">
-        <v>0.2635359762151048</v>
+        <v>0.4643489815250572</v>
       </c>
       <c r="BN3">
-        <v>0.2635359762151048</v>
+        <v>0.299252558090917</v>
       </c>
       <c r="BO3">
-        <v>0.2635359762151048</v>
+        <v>0.299252558090917</v>
       </c>
       <c r="BP3">
-        <v>0.2407338555502002</v>
+        <v>0.299252558090917</v>
       </c>
       <c r="BQ3">
-        <v>0.2179317348852957</v>
+        <v>0.299252558090919</v>
       </c>
       <c r="BR3">
-        <v>0.2179317348852957</v>
+        <v>0.2539108593028014</v>
       </c>
       <c r="BS3">
-        <v>0.2179317348852957</v>
+        <v>0.2085691605146837</v>
       </c>
       <c r="BT3">
-        <v>0.2179317348853078</v>
+        <v>0.208569160514683</v>
       </c>
       <c r="BU3">
-        <v>0.2179317348853078</v>
+        <v>0.2085691605146817</v>
       </c>
       <c r="BV3">
-        <v>0.2179317348853078</v>
+        <v>0.2085691605146806</v>
       </c>
       <c r="BW3">
-        <v>0.2179317348853078</v>
+        <v>0.2085691605146806</v>
       </c>
       <c r="BX3">
-        <v>0.2179317348853078</v>
+        <v>0.2085691605146796</v>
       </c>
       <c r="BY3">
-        <v>0.2179317348853078</v>
+        <v>0.208569160514678</v>
       </c>
       <c r="BZ3">
-        <v>0.2179317348853078</v>
+        <v>0.2085691605146768</v>
       </c>
       <c r="CA3">
-        <v>0.2179317348853078</v>
+        <v>0.2085691605146768</v>
       </c>
       <c r="CB3">
-        <v>0.2179317348853078</v>
+        <v>0.2085691605146768</v>
       </c>
       <c r="CC3">
-        <v>0.2179317348853078</v>
+        <v>0.2085691605146759</v>
       </c>
       <c r="CD3">
-        <v>0.2179317348853078</v>
+        <v>0.2085691605146752</v>
       </c>
       <c r="CE3">
-        <v>0.2179317348853078</v>
+        <v>0.2085691605146752</v>
       </c>
       <c r="CF3">
-        <v>0.2179317348853078</v>
+        <v>0.2085691605146741</v>
       </c>
       <c r="CG3">
-        <v>0.2179317348853078</v>
+        <v>0.2085691605146723</v>
       </c>
       <c r="CH3">
-        <v>0.2179317348853078</v>
+        <v>0.2085691605146706</v>
       </c>
       <c r="CI3">
-        <v>0.2179317348853078</v>
+        <v>0.2085691605146693</v>
       </c>
       <c r="CJ3">
-        <v>0.2179317348853078</v>
+        <v>0.2085691605146679</v>
       </c>
       <c r="CK3">
-        <v>0.2179317348853078</v>
+        <v>0.2085691605146668</v>
       </c>
       <c r="CL3">
-        <v>0.2152115140437559</v>
+        <v>0.2085691605146652</v>
       </c>
       <c r="CM3">
-        <v>0.2124912932022039</v>
+        <v>0.2085691605146625</v>
       </c>
       <c r="CN3">
-        <v>0.2124912932022039</v>
+        <v>0.2085691605146636</v>
       </c>
       <c r="CO3">
-        <v>0.2124912932022039</v>
+        <v>0.2085691605146644</v>
       </c>
       <c r="CP3">
-        <v>0.2124912932022039</v>
+        <v>0.2085691605146644</v>
       </c>
       <c r="CQ3">
-        <v>0.2124912932022039</v>
+        <v>0.2085691605146644</v>
       </c>
       <c r="CR3">
-        <v>0.2124912932022039</v>
+        <v>0.2085691605146644</v>
       </c>
       <c r="CS3">
-        <v>0.2124912932022039</v>
+        <v>0.2085691605146644</v>
       </c>
     </row>
     <row r="4" spans="1:97">
       <c r="A4" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B4">
         <v>0.2</v>
@@ -2528,291 +2377,291 @@
         <v>0.2</v>
       </c>
       <c r="D4">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="E4">
-        <v>0.26</v>
+        <v>0.8</v>
       </c>
       <c r="F4">
-        <v>0.26</v>
+        <v>0.8</v>
       </c>
       <c r="G4">
-        <v>0.26</v>
+        <v>0.8</v>
       </c>
       <c r="H4">
-        <v>0.26</v>
+        <v>0.8</v>
       </c>
       <c r="I4">
-        <v>0.32</v>
+        <v>0.8</v>
       </c>
       <c r="J4">
-        <v>0.32</v>
+        <v>0.8</v>
       </c>
       <c r="K4">
-        <v>0.32</v>
+        <v>0.8</v>
       </c>
       <c r="L4">
-        <v>0.32</v>
+        <v>0.8</v>
       </c>
       <c r="M4">
-        <v>0.32</v>
+        <v>0.8</v>
       </c>
       <c r="N4">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="O4">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="P4">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="Q4">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="R4">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="S4">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="T4">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="U4">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="V4">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="W4">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="X4">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="Y4">
-        <v>0.62</v>
+        <v>0.8</v>
       </c>
       <c r="Z4">
-        <v>0.62</v>
+        <v>0.8</v>
       </c>
       <c r="AA4">
-        <v>0.62</v>
+        <v>0.8</v>
       </c>
       <c r="AB4">
-        <v>0.6012973578033145</v>
+        <v>0.8</v>
       </c>
       <c r="AC4">
-        <v>0.5825947156066376</v>
+        <v>0.7808666142135073</v>
       </c>
       <c r="AD4">
-        <v>0.5638920734099607</v>
+        <v>0.7617332284270149</v>
       </c>
       <c r="AE4">
-        <v>0.545189431213283</v>
+        <v>0.7425998426405221</v>
       </c>
       <c r="AF4">
-        <v>0.5264867890166027</v>
+        <v>0.7234664568540295</v>
       </c>
       <c r="AG4">
-        <v>0.5264867890166027</v>
+        <v>0.704333071067537</v>
       </c>
       <c r="AH4">
-        <v>0.5069817921795178</v>
+        <v>0.6851996852810444</v>
       </c>
       <c r="AI4">
-        <v>0.4874767953424328</v>
+        <v>0.6660662994945517</v>
       </c>
       <c r="AJ4">
-        <v>0.4679717985053478</v>
+        <v>0.6299324437653091</v>
       </c>
       <c r="AK4">
-        <v>0.4484668016682627</v>
+        <v>0.5937985880360664</v>
       </c>
       <c r="AL4">
-        <v>0.4484668016682398</v>
+        <v>0.5576647323068238</v>
       </c>
       <c r="AM4">
-        <v>0.4484668016682398</v>
+        <v>0.5215308765775811</v>
       </c>
       <c r="AN4">
-        <v>0.4484668016682398</v>
+        <v>0.4853970208483385</v>
       </c>
       <c r="AO4">
-        <v>0.4484668016682398</v>
+        <v>0.4853970208483385</v>
       </c>
       <c r="AP4">
-        <v>0.4484668016682319</v>
+        <v>0.4853970208483385</v>
       </c>
       <c r="AQ4">
-        <v>0.4484668016682301</v>
+        <v>0.4853970208483385</v>
       </c>
       <c r="AR4">
-        <v>0.4484668016682283</v>
+        <v>0.4853970208483385</v>
       </c>
       <c r="AS4">
-        <v>0.4484668016682257</v>
+        <v>0.4853970208483385</v>
       </c>
       <c r="AT4">
-        <v>0.4484668016682228</v>
+        <v>0.4853970208483385</v>
       </c>
       <c r="AU4">
-        <v>0.4484668016682191</v>
+        <v>0.4853970208483385</v>
       </c>
       <c r="AV4">
-        <v>0.4484668016682208</v>
+        <v>0.4853970208483385</v>
       </c>
       <c r="AW4">
-        <v>0.4484668016682208</v>
+        <v>0.4853970208483385</v>
       </c>
       <c r="AX4">
-        <v>0.4484668016682208</v>
+        <v>0.4381300328873886</v>
       </c>
       <c r="AY4">
-        <v>0.4484668016682208</v>
+        <v>0.3908630449264385</v>
       </c>
       <c r="AZ4">
-        <v>0.4205081347189896</v>
+        <v>0.3908630449264385</v>
       </c>
       <c r="BA4">
-        <v>0.3925494677697585</v>
+        <v>0.3908630449264385</v>
       </c>
       <c r="BB4">
-        <v>0.3645908008205272</v>
+        <v>0.3908630449264385</v>
       </c>
       <c r="BC4">
-        <v>0.3645908008205272</v>
+        <v>0.3908630449264385</v>
       </c>
       <c r="BD4">
-        <v>0.3645908008205272</v>
+        <v>0.3908630449264385</v>
       </c>
       <c r="BE4">
-        <v>0.3645908008205272</v>
+        <v>0.3908630449264385</v>
       </c>
       <c r="BF4">
-        <v>0.3290224065472402</v>
+        <v>0.3908630449264386</v>
       </c>
       <c r="BG4">
-        <v>0.3290224065472402</v>
+        <v>0.3908630449264386</v>
       </c>
       <c r="BH4">
-        <v>0.3290224065472402</v>
+        <v>0.3908630449264386</v>
       </c>
       <c r="BI4">
-        <v>0.3290224065472402</v>
+        <v>0.3908630449264386</v>
       </c>
       <c r="BJ4">
-        <v>0.3290224065472402</v>
+        <v>0.3908630449264386</v>
       </c>
       <c r="BK4">
-        <v>0.3290224065472402</v>
+        <v>0.3908630449264386</v>
       </c>
       <c r="BL4">
-        <v>0.3290224065472402</v>
+        <v>0.3908630449264386</v>
       </c>
       <c r="BM4">
-        <v>0.3150380175592891</v>
+        <v>0.3908630449264386</v>
       </c>
       <c r="BN4">
-        <v>0.3010536285713381</v>
+        <v>0.3908630449264386</v>
       </c>
       <c r="BO4">
-        <v>0.2870692395833871</v>
+        <v>0.3567167392486495</v>
       </c>
       <c r="BP4">
-        <v>0.287069239583387</v>
+        <v>0.3225704335708605</v>
       </c>
       <c r="BQ4">
-        <v>0.287069239583387</v>
+        <v>0.3225704335708605</v>
       </c>
       <c r="BR4">
-        <v>0.287069239583387</v>
+        <v>0.3225704335708605</v>
       </c>
       <c r="BS4">
-        <v>0.287069239583387</v>
+        <v>0.3225704335708605</v>
       </c>
       <c r="BT4">
-        <v>0.2592952652101174</v>
+        <v>0.3225704335708605</v>
       </c>
       <c r="BU4">
-        <v>0.2315212908368478</v>
+        <v>0.3225704335708605</v>
       </c>
       <c r="BV4">
-        <v>0.2037473164635781</v>
+        <v>0.2651634640457577</v>
       </c>
       <c r="BW4">
-        <v>0.2037473164635781</v>
+        <v>0.2077564945206549</v>
       </c>
       <c r="BX4">
-        <v>0.2037473164635781</v>
+        <v>0.2077564945206549</v>
       </c>
       <c r="BY4">
-        <v>0.2037473164635781</v>
+        <v>0.2077564945206549</v>
       </c>
       <c r="BZ4">
-        <v>0.2037473164635781</v>
+        <v>0.2077564945206549</v>
       </c>
       <c r="CA4">
-        <v>0.2037473164635781</v>
+        <v>0.2077564945206549</v>
       </c>
       <c r="CB4">
-        <v>0.2037473164635781</v>
+        <v>0.2077564945206549</v>
       </c>
       <c r="CC4">
-        <v>0.2037473164635781</v>
+        <v>0.2077564945206549</v>
       </c>
       <c r="CD4">
-        <v>0.2037473164635781</v>
+        <v>0.2077564945206549</v>
       </c>
       <c r="CE4">
-        <v>0.2037473164635781</v>
+        <v>0.2077564945206549</v>
       </c>
       <c r="CF4">
-        <v>0.2037473164635781</v>
+        <v>0.2077564945206549</v>
       </c>
       <c r="CG4">
-        <v>0.2037473164635781</v>
+        <v>0.2077564945206549</v>
       </c>
       <c r="CH4">
-        <v>0.2037473164635781</v>
+        <v>0.2077564945206549</v>
       </c>
       <c r="CI4">
-        <v>0.2037473164635781</v>
+        <v>0.2077564945206549</v>
       </c>
       <c r="CJ4">
-        <v>0.2037473164635781</v>
+        <v>0.2077564945206549</v>
       </c>
       <c r="CK4">
-        <v>0.2037473164635781</v>
+        <v>0.2077564945206549</v>
       </c>
       <c r="CL4">
-        <v>0.2037473164635781</v>
+        <v>0.2077564945206549</v>
       </c>
       <c r="CM4">
-        <v>0.2037473164635781</v>
+        <v>0.2077564945206549</v>
       </c>
       <c r="CN4">
-        <v>0.2037473164635781</v>
+        <v>0.2077564945206549</v>
       </c>
       <c r="CO4">
-        <v>0.2037473164635781</v>
+        <v>0.2077564945206549</v>
       </c>
       <c r="CP4">
-        <v>0.2037473164635781</v>
+        <v>0.2077564945206549</v>
       </c>
       <c r="CQ4">
-        <v>0.2037473164635781</v>
+        <v>0.2077564945206549</v>
       </c>
       <c r="CR4">
-        <v>0.2037473164635781</v>
+        <v>0.2077564945206549</v>
       </c>
       <c r="CS4">
-        <v>0.2037473164635781</v>
+        <v>0.2077564945206549</v>
       </c>
     </row>
     <row r="5" spans="1:97">
       <c r="A5" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B5">
         <v>0.2</v>
@@ -2830,282 +2679,282 @@
         <v>0.2</v>
       </c>
       <c r="G5">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="H5">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="I5">
-        <v>0.32</v>
+        <v>0.8</v>
       </c>
       <c r="J5">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="K5">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="L5">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="M5">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="N5">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="O5">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="P5">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="Q5">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="R5">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="S5">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="T5">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="U5">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="V5">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="W5">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="X5">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="Y5">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="Z5">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AA5">
-        <v>0.5405900293249397</v>
+        <v>0.8</v>
       </c>
       <c r="AB5">
-        <v>0.5211800586498884</v>
+        <v>0.8</v>
       </c>
       <c r="AC5">
-        <v>0.5017700879748371</v>
+        <v>0.8</v>
       </c>
       <c r="AD5">
-        <v>0.4823601172997858</v>
+        <v>0.8</v>
       </c>
       <c r="AE5">
-        <v>0.4629501466247346</v>
+        <v>0.8</v>
       </c>
       <c r="AF5">
-        <v>0.4469067161737303</v>
+        <v>0.8</v>
       </c>
       <c r="AG5">
-        <v>0.4308632857227263</v>
+        <v>0.8</v>
       </c>
       <c r="AH5">
-        <v>0.414819855271722</v>
+        <v>0.8</v>
       </c>
       <c r="AI5">
-        <v>0.3987764248207179</v>
+        <v>0.8</v>
       </c>
       <c r="AJ5">
-        <v>0.3827329943697137</v>
+        <v>0.8</v>
       </c>
       <c r="AK5">
-        <v>0.3827329943697137</v>
+        <v>0.8</v>
       </c>
       <c r="AL5">
-        <v>0.3827329943697137</v>
+        <v>0.8</v>
       </c>
       <c r="AM5">
-        <v>0.3827329943697137</v>
+        <v>0.8</v>
       </c>
       <c r="AN5">
-        <v>0.3827329943697126</v>
+        <v>0.8</v>
       </c>
       <c r="AO5">
-        <v>0.3827329943697126</v>
+        <v>0.8</v>
       </c>
       <c r="AP5">
-        <v>0.3827329943697126</v>
+        <v>0.8</v>
       </c>
       <c r="AQ5">
-        <v>0.3827329943697126</v>
+        <v>0.8</v>
       </c>
       <c r="AR5">
-        <v>0.3827329943697126</v>
+        <v>0.8</v>
       </c>
       <c r="AS5">
-        <v>0.3827329943697126</v>
+        <v>0.8</v>
       </c>
       <c r="AT5">
-        <v>0.3827329943697126</v>
+        <v>0.8</v>
       </c>
       <c r="AU5">
-        <v>0.3827329943697126</v>
+        <v>0.8</v>
       </c>
       <c r="AV5">
-        <v>0.3827329943697137</v>
+        <v>0.8</v>
       </c>
       <c r="AW5">
-        <v>0.3827329943697149</v>
+        <v>0.7588229665338779</v>
       </c>
       <c r="AX5">
-        <v>0.3827329943697163</v>
+        <v>0.717645933067764</v>
       </c>
       <c r="AY5">
-        <v>0.3827329943697163</v>
+        <v>0.6717990842133655</v>
       </c>
       <c r="AZ5">
-        <v>0.3599970390973039</v>
+        <v>0.625952235358967</v>
       </c>
       <c r="BA5">
-        <v>0.3372610838248916</v>
+        <v>0.5801053865045686</v>
       </c>
       <c r="BB5">
-        <v>0.3372610838248932</v>
+        <v>0.5801053865045686</v>
       </c>
       <c r="BC5">
-        <v>0.3372610838248932</v>
+        <v>0.5801053865045686</v>
       </c>
       <c r="BD5">
-        <v>0.3372610838248951</v>
+        <v>0.5801053865045686</v>
       </c>
       <c r="BE5">
-        <v>0.3372610838248969</v>
+        <v>0.5801053865045686</v>
       </c>
       <c r="BF5">
-        <v>0.3071406737292986</v>
+        <v>0.5801053865045686</v>
       </c>
       <c r="BG5">
-        <v>0.2770202636337003</v>
+        <v>0.5801053865045686</v>
       </c>
       <c r="BH5">
-        <v>0.2770202636337019</v>
+        <v>0.5801053865045686</v>
       </c>
       <c r="BI5">
-        <v>0.2770202636337019</v>
+        <v>0.5801053865045686</v>
       </c>
       <c r="BJ5">
-        <v>0.2770202636337019</v>
+        <v>0.5801053865045686</v>
       </c>
       <c r="BK5">
-        <v>0.2770202636337019</v>
+        <v>0.5801053865045686</v>
       </c>
       <c r="BL5">
-        <v>0.2770202636337019</v>
+        <v>0.5801053865045686</v>
       </c>
       <c r="BM5">
-        <v>0.2770202636337032</v>
+        <v>0.5474752026372736</v>
       </c>
       <c r="BN5">
-        <v>0.2770202636337064</v>
+        <v>0.5148450187699785</v>
       </c>
       <c r="BO5">
-        <v>0.2770202636337097</v>
+        <v>0.5148450187699785</v>
       </c>
       <c r="BP5">
-        <v>0.2770202636337118</v>
+        <v>0.5148450187699785</v>
       </c>
       <c r="BQ5">
-        <v>0.2770202636337141</v>
+        <v>0.5148450187699785</v>
       </c>
       <c r="BR5">
-        <v>0.2770202636337162</v>
+        <v>0.3555823531895941</v>
       </c>
       <c r="BS5">
-        <v>0.2770202636337162</v>
+        <v>0.3555823531895941</v>
       </c>
       <c r="BT5">
-        <v>0.2770202636337185</v>
+        <v>0.3555823531895941</v>
       </c>
       <c r="BU5">
-        <v>0.2770202636336913</v>
+        <v>0.284206649251271</v>
       </c>
       <c r="BV5">
-        <v>0.2770202636336913</v>
+        <v>0.2128309453129479</v>
       </c>
       <c r="BW5">
-        <v>0.2512893783902551</v>
+        <v>0.2128309453129479</v>
       </c>
       <c r="BX5">
-        <v>0.2512893783902551</v>
+        <v>0.2128309453129479</v>
       </c>
       <c r="BY5">
-        <v>0.2302423629769222</v>
+        <v>0.2128309453129479</v>
       </c>
       <c r="BZ5">
-        <v>0.2091953475635892</v>
+        <v>0.2128309453129479</v>
       </c>
       <c r="CA5">
-        <v>0.2091953475635797</v>
+        <v>0.2128309453129479</v>
       </c>
       <c r="CB5">
-        <v>0.2091953475635797</v>
+        <v>0.8128309453129479</v>
       </c>
       <c r="CC5">
-        <v>0.2091953475635797</v>
+        <v>0.7681862207565747</v>
       </c>
       <c r="CD5">
-        <v>0.2691953475635797</v>
+        <v>0.7235414962002015</v>
       </c>
       <c r="CE5">
-        <v>0.2691953475635797</v>
+        <v>0.6786219550831004</v>
       </c>
       <c r="CF5">
-        <v>0.2691953475635702</v>
+        <v>0.6337024139659995</v>
       </c>
       <c r="CG5">
-        <v>0.2450427720116457</v>
+        <v>0.5890576894096262</v>
       </c>
       <c r="CH5">
-        <v>0.2450427720116457</v>
+        <v>0.5444129648532531</v>
       </c>
       <c r="CI5">
-        <v>0.2450427720116457</v>
+        <v>0.499911878752953</v>
       </c>
       <c r="CJ5">
-        <v>0.2450427720116457</v>
+        <v>0.4554107926526529</v>
       </c>
       <c r="CK5">
-        <v>0.2227193404769886</v>
+        <v>0.4554107926526529</v>
       </c>
       <c r="CL5">
-        <v>0.2003959089423316</v>
+        <v>0.4554107926526529</v>
       </c>
       <c r="CM5">
-        <v>0.2003959089423316</v>
+        <v>0.4554107926526529</v>
       </c>
       <c r="CN5">
-        <v>0.2003959089423316</v>
+        <v>0.3895256575185835</v>
       </c>
       <c r="CO5">
-        <v>0.2003959089423316</v>
+        <v>0.323640522384514</v>
       </c>
       <c r="CP5">
-        <v>0.2003959089423316</v>
+        <v>0.323640522384514</v>
       </c>
       <c r="CQ5">
-        <v>0.2003959089423316</v>
+        <v>0.323640522384514</v>
       </c>
       <c r="CR5">
-        <v>0.2003959089423316</v>
+        <v>0.323640522384514</v>
       </c>
       <c r="CS5">
-        <v>0.2003959089423316</v>
+        <v>0.323640522384514</v>
       </c>
     </row>
     <row r="6" spans="1:97">
       <c r="A6" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B6">
         <v>0.2</v>
@@ -3114,584 +2963,584 @@
         <v>0.2</v>
       </c>
       <c r="D6">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="E6">
-        <v>0.32</v>
+        <v>0.2</v>
       </c>
       <c r="F6">
-        <v>0.38</v>
+        <v>0.2</v>
       </c>
       <c r="G6">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="H6">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="I6">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="J6">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="K6">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="L6">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="M6">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="N6">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="O6">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="P6">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="Q6">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="R6">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="S6">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="T6">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="U6">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="V6">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="W6">
-        <v>0.5600000000000001</v>
+        <v>0.7557509530720451</v>
       </c>
       <c r="X6">
-        <v>0.5600000000000001</v>
+        <v>0.711501906144086</v>
       </c>
       <c r="Y6">
-        <v>0.5600000000000001</v>
+        <v>0.6672528592161268</v>
       </c>
       <c r="Z6">
-        <v>0.5600000000000001</v>
+        <v>0.6230038122881674</v>
       </c>
       <c r="AA6">
-        <v>0.5600000000000001</v>
+        <v>0.6230038122881729</v>
       </c>
       <c r="AB6">
-        <v>0.62</v>
+        <v>0.6230038122881759</v>
       </c>
       <c r="AC6">
-        <v>0.5997814211239508</v>
+        <v>0.5825666545360785</v>
       </c>
       <c r="AD6">
-        <v>0.579562842247902</v>
+        <v>0.542129496783981</v>
       </c>
       <c r="AE6">
-        <v>0.5593442633718533</v>
+        <v>0.5016923390318835</v>
       </c>
       <c r="AF6">
-        <v>0.5358242819781803</v>
+        <v>0.5016923390318835</v>
       </c>
       <c r="AG6">
-        <v>0.5123043005845075</v>
+        <v>0.4627831463298252</v>
       </c>
       <c r="AH6">
-        <v>0.4887843191908345</v>
+        <v>0.4238739536277669</v>
       </c>
       <c r="AI6">
-        <v>0.4887843191908345</v>
+        <v>0.3849647609257085</v>
       </c>
       <c r="AJ6">
-        <v>0.4606968486806152</v>
+        <v>0.3849647609257085</v>
       </c>
       <c r="AK6">
-        <v>0.4326093781703959</v>
+        <v>0.3849647609257085</v>
       </c>
       <c r="AL6">
-        <v>0.4045219076601765</v>
+        <v>0.3849647609257085</v>
       </c>
       <c r="AM6">
-        <v>0.4045219076601765</v>
+        <v>0.3849647609257085</v>
       </c>
       <c r="AN6">
-        <v>0.4045219076601765</v>
+        <v>0.3849647609257085</v>
       </c>
       <c r="AO6">
-        <v>0.4045219076601765</v>
+        <v>0.3849647609257085</v>
       </c>
       <c r="AP6">
-        <v>0.4045219076601765</v>
+        <v>0.3849647609257085</v>
       </c>
       <c r="AQ6">
-        <v>0.4045219076601765</v>
+        <v>0.3849647609257085</v>
       </c>
       <c r="AR6">
-        <v>0.4045219076601765</v>
+        <v>0.3849647609257085</v>
       </c>
       <c r="AS6">
-        <v>0.4045219076601765</v>
+        <v>0.3849647609257085</v>
       </c>
       <c r="AT6">
-        <v>0.4045219076601765</v>
+        <v>0.3849647609257085</v>
       </c>
       <c r="AU6">
-        <v>0.4045219076601765</v>
+        <v>0.3849647609257085</v>
       </c>
       <c r="AV6">
-        <v>0.4045219076601765</v>
+        <v>0.3849647609257085</v>
       </c>
       <c r="AW6">
-        <v>0.4045219076601765</v>
+        <v>0.3849647609257085</v>
       </c>
       <c r="AX6">
-        <v>0.4045219076601765</v>
+        <v>0.3849647609257086</v>
       </c>
       <c r="AY6">
-        <v>0.4045219076601765</v>
+        <v>0.3849647609257086</v>
       </c>
       <c r="AZ6">
-        <v>0.4045219076601765</v>
+        <v>0.3849647609257086</v>
       </c>
       <c r="BA6">
-        <v>0.4045219076601765</v>
+        <v>0.3849647609257086</v>
       </c>
       <c r="BB6">
-        <v>0.4045219076601765</v>
+        <v>0.3849647609257086</v>
       </c>
       <c r="BC6">
-        <v>0.4045219076601765</v>
+        <v>0.3194454030324246</v>
       </c>
       <c r="BD6">
-        <v>0.4045219076601765</v>
+        <v>0.2539260451391406</v>
       </c>
       <c r="BE6">
-        <v>0.4045219076601765</v>
+        <v>0.2539260451391406</v>
       </c>
       <c r="BF6">
-        <v>0.4045219076601765</v>
+        <v>0.2539260451391406</v>
       </c>
       <c r="BG6">
-        <v>0.4045219076601765</v>
+        <v>0.2539260451391406</v>
       </c>
       <c r="BH6">
-        <v>0.3697861755796487</v>
+        <v>0.2539260451391406</v>
       </c>
       <c r="BI6">
-        <v>0.3350504434991208</v>
+        <v>0.2539260451391406</v>
       </c>
       <c r="BJ6">
-        <v>0.300314711418593</v>
+        <v>0.2539260451391406</v>
       </c>
       <c r="BK6">
-        <v>0.300314711418593</v>
+        <v>0.2539260451391406</v>
       </c>
       <c r="BL6">
-        <v>0.2304606608827331</v>
+        <v>0.2539260451391406</v>
       </c>
       <c r="BM6">
-        <v>0.2304606608827331</v>
+        <v>0.2539260451391406</v>
       </c>
       <c r="BN6">
-        <v>0.2304606608827331</v>
+        <v>0.2539260451391406</v>
       </c>
       <c r="BO6">
-        <v>0.2304606608827331</v>
+        <v>0.2539260451391406</v>
       </c>
       <c r="BP6">
-        <v>0.2242096417485092</v>
+        <v>0.2539260451391406</v>
       </c>
       <c r="BQ6">
-        <v>0.2242096417485092</v>
+        <v>0.2539260451391406</v>
       </c>
       <c r="BR6">
-        <v>0.2242096417485092</v>
+        <v>0.2539260451391406</v>
       </c>
       <c r="BS6">
-        <v>0.201984436869565</v>
+        <v>0.2539260451391406</v>
       </c>
       <c r="BT6">
-        <v>0.201984436869565</v>
+        <v>0.2539260451391406</v>
       </c>
       <c r="BU6">
-        <v>0.201984436869565</v>
+        <v>0.2539260451391406</v>
       </c>
       <c r="BV6">
-        <v>0.201984436869565</v>
+        <v>0.2539260451391406</v>
       </c>
       <c r="BW6">
-        <v>0.201984436869565</v>
+        <v>0.2539260451391406</v>
       </c>
       <c r="BX6">
-        <v>0.201984436869565</v>
+        <v>0.2539260451391406</v>
       </c>
       <c r="BY6">
-        <v>0.201984436869565</v>
+        <v>0.2539260451391406</v>
       </c>
       <c r="BZ6">
-        <v>0.201984436869565</v>
+        <v>0.2484633369533129</v>
       </c>
       <c r="CA6">
-        <v>0.201984436869565</v>
+        <v>0.2430006287674851</v>
       </c>
       <c r="CB6">
-        <v>0.201984436869565</v>
+        <v>0.2430006287674851</v>
       </c>
       <c r="CC6">
-        <v>0.201984436869565</v>
+        <v>0.2430006287674851</v>
       </c>
       <c r="CD6">
-        <v>0.201984436869565</v>
+        <v>0.2430006287674851</v>
       </c>
       <c r="CE6">
-        <v>0.201984436869565</v>
+        <v>0.2430006287674851</v>
       </c>
       <c r="CF6">
-        <v>0.201984436869565</v>
+        <v>0.2430006287674851</v>
       </c>
       <c r="CG6">
-        <v>0.201984436869565</v>
+        <v>0.2430006287674851</v>
       </c>
       <c r="CH6">
-        <v>0.201984436869565</v>
+        <v>0.2374776423415783</v>
       </c>
       <c r="CI6">
-        <v>0.201984436869565</v>
+        <v>0.2319546559156714</v>
       </c>
       <c r="CJ6">
-        <v>0.201984436869565</v>
+        <v>0.2319546559156714</v>
       </c>
       <c r="CK6">
-        <v>0.201984436869565</v>
+        <v>0.2319546559156714</v>
       </c>
       <c r="CL6">
-        <v>0.201984436869565</v>
+        <v>0.2319546559156714</v>
       </c>
       <c r="CM6">
-        <v>0.201984436869565</v>
+        <v>0.2319546559156714</v>
       </c>
       <c r="CN6">
-        <v>0.201984436869565</v>
+        <v>0.2319546559156714</v>
       </c>
       <c r="CO6">
-        <v>0.201984436869565</v>
+        <v>0.2319546559156714</v>
       </c>
       <c r="CP6">
-        <v>0.201984436869565</v>
+        <v>0.2319546559156714</v>
       </c>
       <c r="CQ6">
-        <v>0.201984436869565</v>
+        <v>0.2319546559156714</v>
       </c>
       <c r="CR6">
-        <v>0.201984436869565</v>
+        <v>0.2319546559156714</v>
       </c>
       <c r="CS6">
-        <v>0.201984436869565</v>
+        <v>0.2319546559156714</v>
       </c>
     </row>
     <row r="7" spans="1:97">
       <c r="A7" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B7">
         <v>0.2</v>
       </c>
       <c r="C7">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="D7">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="E7">
-        <v>0.26</v>
+        <v>0.8</v>
       </c>
       <c r="F7">
-        <v>0.26</v>
+        <v>0.8</v>
       </c>
       <c r="G7">
-        <v>0.26</v>
+        <v>0.8</v>
       </c>
       <c r="H7">
-        <v>0.32</v>
+        <v>0.8</v>
       </c>
       <c r="I7">
-        <v>0.32</v>
+        <v>0.8</v>
       </c>
       <c r="J7">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="K7">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="L7">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="M7">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="N7">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="O7">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="P7">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="Q7">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="R7">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="S7">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="T7">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="U7">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="V7">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="W7">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="X7">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="Y7">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="Z7">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AA7">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AB7">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AC7">
-        <v>0.5422304216716225</v>
+        <v>0.8</v>
       </c>
       <c r="AD7">
-        <v>0.5244608433432449</v>
+        <v>0.8</v>
       </c>
       <c r="AE7">
-        <v>0.5066912650148674</v>
+        <v>0.8</v>
       </c>
       <c r="AF7">
-        <v>0.4889216866864899</v>
+        <v>0.7684276495932569</v>
       </c>
       <c r="AG7">
-        <v>0.4711521083581124</v>
+        <v>0.7368552991865011</v>
       </c>
       <c r="AH7">
-        <v>0.4711521083581124</v>
+        <v>0.7052829487797451</v>
       </c>
       <c r="AI7">
-        <v>0.4508232061799597</v>
+        <v>0.6737105983729891</v>
       </c>
       <c r="AJ7">
-        <v>0.4304943040018071</v>
+        <v>0.6421382479662331</v>
       </c>
       <c r="AK7">
-        <v>0.4101654018236545</v>
+        <v>0.6105658975594772</v>
       </c>
       <c r="AL7">
-        <v>0.3898364996455018</v>
+        <v>0.6105658975594772</v>
       </c>
       <c r="AM7">
-        <v>0.3898364996455018</v>
+        <v>0.6105658975594842</v>
       </c>
       <c r="AN7">
-        <v>0.3898364996455019</v>
+        <v>0.6105658975594886</v>
       </c>
       <c r="AO7">
-        <v>0.3898364996455019</v>
+        <v>0.6105658975594925</v>
       </c>
       <c r="AP7">
-        <v>0.3898364996455019</v>
+        <v>0.610565897559495</v>
       </c>
       <c r="AQ7">
-        <v>0.3841035462950422</v>
+        <v>0.610565897559495</v>
       </c>
       <c r="AR7">
-        <v>0.3783705929445826</v>
+        <v>0.6105658975595066</v>
       </c>
       <c r="AS7">
-        <v>0.372637639594123</v>
+        <v>0.6105658975595066</v>
       </c>
       <c r="AT7">
-        <v>0.3669046862436634</v>
+        <v>0.6105658975595066</v>
       </c>
       <c r="AU7">
-        <v>0.3611717328932038</v>
+        <v>0.6105658975595066</v>
       </c>
       <c r="AV7">
-        <v>0.3611717328932038</v>
+        <v>0.5517284893096107</v>
       </c>
       <c r="AW7">
-        <v>0.3611717328932038</v>
+        <v>0.4928910810597149</v>
       </c>
       <c r="AX7">
-        <v>0.3611717328932038</v>
+        <v>0.4928910810597149</v>
       </c>
       <c r="AY7">
-        <v>0.3382483084660045</v>
+        <v>0.4462565262692784</v>
       </c>
       <c r="AZ7">
-        <v>0.3153248840388053</v>
+        <v>0.3996219714788419</v>
       </c>
       <c r="BA7">
-        <v>0.2924014596116061</v>
+        <v>0.3996219714788419</v>
       </c>
       <c r="BB7">
-        <v>0.2924014596116061</v>
+        <v>0.3996219714788419</v>
       </c>
       <c r="BC7">
-        <v>0.2924014596116061</v>
+        <v>0.3996219714788419</v>
       </c>
       <c r="BD7">
-        <v>0.2924014596116061</v>
+        <v>0.3996219714788419</v>
       </c>
       <c r="BE7">
-        <v>0.2924014596116061</v>
+        <v>0.3996219714788419</v>
       </c>
       <c r="BF7">
-        <v>0.2924014596116061</v>
+        <v>0.3393811512876453</v>
       </c>
       <c r="BG7">
-        <v>0.2924014596116061</v>
+        <v>0.2791403310964486</v>
       </c>
       <c r="BH7">
-        <v>0.2924014596116061</v>
+        <v>0.2791403310964486</v>
       </c>
       <c r="BI7">
-        <v>0.2924014596116061</v>
+        <v>0.241960028450452</v>
       </c>
       <c r="BJ7">
-        <v>0.2924014596116061</v>
+        <v>0.2047797258044554</v>
       </c>
       <c r="BK7">
-        <v>0.2774905322871875</v>
+        <v>0.2047797258044554</v>
       </c>
       <c r="BL7">
-        <v>0.2774905322871875</v>
+        <v>0.2047797258044554</v>
       </c>
       <c r="BM7">
-        <v>0.2401859649335139</v>
+        <v>0.2047797258044554</v>
       </c>
       <c r="BN7">
-        <v>0.2028813975798403</v>
+        <v>0.2047797258044554</v>
       </c>
       <c r="BO7">
-        <v>0.2028813975798403</v>
+        <v>0.2047797258044554</v>
       </c>
       <c r="BP7">
-        <v>0.2028813975798403</v>
+        <v>0.2047797258044554</v>
       </c>
       <c r="BQ7">
-        <v>0.2028813975798403</v>
+        <v>0.2047797258044554</v>
       </c>
       <c r="BR7">
-        <v>0.2028813975798403</v>
+        <v>0.2047797258044554</v>
       </c>
       <c r="BS7">
-        <v>0.2028813975798403</v>
+        <v>0.2047797258044554</v>
       </c>
       <c r="BT7">
-        <v>0.2028813975798403</v>
+        <v>0.2047797258044554</v>
       </c>
       <c r="BU7">
-        <v>0.2028813975798403</v>
+        <v>0.2047797258044554</v>
       </c>
       <c r="BV7">
-        <v>0.2028813975798403</v>
+        <v>0.2047797258044554</v>
       </c>
       <c r="BW7">
-        <v>0.2028813975798403</v>
+        <v>0.2047797258044554</v>
       </c>
       <c r="BX7">
-        <v>0.2028813975798403</v>
+        <v>0.2047797258044554</v>
       </c>
       <c r="BY7">
-        <v>0.2028813975798403</v>
+        <v>0.2047797258044554</v>
       </c>
       <c r="BZ7">
-        <v>0.2028813975798403</v>
+        <v>0.2047797258044554</v>
       </c>
       <c r="CA7">
-        <v>0.2028813975798403</v>
+        <v>0.2047797258044554</v>
       </c>
       <c r="CB7">
-        <v>0.2028813975798403</v>
+        <v>0.2047797258044554</v>
       </c>
       <c r="CC7">
-        <v>0.2028813975798403</v>
+        <v>0.2047797258044554</v>
       </c>
       <c r="CD7">
-        <v>0.2028813975798403</v>
+        <v>0.2047797258044554</v>
       </c>
       <c r="CE7">
-        <v>0.2028813975798403</v>
+        <v>0.2047797258044554</v>
       </c>
       <c r="CF7">
-        <v>0.2028813975798403</v>
+        <v>0.2047797258044554</v>
       </c>
       <c r="CG7">
-        <v>0.2028813975798403</v>
+        <v>0.2047797258044554</v>
       </c>
       <c r="CH7">
-        <v>0.2028813975798403</v>
+        <v>0.2047797258044554</v>
       </c>
       <c r="CI7">
-        <v>0.2028813975798403</v>
+        <v>0.2047797258044554</v>
       </c>
       <c r="CJ7">
-        <v>0.2028813975798403</v>
+        <v>0.2047797258044554</v>
       </c>
       <c r="CK7">
-        <v>0.2028813975798403</v>
+        <v>0.2047797258044554</v>
       </c>
       <c r="CL7">
-        <v>0.2028813975798403</v>
+        <v>0.2047797258044554</v>
       </c>
       <c r="CM7">
-        <v>0.2028813975798403</v>
+        <v>0.2047797258044554</v>
       </c>
       <c r="CN7">
-        <v>0.2028813975798403</v>
+        <v>0.2047797258044554</v>
       </c>
       <c r="CO7">
-        <v>0.2028813975798403</v>
+        <v>0.2047797258044554</v>
       </c>
       <c r="CP7">
-        <v>0.2028813975798403</v>
+        <v>0.2047797258044554</v>
       </c>
       <c r="CQ7">
-        <v>0.2028813975798403</v>
+        <v>0.2047797258044554</v>
       </c>
       <c r="CR7">
-        <v>0.2028813975798403</v>
+        <v>0.2047797258044554</v>
       </c>
       <c r="CS7">
-        <v>0.2028813975798403</v>
+        <v>0.2047797258044554</v>
       </c>
     </row>
     <row r="8" spans="1:97">
       <c r="A8" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B8">
         <v>0.2</v>
@@ -3700,291 +3549,291 @@
         <v>0.2</v>
       </c>
       <c r="D8">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="E8">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="F8">
-        <v>0.26</v>
+        <v>0.8</v>
       </c>
       <c r="G8">
-        <v>0.26</v>
+        <v>0.8</v>
       </c>
       <c r="H8">
-        <v>0.32</v>
+        <v>0.8</v>
       </c>
       <c r="I8">
-        <v>0.32</v>
+        <v>0.8</v>
       </c>
       <c r="J8">
-        <v>0.32</v>
+        <v>0.8</v>
       </c>
       <c r="K8">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="L8">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="M8">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="N8">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="O8">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="P8">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="Q8">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="R8">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="S8">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="T8">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="U8">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="V8">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="W8">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="X8">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="Y8">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="Z8">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="AA8">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AB8">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AC8">
-        <v>0.5504333071067173</v>
+        <v>0.8</v>
       </c>
       <c r="AD8">
-        <v>0.5408666142134603</v>
+        <v>0.7697316421033042</v>
       </c>
       <c r="AE8">
-        <v>0.531299921320202</v>
+        <v>0.7394632842066086</v>
       </c>
       <c r="AF8">
-        <v>0.5217332284269407</v>
+        <v>0.7091949263099128</v>
       </c>
       <c r="AG8">
-        <v>0.5121665355336817</v>
+        <v>0.6789265684132172</v>
       </c>
       <c r="AH8">
-        <v>0.5025998426404256</v>
+        <v>0.6486582105165214</v>
       </c>
       <c r="AI8">
-        <v>0.4930331497471709</v>
+        <v>0.6183898526198256</v>
       </c>
       <c r="AJ8">
-        <v>0.4930331497471709</v>
+        <v>0.6183898526198256</v>
       </c>
       <c r="AK8">
-        <v>0.4930331497471709</v>
+        <v>0.6183898526198256</v>
       </c>
       <c r="AL8">
-        <v>0.4930331497471709</v>
+        <v>0.6183898526198256</v>
       </c>
       <c r="AM8">
-        <v>0.4930331497471709</v>
+        <v>0.6183898526198256</v>
       </c>
       <c r="AN8">
-        <v>0.4930331497471709</v>
+        <v>0.5614583824415921</v>
       </c>
       <c r="AO8">
-        <v>0.4930331497471709</v>
+        <v>0.5045269122633584</v>
       </c>
       <c r="AP8">
-        <v>0.4930331497471446</v>
+        <v>0.4475954420851249</v>
       </c>
       <c r="AQ8">
-        <v>0.4930331497471421</v>
+        <v>0.4475954420851249</v>
       </c>
       <c r="AR8">
-        <v>0.4930331497471395</v>
+        <v>0.4475954420851249</v>
       </c>
       <c r="AS8">
-        <v>0.493033149747137</v>
+        <v>0.4475954420851249</v>
       </c>
       <c r="AT8">
-        <v>0.4930331497471336</v>
+        <v>0.4385621371413527</v>
       </c>
       <c r="AU8">
-        <v>0.4930331497471299</v>
+        <v>0.4295288321975805</v>
       </c>
       <c r="AV8">
-        <v>0.4930331497471299</v>
+        <v>0.4204955272538082</v>
       </c>
       <c r="AW8">
-        <v>0.4930331497471283</v>
+        <v>0.411462222310036</v>
       </c>
       <c r="AX8">
-        <v>0.4930331497471283</v>
+        <v>0.4024289173662637</v>
       </c>
       <c r="AY8">
-        <v>0.4930331497471264</v>
+        <v>0.4024289173662637</v>
       </c>
       <c r="AZ8">
-        <v>0.4930331497471233</v>
+        <v>0.402428917366264</v>
       </c>
       <c r="BA8">
-        <v>0.4574156320962692</v>
+        <v>0.4024289173662643</v>
       </c>
       <c r="BB8">
-        <v>0.4217981144454143</v>
+        <v>0.3495948826122601</v>
       </c>
       <c r="BC8">
-        <v>0.4217981144454143</v>
+        <v>0.3495948826122601</v>
       </c>
       <c r="BD8">
-        <v>0.4217981144454143</v>
+        <v>0.3495948826122601</v>
       </c>
       <c r="BE8">
-        <v>0.4217981144454143</v>
+        <v>0.3495948826122601</v>
       </c>
       <c r="BF8">
-        <v>0.4217981144454143</v>
+        <v>0.3495948826122601</v>
       </c>
       <c r="BG8">
-        <v>0.4217981144454143</v>
+        <v>0.3495948826122601</v>
       </c>
       <c r="BH8">
-        <v>0.3938107126828934</v>
+        <v>0.3495948826122601</v>
       </c>
       <c r="BI8">
-        <v>0.3658233109203725</v>
+        <v>0.3495948826122601</v>
       </c>
       <c r="BJ8">
-        <v>0.3378359091578516</v>
+        <v>0.3495948826122601</v>
       </c>
       <c r="BK8">
-        <v>0.3378359091578516</v>
+        <v>0.3495948826122601</v>
       </c>
       <c r="BL8">
-        <v>0.3378359091578516</v>
+        <v>0.3495948826122601</v>
       </c>
       <c r="BM8">
-        <v>0.3378359091578516</v>
+        <v>0.3495948826122601</v>
       </c>
       <c r="BN8">
-        <v>0.3378359091578516</v>
+        <v>0.3495948826122601</v>
       </c>
       <c r="BO8">
-        <v>0.3378359091578516</v>
+        <v>0.3495948826122601</v>
       </c>
       <c r="BP8">
-        <v>0.3378359091578516</v>
+        <v>0.3495948826122601</v>
       </c>
       <c r="BQ8">
-        <v>0.3378359091578516</v>
+        <v>0.3495948826122601</v>
       </c>
       <c r="BR8">
-        <v>0.2582045763676594</v>
+        <v>0.3495948826122601</v>
       </c>
       <c r="BS8">
-        <v>0.2582045763676594</v>
+        <v>0.3495948826122601</v>
       </c>
       <c r="BT8">
-        <v>0.2295520738490589</v>
+        <v>0.3495948826122601</v>
       </c>
       <c r="BU8">
-        <v>0.2008995713304584</v>
+        <v>0.3495948826122601</v>
       </c>
       <c r="BV8">
-        <v>0.2008995713304584</v>
+        <v>0.3495948826122601</v>
       </c>
       <c r="BW8">
-        <v>0.2008995713304584</v>
+        <v>0.3495948826122601</v>
       </c>
       <c r="BX8">
-        <v>0.2008995713304584</v>
+        <v>0.2760592880733344</v>
       </c>
       <c r="BY8">
-        <v>0.2008995713304584</v>
+        <v>0.2025236935344088</v>
       </c>
       <c r="BZ8">
-        <v>0.2008995713304584</v>
+        <v>0.2025236935344088</v>
       </c>
       <c r="CA8">
-        <v>0.2008995713304584</v>
+        <v>0.2025236935344088</v>
       </c>
       <c r="CB8">
-        <v>0.2008995713304584</v>
+        <v>0.2025236935344088</v>
       </c>
       <c r="CC8">
-        <v>0.2008995713304584</v>
+        <v>0.2025236935344088</v>
       </c>
       <c r="CD8">
-        <v>0.2008995713304584</v>
+        <v>0.2025236935344088</v>
       </c>
       <c r="CE8">
-        <v>0.2008995713304584</v>
+        <v>0.2025236935344088</v>
       </c>
       <c r="CF8">
-        <v>0.2008995713304584</v>
+        <v>0.2025236935344088</v>
       </c>
       <c r="CG8">
-        <v>0.2008995713304584</v>
+        <v>0.2025236935344088</v>
       </c>
       <c r="CH8">
-        <v>0.2008995713304584</v>
+        <v>0.2025236935344088</v>
       </c>
       <c r="CI8">
-        <v>0.2008995713304584</v>
+        <v>0.2025236935344088</v>
       </c>
       <c r="CJ8">
-        <v>0.2008995713304584</v>
+        <v>0.2025236935344088</v>
       </c>
       <c r="CK8">
-        <v>0.2008995713304584</v>
+        <v>0.2025236935344088</v>
       </c>
       <c r="CL8">
-        <v>0.2008995713304584</v>
+        <v>0.2025236935344088</v>
       </c>
       <c r="CM8">
-        <v>0.2008995713304584</v>
+        <v>0.2025236935344088</v>
       </c>
       <c r="CN8">
-        <v>0.2008995713304584</v>
+        <v>0.2025236935344088</v>
       </c>
       <c r="CO8">
-        <v>0.2008995713304584</v>
+        <v>0.2025236935344088</v>
       </c>
       <c r="CP8">
-        <v>0.2008995713304584</v>
+        <v>0.2025236935344088</v>
       </c>
       <c r="CQ8">
-        <v>0.2008995713304584</v>
+        <v>0.2025236935344088</v>
       </c>
       <c r="CR8">
-        <v>0.2008995713304584</v>
+        <v>0.2025236935344088</v>
       </c>
       <c r="CS8">
-        <v>0.2008995713304584</v>
+        <v>0.2025236935344088</v>
       </c>
     </row>
     <row r="9" spans="1:97">
       <c r="A9" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B9">
         <v>0.2</v>
@@ -3993,291 +3842,291 @@
         <v>0.2</v>
       </c>
       <c r="D9">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="E9">
-        <v>0.26</v>
+        <v>0.8</v>
       </c>
       <c r="F9">
-        <v>0.26</v>
+        <v>0.8</v>
       </c>
       <c r="G9">
-        <v>0.32</v>
+        <v>0.8</v>
       </c>
       <c r="H9">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="I9">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="J9">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="K9">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="L9">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="M9">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="N9">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="O9">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="P9">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="Q9">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="R9">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="S9">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="T9">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="U9">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="V9">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="W9">
-        <v>0.62</v>
+        <v>0.8</v>
       </c>
       <c r="X9">
-        <v>0.68</v>
+        <v>0.8</v>
       </c>
       <c r="Y9">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="Z9">
-        <v>0.7286415617055514</v>
+        <v>0.8</v>
       </c>
       <c r="AA9">
-        <v>0.717283123411115</v>
+        <v>0.7611800586498975</v>
       </c>
       <c r="AB9">
-        <v>0.7059246851166786</v>
+        <v>0.7223601172997949</v>
       </c>
       <c r="AC9">
-        <v>0.6945662468222431</v>
+        <v>0.6835401759496924</v>
       </c>
       <c r="AD9">
-        <v>0.683207808527807</v>
+        <v>0.6447202345995898</v>
       </c>
       <c r="AE9">
-        <v>0.6718493702333697</v>
+        <v>0.6059002932494872</v>
       </c>
       <c r="AF9">
-        <v>0.6604909319389284</v>
+        <v>0.5696655610534518</v>
       </c>
       <c r="AG9">
-        <v>0.6491324936444867</v>
+        <v>0.5334308288574163</v>
       </c>
       <c r="AH9">
-        <v>0.6288984584808552</v>
+        <v>0.4971960966613809</v>
       </c>
       <c r="AI9">
-        <v>0.608664423317223</v>
+        <v>0.4971960966613809</v>
       </c>
       <c r="AJ9">
-        <v>0.5884303881535914</v>
+        <v>0.4410211556409422</v>
       </c>
       <c r="AK9">
-        <v>0.5884303881535844</v>
+        <v>0.3848462146205034</v>
       </c>
       <c r="AL9">
-        <v>0.588430388153578</v>
+        <v>0.3286712736000647</v>
       </c>
       <c r="AM9">
-        <v>0.5884303881535735</v>
+        <v>0.9286712736000641</v>
       </c>
       <c r="AN9">
-        <v>0.5884303881535735</v>
+        <v>0.9286712736000641</v>
       </c>
       <c r="AO9">
-        <v>0.5884303881535735</v>
+        <v>0.9286712736000641</v>
       </c>
       <c r="AP9">
-        <v>0.5884303881535616</v>
+        <v>0.9286712736000641</v>
       </c>
       <c r="AQ9">
-        <v>0.5884303881535586</v>
+        <v>0.9286712736000641</v>
       </c>
       <c r="AR9">
-        <v>0.5884303881535586</v>
+        <v>0.9286712736000641</v>
       </c>
       <c r="AS9">
-        <v>0.5884303881535509</v>
+        <v>0.9286712736000641</v>
       </c>
       <c r="AT9">
-        <v>0.5884303881535472</v>
+        <v>0.9286712736000641</v>
       </c>
       <c r="AU9">
-        <v>0.5884303881535439</v>
+        <v>0.9286712736000641</v>
       </c>
       <c r="AV9">
-        <v>0.5884303881535413</v>
+        <v>0.9286712736000641</v>
       </c>
       <c r="AW9">
-        <v>0.5884303881535384</v>
+        <v>0.9286712736000641</v>
       </c>
       <c r="AX9">
-        <v>0.559381276942324</v>
+        <v>0.9286712736000641</v>
       </c>
       <c r="AY9">
-        <v>0.530332165731109</v>
+        <v>0.9286712736000641</v>
       </c>
       <c r="AZ9">
-        <v>0.4971365188705387</v>
+        <v>0.8622799798789235</v>
       </c>
       <c r="BA9">
-        <v>0.4639408720099673</v>
+        <v>0.7958886861577826</v>
       </c>
       <c r="BB9">
-        <v>0.4307452251493954</v>
+        <v>0.729497392436642</v>
       </c>
       <c r="BC9">
-        <v>0.4307452251493954</v>
+        <v>0.729497392436642</v>
       </c>
       <c r="BD9">
-        <v>0.4307452251493954</v>
+        <v>0.729497392436642</v>
       </c>
       <c r="BE9">
-        <v>0.4307452251493954</v>
+        <v>0.655626985447363</v>
       </c>
       <c r="BF9">
-        <v>0.4307452251493954</v>
+        <v>0.5817565784580838</v>
       </c>
       <c r="BG9">
-        <v>0.404025232258412</v>
+        <v>0.5817565784580838</v>
       </c>
       <c r="BH9">
-        <v>0.3773052393674285</v>
+        <v>0.5817565784580838</v>
       </c>
       <c r="BI9">
-        <v>0.3773052393674285</v>
+        <v>0.5817565784580838</v>
       </c>
       <c r="BJ9">
-        <v>0.3773052393674285</v>
+        <v>0.5128672737774215</v>
       </c>
       <c r="BK9">
-        <v>0.3773052393674275</v>
+        <v>0.4439779690967592</v>
       </c>
       <c r="BL9">
-        <v>0.3532945381721761</v>
+        <v>0.4439779690967592</v>
       </c>
       <c r="BM9">
-        <v>0.3292838369769248</v>
+        <v>0.4439779690967592</v>
       </c>
       <c r="BN9">
-        <v>0.3052731357816735</v>
+        <v>0.4439779690967592</v>
       </c>
       <c r="BO9">
-        <v>0.3052731357816735</v>
+        <v>0.4439779690967592</v>
       </c>
       <c r="BP9">
-        <v>0.2770976471128763</v>
+        <v>0.3692338404406071</v>
       </c>
       <c r="BQ9">
-        <v>0.2489221584440791</v>
+        <v>0.2944897117844552</v>
       </c>
       <c r="BR9">
-        <v>0.220746669775282</v>
+        <v>0.2944897117844552</v>
       </c>
       <c r="BS9">
-        <v>0.2207466697752812</v>
+        <v>0.2944897117844552</v>
       </c>
       <c r="BT9">
-        <v>0.2207466697752832</v>
+        <v>0.2944897117844552</v>
       </c>
       <c r="BU9">
-        <v>0.2001410859837891</v>
+        <v>0.2944897117844552</v>
       </c>
       <c r="BV9">
-        <v>0.2001410859837891</v>
+        <v>0.2944897117844552</v>
       </c>
       <c r="BW9">
-        <v>0.2001410859837891</v>
+        <v>0.2944897117844552</v>
       </c>
       <c r="BX9">
-        <v>0.2001410859837891</v>
+        <v>0.2944897117844552</v>
       </c>
       <c r="BY9">
-        <v>0.2001410859837891</v>
+        <v>0.2944897117844552</v>
       </c>
       <c r="BZ9">
-        <v>0.2001410859837891</v>
+        <v>0.2944897117844552</v>
       </c>
       <c r="CA9">
-        <v>0.2001410859837891</v>
+        <v>0.2944897117844552</v>
       </c>
       <c r="CB9">
-        <v>0.2001410859837891</v>
+        <v>0.2944897117844552</v>
       </c>
       <c r="CC9">
-        <v>0.2001410859837891</v>
+        <v>0.2944897117844552</v>
       </c>
       <c r="CD9">
-        <v>0.2001410859837891</v>
+        <v>0.2944897117844552</v>
       </c>
       <c r="CE9">
-        <v>0.2001410859837891</v>
+        <v>0.2944897117844552</v>
       </c>
       <c r="CF9">
-        <v>0.2001410859837891</v>
+        <v>0.2944897117844552</v>
       </c>
       <c r="CG9">
-        <v>0.2001410859837891</v>
+        <v>0.2944897117844552</v>
       </c>
       <c r="CH9">
-        <v>0.2001410859837891</v>
+        <v>0.2944897117844552</v>
       </c>
       <c r="CI9">
-        <v>0.2001410859837891</v>
+        <v>0.2944897117844552</v>
       </c>
       <c r="CJ9">
-        <v>0.2001410859837891</v>
+        <v>0.2944897117844552</v>
       </c>
       <c r="CK9">
-        <v>0.2001410859837891</v>
+        <v>0.2498428487151221</v>
       </c>
       <c r="CL9">
-        <v>0.2001410859837891</v>
+        <v>0.205195985645789</v>
       </c>
       <c r="CM9">
-        <v>0.2001410859837891</v>
+        <v>0.205195985645789</v>
       </c>
       <c r="CN9">
-        <v>0.2001410859837891</v>
+        <v>0.205195985645789</v>
       </c>
       <c r="CO9">
-        <v>0.2001410859837891</v>
+        <v>0.205195985645789</v>
       </c>
       <c r="CP9">
-        <v>0.2001410859837891</v>
+        <v>0.205195985645789</v>
       </c>
       <c r="CQ9">
-        <v>0.2001410859837891</v>
+        <v>0.205195985645789</v>
       </c>
       <c r="CR9">
-        <v>0.2001410859837891</v>
+        <v>0.205195985645789</v>
       </c>
       <c r="CS9">
-        <v>0.2001410859837891</v>
+        <v>0.205195985645789</v>
       </c>
     </row>
     <row r="10" spans="1:97">
       <c r="A10" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B10">
         <v>0.2</v>
@@ -4286,291 +4135,291 @@
         <v>0.2</v>
       </c>
       <c r="D10">
-        <v>0.26</v>
+        <v>0.8</v>
       </c>
       <c r="E10">
-        <v>0.26</v>
+        <v>0.8</v>
       </c>
       <c r="F10">
-        <v>0.26</v>
+        <v>0.8</v>
       </c>
       <c r="G10">
-        <v>0.32</v>
+        <v>0.8</v>
       </c>
       <c r="H10">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="I10">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="J10">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="K10">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="L10">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="M10">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="N10">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="O10">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="P10">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="Q10">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="R10">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="S10">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="T10">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="U10">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="V10">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="W10">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="X10">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="Y10">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="Z10">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="AA10">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AB10">
-        <v>0.5375288550706585</v>
+        <v>0.8</v>
       </c>
       <c r="AC10">
-        <v>0.515057710141273</v>
+        <v>0.8</v>
       </c>
       <c r="AD10">
-        <v>0.4925865652118875</v>
+        <v>0.7560235503215235</v>
       </c>
       <c r="AE10">
-        <v>0.4925865652118875</v>
+        <v>0.7120471006430468</v>
       </c>
       <c r="AF10">
-        <v>0.4768003900085095</v>
+        <v>0.6680706509645702</v>
       </c>
       <c r="AG10">
-        <v>0.4610142148051316</v>
+        <v>0.6680706509645702</v>
       </c>
       <c r="AH10">
-        <v>0.4452280396017536</v>
+        <v>0.6290606572904003</v>
       </c>
       <c r="AI10">
-        <v>0.4294418643983755</v>
+        <v>0.5900506636162303</v>
       </c>
       <c r="AJ10">
-        <v>0.4136556891949976</v>
+        <v>0.5510406699420604</v>
       </c>
       <c r="AK10">
-        <v>0.3978695139916196</v>
+        <v>0.5120306762678903</v>
       </c>
       <c r="AL10">
-        <v>0.3978695139916196</v>
+        <v>0.5120306762678903</v>
       </c>
       <c r="AM10">
-        <v>0.3978695139916196</v>
+        <v>0.5120306762678903</v>
       </c>
       <c r="AN10">
-        <v>0.3978695139916196</v>
+        <v>0.5120306762678903</v>
       </c>
       <c r="AO10">
-        <v>0.3978695139916196</v>
+        <v>0.5120306762678903</v>
       </c>
       <c r="AP10">
-        <v>0.3978695139916196</v>
+        <v>0.5120306762678903</v>
       </c>
       <c r="AQ10">
-        <v>0.3978695139916196</v>
+        <v>0.5120306762678903</v>
       </c>
       <c r="AR10">
-        <v>0.3978695139916196</v>
+        <v>0.5120306762678903</v>
       </c>
       <c r="AS10">
-        <v>0.3929201693165391</v>
+        <v>0.5120306762678903</v>
       </c>
       <c r="AT10">
-        <v>0.3879708246414585</v>
+        <v>0.5120306762678903</v>
       </c>
       <c r="AU10">
-        <v>0.383021479966378</v>
+        <v>0.5120306762678903</v>
       </c>
       <c r="AV10">
-        <v>0.3780721352912974</v>
+        <v>0.5120306762678903</v>
       </c>
       <c r="AW10">
-        <v>0.3731227906162168</v>
+        <v>0.5120306762678903</v>
       </c>
       <c r="AX10">
-        <v>0.3731227906162168</v>
+        <v>0.5120306762678903</v>
       </c>
       <c r="AY10">
-        <v>0.3731227906162168</v>
+        <v>0.5120306762678903</v>
       </c>
       <c r="AZ10">
-        <v>0.3731227906162168</v>
+        <v>0.5120306762678903</v>
       </c>
       <c r="BA10">
-        <v>0.3731227906162168</v>
+        <v>0.5120306762678903</v>
       </c>
       <c r="BB10">
-        <v>0.3731227906162168</v>
+        <v>0.5120306762678903</v>
       </c>
       <c r="BC10">
-        <v>0.3731227906162168</v>
+        <v>0.5120306762678903</v>
       </c>
       <c r="BD10">
-        <v>0.3731227906162168</v>
+        <v>0.5120306762678903</v>
       </c>
       <c r="BE10">
-        <v>0.3403631116695749</v>
+        <v>0.4569082663047908</v>
       </c>
       <c r="BF10">
-        <v>0.3076034327229329</v>
+        <v>0.4017858563416913</v>
       </c>
       <c r="BG10">
-        <v>0.3076034327229329</v>
+        <v>0.4017858563416913</v>
       </c>
       <c r="BH10">
-        <v>0.2714924376965032</v>
+        <v>0.4017858563416913</v>
       </c>
       <c r="BI10">
-        <v>0.2714924376965032</v>
+        <v>0.4017858563416913</v>
       </c>
       <c r="BJ10">
-        <v>0.2714924376965031</v>
+        <v>0.4017858563416913</v>
       </c>
       <c r="BK10">
-        <v>0.2714924376965031</v>
+        <v>0.4017858563416913</v>
       </c>
       <c r="BL10">
-        <v>0.2714924376965031</v>
+        <v>0.4017858563416913</v>
       </c>
       <c r="BM10">
-        <v>0.2714924376965031</v>
+        <v>0.3454429798033409</v>
       </c>
       <c r="BN10">
-        <v>0.2714924376965031</v>
+        <v>0.3454429798033409</v>
       </c>
       <c r="BO10">
-        <v>0.2714924376965031</v>
+        <v>0.3454429798033409</v>
       </c>
       <c r="BP10">
-        <v>0.2714924376965031</v>
+        <v>0.2034413381818072</v>
       </c>
       <c r="BQ10">
-        <v>0.2714924376965031</v>
+        <v>0.2034413381818072</v>
       </c>
       <c r="BR10">
-        <v>0.2684314806233365</v>
+        <v>0.2034413381818072</v>
       </c>
       <c r="BS10">
-        <v>0.2684314806233365</v>
+        <v>0.2034413381818072</v>
       </c>
       <c r="BT10">
-        <v>0.2684314806233365</v>
+        <v>0.2034413381818072</v>
       </c>
       <c r="BU10">
-        <v>0.2684314806233365</v>
+        <v>0.2034413381818072</v>
       </c>
       <c r="BV10">
-        <v>0.2684314806233365</v>
+        <v>0.2034413381818072</v>
       </c>
       <c r="BW10">
-        <v>0.2473765898224805</v>
+        <v>0.2034413381818072</v>
       </c>
       <c r="BX10">
-        <v>0.2263216990216245</v>
+        <v>0.2034413381818072</v>
       </c>
       <c r="BY10">
-        <v>0.2017672301061697</v>
+        <v>0.2034413381818072</v>
       </c>
       <c r="BZ10">
-        <v>0.2017672301061697</v>
+        <v>0.2034413381818072</v>
       </c>
       <c r="CA10">
-        <v>0.2017672301061697</v>
+        <v>0.2034413381818072</v>
       </c>
       <c r="CB10">
-        <v>0.2017672301061697</v>
+        <v>0.2034413381818072</v>
       </c>
       <c r="CC10">
-        <v>0.2017672301061697</v>
+        <v>0.2034413381818072</v>
       </c>
       <c r="CD10">
-        <v>0.2017672301061697</v>
+        <v>0.2034413381818072</v>
       </c>
       <c r="CE10">
-        <v>0.2017672301061697</v>
+        <v>0.2034413381818072</v>
       </c>
       <c r="CF10">
-        <v>0.2017672301061697</v>
+        <v>0.2034413381818072</v>
       </c>
       <c r="CG10">
-        <v>0.2017672301061697</v>
+        <v>0.2034413381818072</v>
       </c>
       <c r="CH10">
-        <v>0.2017672301061697</v>
+        <v>0.2034413381818072</v>
       </c>
       <c r="CI10">
-        <v>0.2017672301061697</v>
+        <v>0.2034413381818072</v>
       </c>
       <c r="CJ10">
-        <v>0.2017672301061697</v>
+        <v>0.2034413381818072</v>
       </c>
       <c r="CK10">
-        <v>0.2017672301061602</v>
+        <v>0.2034413381818072</v>
       </c>
       <c r="CL10">
-        <v>0.2017672301061508</v>
+        <v>0.2034413381818072</v>
       </c>
       <c r="CM10">
-        <v>0.2017672301061508</v>
+        <v>0.2034413381818072</v>
       </c>
       <c r="CN10">
-        <v>0.2017672301061508</v>
+        <v>0.2034413381818072</v>
       </c>
       <c r="CO10">
-        <v>0.2017672301061508</v>
+        <v>0.2034413381818072</v>
       </c>
       <c r="CP10">
-        <v>0.2017672301061508</v>
+        <v>0.2034413381818072</v>
       </c>
       <c r="CQ10">
-        <v>0.2017672301061508</v>
+        <v>0.2034413381818072</v>
       </c>
       <c r="CR10">
-        <v>0.2017672301061508</v>
+        <v>0.2034413381818072</v>
       </c>
       <c r="CS10">
-        <v>0.2017672301061508</v>
+        <v>0.2034413381818072</v>
       </c>
     </row>
     <row r="11" spans="1:97">
       <c r="A11" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B11">
         <v>0.2</v>
@@ -4579,1463 +4428,1463 @@
         <v>0.2</v>
       </c>
       <c r="D11">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="E11">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="F11">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="G11">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="H11">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="I11">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="J11">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="K11">
-        <v>0.26</v>
+        <v>0.8</v>
       </c>
       <c r="L11">
-        <v>0.26</v>
+        <v>0.8</v>
       </c>
       <c r="M11">
-        <v>0.26</v>
+        <v>0.8</v>
       </c>
       <c r="N11">
-        <v>0.26</v>
+        <v>0.8</v>
       </c>
       <c r="O11">
-        <v>0.26</v>
+        <v>0.8</v>
       </c>
       <c r="P11">
-        <v>0.26</v>
+        <v>0.8</v>
       </c>
       <c r="Q11">
-        <v>0.26</v>
+        <v>0.8</v>
       </c>
       <c r="R11">
-        <v>0.32</v>
+        <v>0.8</v>
       </c>
       <c r="S11">
-        <v>0.32</v>
+        <v>0.8</v>
       </c>
       <c r="T11">
-        <v>0.32</v>
+        <v>0.8</v>
       </c>
       <c r="U11">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="V11">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="W11">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="X11">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="Y11">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="Z11">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="AA11">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="AB11">
-        <v>0.4212057227035149</v>
+        <v>0.7624114454070294</v>
       </c>
       <c r="AC11">
-        <v>0.4024114454070296</v>
+        <v>0.7248228908140587</v>
       </c>
       <c r="AD11">
-        <v>0.3836171681105443</v>
+        <v>0.6872343362210881</v>
       </c>
       <c r="AE11">
-        <v>0.364822890814059</v>
+        <v>0.6496457816281176</v>
       </c>
       <c r="AF11">
-        <v>0.3460286135175737</v>
+        <v>0.612057227035147</v>
       </c>
       <c r="AG11">
-        <v>0.3270540677448907</v>
+        <v>0.612057227035147</v>
       </c>
       <c r="AH11">
-        <v>0.3080795219722077</v>
+        <v>0.612057227035147</v>
       </c>
       <c r="AI11">
-        <v>0.3080795219722077</v>
+        <v>0.5852654952269496</v>
       </c>
       <c r="AJ11">
-        <v>0.3080795219722077</v>
+        <v>0.5584737634187521</v>
       </c>
       <c r="AK11">
-        <v>0.3080795219722077</v>
+        <v>0.5316820316105552</v>
       </c>
       <c r="AL11">
-        <v>0.3080795219722077</v>
+        <v>0.5048902998023582</v>
       </c>
       <c r="AM11">
-        <v>0.3080795219722077</v>
+        <v>0.504890299802361</v>
       </c>
       <c r="AN11">
-        <v>0.3080795219722077</v>
+        <v>0.504890299802361</v>
       </c>
       <c r="AO11">
-        <v>0.3080795219722077</v>
+        <v>0.504890299802361</v>
       </c>
       <c r="AP11">
-        <v>0.3080795219722077</v>
+        <v>0.504890299802361</v>
       </c>
       <c r="AQ11">
-        <v>0.3080795219722077</v>
+        <v>0.504890299802361</v>
       </c>
       <c r="AR11">
-        <v>0.3080795219722077</v>
+        <v>0.504890299802361</v>
       </c>
       <c r="AS11">
-        <v>0.3080795219722077</v>
+        <v>0.504890299802361</v>
       </c>
       <c r="AT11">
-        <v>0.3080795219722077</v>
+        <v>0.504890299802361</v>
       </c>
       <c r="AU11">
-        <v>0.3080795219722077</v>
+        <v>0.504890299802361</v>
       </c>
       <c r="AV11">
-        <v>0.3080795219722077</v>
+        <v>0.504890299802361</v>
       </c>
       <c r="AW11">
-        <v>0.3080795219722077</v>
+        <v>0.504890299802361</v>
       </c>
       <c r="AX11">
-        <v>0.3080795219722077</v>
+        <v>0.504890299802361</v>
       </c>
       <c r="AY11">
-        <v>0.3080795219722077</v>
+        <v>0.504890299802361</v>
       </c>
       <c r="AZ11">
-        <v>0.3080795219722077</v>
+        <v>0.504890299802361</v>
       </c>
       <c r="BA11">
-        <v>0.3080795219722077</v>
+        <v>0.504890299802361</v>
       </c>
       <c r="BB11">
-        <v>0.3080795219722076</v>
+        <v>0.504890299802361</v>
       </c>
       <c r="BC11">
-        <v>0.3080795219722076</v>
+        <v>0.504890299802361</v>
       </c>
       <c r="BD11">
-        <v>0.3080795219722076</v>
+        <v>0.504890299802361</v>
       </c>
       <c r="BE11">
-        <v>0.3080795219722076</v>
+        <v>0.504890299802361</v>
       </c>
       <c r="BF11">
-        <v>0.3080795219722076</v>
+        <v>0.504890299802361</v>
       </c>
       <c r="BG11">
-        <v>0.3080795219722076</v>
+        <v>0.504890299802361</v>
       </c>
       <c r="BH11">
-        <v>0.3080795219722076</v>
+        <v>0.43266830974953</v>
       </c>
       <c r="BI11">
-        <v>0.3080795219722076</v>
+        <v>0.43266830974953</v>
       </c>
       <c r="BJ11">
-        <v>0.3080795219722076</v>
+        <v>0.43266830974953</v>
       </c>
       <c r="BK11">
-        <v>0.3080795219722076</v>
+        <v>0.43266830974953</v>
       </c>
       <c r="BL11">
-        <v>0.3080795219722076</v>
+        <v>0.43266830974953</v>
       </c>
       <c r="BM11">
-        <v>0.2799080837030324</v>
+        <v>0.43266830974953</v>
       </c>
       <c r="BN11">
-        <v>0.2799080837030324</v>
+        <v>0.43266830974953</v>
       </c>
       <c r="BO11">
-        <v>0.2628349308641378</v>
+        <v>0.43266830974953</v>
       </c>
       <c r="BP11">
-        <v>0.2457617780252433</v>
+        <v>0.420166271481082</v>
       </c>
       <c r="BQ11">
-        <v>0.2457617780252433</v>
+        <v>0.420166271481082</v>
       </c>
       <c r="BR11">
-        <v>0.2230909286311845</v>
+        <v>0.420166271481082</v>
       </c>
       <c r="BS11">
-        <v>0.2004200792371257</v>
+        <v>0.420166271481082</v>
       </c>
       <c r="BT11">
-        <v>0.2004200792371257</v>
+        <v>0.3646183227345426</v>
       </c>
       <c r="BU11">
-        <v>0.2004200792371257</v>
+        <v>0.3090703739880031</v>
       </c>
       <c r="BV11">
-        <v>0.2004200792371257</v>
+        <v>0.2535224252414636</v>
       </c>
       <c r="BW11">
-        <v>0.2004200792371257</v>
+        <v>0.2020606547545913</v>
       </c>
       <c r="BX11">
-        <v>0.2004200792371257</v>
+        <v>0.2020606547545913</v>
       </c>
       <c r="BY11">
-        <v>0.2004200792371257</v>
+        <v>0.2020606547545913</v>
       </c>
       <c r="BZ11">
-        <v>0.2004200792371257</v>
+        <v>0.8020606547545913</v>
       </c>
       <c r="CA11">
-        <v>0.2004200792371257</v>
+        <v>0.7465193621777949</v>
       </c>
       <c r="CB11">
-        <v>0.2004200792371257</v>
+        <v>0.6864341092831071</v>
       </c>
       <c r="CC11">
-        <v>0.2004200792371257</v>
+        <v>0.6263488563884193</v>
       </c>
       <c r="CD11">
-        <v>0.2004200792371257</v>
+        <v>0.6263488563884193</v>
       </c>
       <c r="CE11">
-        <v>0.2004200792371257</v>
+        <v>0.5841744047231625</v>
       </c>
       <c r="CF11">
-        <v>0.2004200792371257</v>
+        <v>0.5186217524590654</v>
       </c>
       <c r="CG11">
-        <v>0.2004200792371257</v>
+        <v>0.4530691001949683</v>
       </c>
       <c r="CH11">
-        <v>0.2004200792371257</v>
+        <v>0.4530691001949683</v>
       </c>
       <c r="CI11">
-        <v>0.2004200792371257</v>
+        <v>0.4530691001949683</v>
       </c>
       <c r="CJ11">
-        <v>0.2004200792371257</v>
+        <v>0.4530691001949683</v>
       </c>
       <c r="CK11">
-        <v>0.2004200792371257</v>
+        <v>0.4530691001949683</v>
       </c>
       <c r="CL11">
-        <v>0.2004200792371257</v>
+        <v>0.4530691001949683</v>
       </c>
       <c r="CM11">
-        <v>0.2004200792371257</v>
+        <v>0.4056468003472211</v>
       </c>
       <c r="CN11">
-        <v>0.2004200792371257</v>
+        <v>0.358224500499474</v>
       </c>
       <c r="CO11">
-        <v>0.2004200792371257</v>
+        <v>0.358224500499474</v>
       </c>
       <c r="CP11">
-        <v>0.2004200792371257</v>
+        <v>0.2923393653654045</v>
       </c>
       <c r="CQ11">
-        <v>0.2004200792371257</v>
+        <v>0.226454230231335</v>
       </c>
       <c r="CR11">
-        <v>0.2004200792371257</v>
+        <v>0.226454230231335</v>
       </c>
       <c r="CS11">
-        <v>0.2004200792371257</v>
+        <v>0.226454230231335</v>
       </c>
     </row>
     <row r="12" spans="1:97">
       <c r="A12" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B12">
         <v>0.2</v>
       </c>
       <c r="C12">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="D12">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="E12">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="F12">
-        <v>0.32</v>
+        <v>0.2</v>
       </c>
       <c r="G12">
-        <v>0.32</v>
+        <v>0.8</v>
       </c>
       <c r="H12">
-        <v>0.32</v>
+        <v>0.8</v>
       </c>
       <c r="I12">
-        <v>0.32</v>
+        <v>0.8</v>
       </c>
       <c r="J12">
-        <v>0.32</v>
+        <v>0.8</v>
       </c>
       <c r="K12">
-        <v>0.32</v>
+        <v>0.8</v>
       </c>
       <c r="L12">
-        <v>0.32</v>
+        <v>0.8</v>
       </c>
       <c r="M12">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="N12">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="O12">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="P12">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="Q12">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="R12">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="S12">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="T12">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="U12">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="V12">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="W12">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="X12">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="Y12">
-        <v>0.62</v>
+        <v>0.8</v>
       </c>
       <c r="Z12">
-        <v>0.6011378983886542</v>
+        <v>0.777283123411144</v>
       </c>
       <c r="AA12">
-        <v>0.5822757967773097</v>
+        <v>0.754566246822281</v>
       </c>
       <c r="AB12">
-        <v>0.5634136951659655</v>
+        <v>0.7318493702334181</v>
       </c>
       <c r="AC12">
-        <v>0.5445515935546212</v>
+        <v>0.7091324936445552</v>
       </c>
       <c r="AD12">
-        <v>0.544551593554619</v>
+        <v>0.6864156170556922</v>
       </c>
       <c r="AE12">
-        <v>0.5261216491353077</v>
+        <v>0.6636987404668292</v>
       </c>
       <c r="AF12">
-        <v>0.5076917047159928</v>
+        <v>0.6409818638779663</v>
       </c>
       <c r="AG12">
-        <v>0.4892617602966762</v>
+        <v>0.6182649872891034</v>
       </c>
       <c r="AH12">
-        <v>0.470831815877358</v>
+        <v>0.6182649872891034</v>
       </c>
       <c r="AI12">
-        <v>0.452401871458039</v>
+        <v>0.6182649872891034</v>
       </c>
       <c r="AJ12">
-        <v>0.45240187145803</v>
+        <v>0.6182649872891034</v>
       </c>
       <c r="AK12">
-        <v>0.4524018714580233</v>
+        <v>0.6182649872891034</v>
       </c>
       <c r="AL12">
-        <v>0.4524018714580173</v>
+        <v>0.6182649872891034</v>
       </c>
       <c r="AM12">
-        <v>0.4524018714580132</v>
+        <v>0.6182649872891034</v>
       </c>
       <c r="AN12">
-        <v>0.4524018714580132</v>
+        <v>0.6182649872891034</v>
       </c>
       <c r="AO12">
-        <v>0.4524018714580132</v>
+        <v>0.6182649872891034</v>
       </c>
       <c r="AP12">
-        <v>0.4524018714580025</v>
+        <v>0.6182649872891034</v>
       </c>
       <c r="AQ12">
-        <v>0.452401871458</v>
+        <v>0.6182649872891034</v>
       </c>
       <c r="AR12">
-        <v>0.4524018714579967</v>
+        <v>0.5625486936137294</v>
       </c>
       <c r="AS12">
-        <v>0.4524018714579926</v>
+        <v>0.5068323999383554</v>
       </c>
       <c r="AT12">
-        <v>0.4524018714579882</v>
+        <v>0.4511161062629814</v>
       </c>
       <c r="AU12">
-        <v>0.4490210096025617</v>
+        <v>0.4511161062629814</v>
       </c>
       <c r="AV12">
-        <v>0.4456401477471354</v>
+        <v>0.4511161062629814</v>
       </c>
       <c r="AW12">
-        <v>0.4422592858917088</v>
+        <v>0.4511161062629814</v>
       </c>
       <c r="AX12">
-        <v>0.4388784240362827</v>
+        <v>0.4511161062629823</v>
       </c>
       <c r="AY12">
-        <v>0.4354975621808558</v>
+        <v>0.4511161062629823</v>
       </c>
       <c r="AZ12">
-        <v>0.4321167003254264</v>
+        <v>0.4511161062629823</v>
       </c>
       <c r="BA12">
-        <v>0.4287358384699972</v>
+        <v>0.4511161062629824</v>
       </c>
       <c r="BB12">
-        <v>0.4287358384699972</v>
+        <v>0.4511161062629831</v>
       </c>
       <c r="BC12">
-        <v>0.4287358384699972</v>
+        <v>0.4034957592238844</v>
       </c>
       <c r="BD12">
-        <v>0.4287358384699972</v>
+        <v>0.3558754121847858</v>
       </c>
       <c r="BE12">
-        <v>0.3918006349753577</v>
+        <v>0.3558754121847861</v>
       </c>
       <c r="BF12">
-        <v>0.3548654314807181</v>
+        <v>0.284738623638212</v>
       </c>
       <c r="BG12">
-        <v>0.3548654314807181</v>
+        <v>0.284738623638212</v>
       </c>
       <c r="BH12">
-        <v>0.3548654314807181</v>
+        <v>0.284738623638212</v>
       </c>
       <c r="BI12">
-        <v>0.3548654314807181</v>
+        <v>0.284738623638212</v>
       </c>
       <c r="BJ12">
-        <v>0.3548654314807181</v>
+        <v>0.284738623638212</v>
       </c>
       <c r="BK12">
-        <v>0.3548654314807181</v>
+        <v>0.284738623638212</v>
       </c>
       <c r="BL12">
-        <v>0.3548654314807181</v>
+        <v>0.284738623638212</v>
       </c>
       <c r="BM12">
-        <v>0.3548654314807181</v>
+        <v>0.284738623638212</v>
       </c>
       <c r="BN12">
-        <v>0.3548654314807181</v>
+        <v>0.284738623638212</v>
       </c>
       <c r="BO12">
-        <v>0.3548654314807181</v>
+        <v>0.284738623638212</v>
       </c>
       <c r="BP12">
-        <v>0.3174933671526421</v>
+        <v>0.284738623638212</v>
       </c>
       <c r="BQ12">
-        <v>0.2801213028245661</v>
+        <v>0.284738623638212</v>
       </c>
       <c r="BR12">
-        <v>0.2801213028245661</v>
+        <v>0.284738623638212</v>
       </c>
       <c r="BS12">
-        <v>0.2801213028245661</v>
+        <v>0.284738623638212</v>
       </c>
       <c r="BT12">
-        <v>0.2801213028245661</v>
+        <v>0.284738623638212</v>
       </c>
       <c r="BU12">
-        <v>0.2801213028245661</v>
+        <v>0.284738623638212</v>
       </c>
       <c r="BV12">
-        <v>0.2801213028245661</v>
+        <v>0.284738623638212</v>
       </c>
       <c r="BW12">
-        <v>0.2801213028245661</v>
+        <v>0.284738623638212</v>
       </c>
       <c r="BX12">
-        <v>0.2433535055551033</v>
+        <v>0.284738623638212</v>
       </c>
       <c r="BY12">
-        <v>0.2065857082856404</v>
+        <v>0.242644592811546</v>
       </c>
       <c r="BZ12">
-        <v>0.2065857082856404</v>
+        <v>0.2005505619848802</v>
       </c>
       <c r="CA12">
-        <v>0.2065857082856404</v>
+        <v>0.2005505619848802</v>
       </c>
       <c r="CB12">
-        <v>0.2065857082856404</v>
+        <v>0.2005505619848802</v>
       </c>
       <c r="CC12">
-        <v>0.2065857082856404</v>
+        <v>0.2005505619848802</v>
       </c>
       <c r="CD12">
-        <v>0.2065857082856404</v>
+        <v>0.2005505619848802</v>
       </c>
       <c r="CE12">
-        <v>0.2065857082856404</v>
+        <v>0.2005505619848802</v>
       </c>
       <c r="CF12">
-        <v>0.2065857082856404</v>
+        <v>0.2005505619848802</v>
       </c>
       <c r="CG12">
-        <v>0.2065857082856404</v>
+        <v>0.2005505619848802</v>
       </c>
       <c r="CH12">
-        <v>0.2065857082856404</v>
+        <v>0.2005505619848802</v>
       </c>
       <c r="CI12">
-        <v>0.2065857082856404</v>
+        <v>0.2005505619848802</v>
       </c>
       <c r="CJ12">
-        <v>0.2065857082856405</v>
+        <v>0.2005505619848802</v>
       </c>
       <c r="CK12">
-        <v>0.2065857082856405</v>
+        <v>0.2005505619848802</v>
       </c>
       <c r="CL12">
-        <v>0.2065857082856405</v>
+        <v>0.2005505619848802</v>
       </c>
       <c r="CM12">
-        <v>0.2065857082856404</v>
+        <v>0.2005505619848802</v>
       </c>
       <c r="CN12">
-        <v>0.2065857082856404</v>
+        <v>0.2005505619848802</v>
       </c>
       <c r="CO12">
-        <v>0.2665857082856404</v>
+        <v>0.2005505619848802</v>
       </c>
       <c r="CP12">
-        <v>0.2336431407186057</v>
+        <v>0.2005505619848802</v>
       </c>
       <c r="CQ12">
-        <v>0.200700573151571</v>
+        <v>0.2005505619848802</v>
       </c>
       <c r="CR12">
-        <v>0.200700573151571</v>
+        <v>0.2005505619848802</v>
       </c>
       <c r="CS12">
-        <v>0.200700573151571</v>
+        <v>0.2005505619848802</v>
       </c>
     </row>
     <row r="13" spans="1:97">
       <c r="A13" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B13">
         <v>0.2</v>
       </c>
       <c r="C13">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="D13">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="E13">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="F13">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="G13">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="H13">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="I13">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="J13">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="K13">
-        <v>0.32</v>
+        <v>0.2</v>
       </c>
       <c r="L13">
-        <v>0.38</v>
+        <v>0.2</v>
       </c>
       <c r="M13">
-        <v>0.38</v>
+        <v>0.2</v>
       </c>
       <c r="N13">
-        <v>0.38</v>
+        <v>0.2</v>
       </c>
       <c r="O13">
-        <v>0.38</v>
+        <v>0.2</v>
       </c>
       <c r="P13">
-        <v>0.38</v>
+        <v>0.2</v>
       </c>
       <c r="Q13">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="R13">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="S13">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="T13">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="U13">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="V13">
-        <v>0.62</v>
+        <v>0.8</v>
       </c>
       <c r="W13">
-        <v>0.62</v>
+        <v>0.8</v>
       </c>
       <c r="X13">
-        <v>0.62</v>
+        <v>0.7601824340204393</v>
       </c>
       <c r="Y13">
-        <v>0.62</v>
+        <v>0.7203648680407569</v>
       </c>
       <c r="Z13">
-        <v>0.62</v>
+        <v>0.6805473020610747</v>
       </c>
       <c r="AA13">
-        <v>0.62</v>
+        <v>0.6407297360813929</v>
       </c>
       <c r="AB13">
-        <v>0.62</v>
+        <v>0.6009121701017412</v>
       </c>
       <c r="AC13">
-        <v>0.6017424237088689</v>
+        <v>0.6009121701017456</v>
       </c>
       <c r="AD13">
-        <v>0.5834848474177379</v>
+        <v>0.5697715631939532</v>
       </c>
       <c r="AE13">
-        <v>0.5652272711266066</v>
+        <v>0.5386309562861606</v>
       </c>
       <c r="AF13">
-        <v>0.5469696948354755</v>
+        <v>0.5074903493783682</v>
       </c>
       <c r="AG13">
-        <v>0.5257481787608352</v>
+        <v>0.4763497424705758</v>
       </c>
       <c r="AH13">
-        <v>0.5045266626861949</v>
+        <v>0.4452091355627835</v>
       </c>
       <c r="AI13">
-        <v>0.4833051466115546</v>
+        <v>0.4452091355627835</v>
       </c>
       <c r="AJ13">
-        <v>0.4620836305369143</v>
+        <v>0.4452091355627835</v>
       </c>
       <c r="AK13">
-        <v>0.4455827604855617</v>
+        <v>0.4452091355627835</v>
       </c>
       <c r="AL13">
-        <v>0.4290818904342091</v>
+        <v>0.4452091355627835</v>
       </c>
       <c r="AM13">
-        <v>0.4125810203828565</v>
+        <v>0.4452091355627835</v>
       </c>
       <c r="AN13">
-        <v>0.4125810203828565</v>
+        <v>0.4452091355627835</v>
       </c>
       <c r="AO13">
-        <v>0.4125810203828565</v>
+        <v>0.4452091355627835</v>
       </c>
       <c r="AP13">
-        <v>0.4125810203828565</v>
+        <v>0.4452091355627835</v>
       </c>
       <c r="AQ13">
-        <v>0.4125810203828565</v>
+        <v>0.4452091355627835</v>
       </c>
       <c r="AR13">
-        <v>0.4125810203828565</v>
+        <v>0.4452091355627835</v>
       </c>
       <c r="AS13">
-        <v>0.4125810203828565</v>
+        <v>0.4452091355627835</v>
       </c>
       <c r="AT13">
-        <v>0.4125810203828565</v>
+        <v>0.4452091355627835</v>
       </c>
       <c r="AU13">
-        <v>0.4125810203828565</v>
+        <v>0.4452091355627835</v>
       </c>
       <c r="AV13">
-        <v>0.4125810203828565</v>
+        <v>0.4452091355627835</v>
       </c>
       <c r="AW13">
-        <v>0.4125810203828565</v>
+        <v>0.4452091355627835</v>
       </c>
       <c r="AX13">
-        <v>0.4125810203828565</v>
+        <v>0.3871109131403626</v>
       </c>
       <c r="AY13">
-        <v>0.4125810203828565</v>
+        <v>0.3290126907179418</v>
       </c>
       <c r="AZ13">
-        <v>0.3810502501249827</v>
+        <v>0.3290126907179418</v>
       </c>
       <c r="BA13">
-        <v>0.3810502501249827</v>
+        <v>0.3290126907179419</v>
       </c>
       <c r="BB13">
-        <v>0.3810502501249827</v>
+        <v>0.3290126907179422</v>
       </c>
       <c r="BC13">
-        <v>0.3810502501249827</v>
+        <v>0.3290126907179429</v>
       </c>
       <c r="BD13">
-        <v>0.3810502501249827</v>
+        <v>0.3290126907179435</v>
       </c>
       <c r="BE13">
-        <v>0.3810502501249827</v>
+        <v>0.3290126907179435</v>
       </c>
       <c r="BF13">
-        <v>0.3810502501249827</v>
+        <v>0.3290126907179441</v>
       </c>
       <c r="BG13">
-        <v>0.3810502501249827</v>
+        <v>0.3290126907179441</v>
       </c>
       <c r="BH13">
-        <v>0.3810502501249827</v>
+        <v>0.3290126907179441</v>
       </c>
       <c r="BI13">
-        <v>0.3810502501249827</v>
+        <v>0.3290126907179448</v>
       </c>
       <c r="BJ13">
-        <v>0.3810502501249827</v>
+        <v>0.3290126907179455</v>
       </c>
       <c r="BK13">
-        <v>0.3810502501249827</v>
+        <v>0.3290126907179455</v>
       </c>
       <c r="BL13">
-        <v>0.3810502501249827</v>
+        <v>0.3290126907179461</v>
       </c>
       <c r="BM13">
-        <v>0.3624690008962941</v>
+        <v>0.3290126907179468</v>
       </c>
       <c r="BN13">
-        <v>0.279920789179224</v>
+        <v>0.3290126907179513</v>
       </c>
       <c r="BO13">
-        <v>0.279920789179224</v>
+        <v>0.3290126907179513</v>
       </c>
       <c r="BP13">
-        <v>0.279920789179224</v>
+        <v>0.3290126907179513</v>
       </c>
       <c r="BQ13">
-        <v>0.279920789179224</v>
+        <v>0.3290126907179513</v>
       </c>
       <c r="BR13">
-        <v>0.279920789179224</v>
+        <v>0.3290126907179513</v>
       </c>
       <c r="BS13">
-        <v>0.279920789179224</v>
+        <v>0.3290126907179557</v>
       </c>
       <c r="BT13">
-        <v>0.279920789179224</v>
+        <v>0.3290126907179681</v>
       </c>
       <c r="BU13">
-        <v>0.279920789179224</v>
+        <v>0.3290126907179681</v>
       </c>
       <c r="BV13">
-        <v>0.279920789179224</v>
+        <v>0.3290126907179681</v>
       </c>
       <c r="BW13">
-        <v>0.279920789179224</v>
+        <v>0.3290126907179708</v>
       </c>
       <c r="BX13">
-        <v>0.279920789179224</v>
+        <v>0.2649611971194021</v>
       </c>
       <c r="BY13">
-        <v>0.279920789179224</v>
+        <v>0.2009097035208334</v>
       </c>
       <c r="BZ13">
-        <v>0.279920789179224</v>
+        <v>0.2009097035208334</v>
       </c>
       <c r="CA13">
-        <v>0.3399207891792242</v>
+        <v>0.2009097035208334</v>
       </c>
       <c r="CB13">
-        <v>0.3399207891792242</v>
+        <v>0.2009097035208334</v>
       </c>
       <c r="CC13">
-        <v>0.3399207891792242</v>
+        <v>0.2009097035208334</v>
       </c>
       <c r="CD13">
-        <v>0.3399207891792242</v>
+        <v>0.2009097035208421</v>
       </c>
       <c r="CE13">
-        <v>0.3399207891792242</v>
+        <v>0.2009097035208421</v>
       </c>
       <c r="CF13">
-        <v>0.3399207891792242</v>
+        <v>0.2009097035208461</v>
       </c>
       <c r="CG13">
-        <v>0.3175984269010376</v>
+        <v>0.2009097035208461</v>
       </c>
       <c r="CH13">
-        <v>0.295276064622851</v>
+        <v>0.2009097035208486</v>
       </c>
       <c r="CI13">
-        <v>0.2730255215727009</v>
+        <v>0.2009097035208511</v>
       </c>
       <c r="CJ13">
-        <v>0.2507749785225509</v>
+        <v>0.2009097035208536</v>
       </c>
       <c r="CK13">
-        <v>0.2507749785225509</v>
+        <v>0.2009097035208536</v>
       </c>
       <c r="CL13">
-        <v>0.2507749785225509</v>
+        <v>0.2009097035208536</v>
       </c>
       <c r="CM13">
-        <v>0.2270638285986774</v>
+        <v>0.2009097035208536</v>
       </c>
       <c r="CN13">
-        <v>0.2033526786748037</v>
+        <v>0.2009097035208536</v>
       </c>
       <c r="CO13">
-        <v>0.2033526786748037</v>
+        <v>0.2009097035208536</v>
       </c>
       <c r="CP13">
-        <v>0.2033526786748037</v>
+        <v>0.2009097035208536</v>
       </c>
       <c r="CQ13">
-        <v>0.2033526786748037</v>
+        <v>0.2009097035208536</v>
       </c>
       <c r="CR13">
-        <v>0.2033526786748037</v>
+        <v>0.2009097035208536</v>
       </c>
       <c r="CS13">
-        <v>0.2033526786748037</v>
+        <v>0.2009097035208536</v>
       </c>
     </row>
     <row r="14" spans="1:97">
       <c r="A14" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B14">
         <v>0.2</v>
       </c>
       <c r="C14">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="D14">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="E14">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="F14">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="G14">
-        <v>0.32</v>
+        <v>0.2</v>
       </c>
       <c r="H14">
-        <v>0.32</v>
+        <v>0.2</v>
       </c>
       <c r="I14">
-        <v>0.32</v>
+        <v>0.2</v>
       </c>
       <c r="J14">
-        <v>0.32</v>
+        <v>0.2</v>
       </c>
       <c r="K14">
-        <v>0.32</v>
+        <v>0.2</v>
       </c>
       <c r="L14">
-        <v>0.32</v>
+        <v>0.2</v>
       </c>
       <c r="M14">
-        <v>0.32</v>
+        <v>0.2</v>
       </c>
       <c r="N14">
-        <v>0.32</v>
+        <v>0.2</v>
       </c>
       <c r="O14">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="P14">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="Q14">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="R14">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="S14">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="T14">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="U14">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="V14">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="W14">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="X14">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="Y14">
-        <v>0.4783365331301955</v>
+        <v>0.8</v>
       </c>
       <c r="Z14">
-        <v>0.4566730662603909</v>
+        <v>0.8</v>
       </c>
       <c r="AA14">
-        <v>0.4350095993905865</v>
+        <v>0.8</v>
       </c>
       <c r="AB14">
-        <v>0.413346132520782</v>
+        <v>0.7625947156066715</v>
       </c>
       <c r="AC14">
-        <v>0.4733461325207819</v>
+        <v>0.7251894312133339</v>
       </c>
       <c r="AD14">
-        <v>0.4577758290668857</v>
+        <v>0.687784146819991</v>
       </c>
       <c r="AE14">
-        <v>0.4422055256129895</v>
+        <v>0.6503788624266512</v>
       </c>
       <c r="AF14">
-        <v>0.4266352221590933</v>
+        <v>0.6129735780333081</v>
       </c>
       <c r="AG14">
-        <v>0.4110649187051971</v>
+        <v>0.5705305458840209</v>
       </c>
       <c r="AH14">
-        <v>0.3954946152513009</v>
+        <v>0.5280875137347486</v>
       </c>
       <c r="AI14">
-        <v>0.3954946152513009</v>
+        <v>0.4856444815854783</v>
       </c>
       <c r="AJ14">
-        <v>0.3954946152513009</v>
+        <v>0.4432014494362044</v>
       </c>
       <c r="AK14">
-        <v>0.3954946152513009</v>
+        <v>0.4432014494362044</v>
       </c>
       <c r="AL14">
-        <v>0.3954946152513009</v>
+        <v>0.4432014494362044</v>
       </c>
       <c r="AM14">
-        <v>0.3954946152513009</v>
+        <v>0.4432014494362044</v>
       </c>
       <c r="AN14">
-        <v>0.3670288801621842</v>
+        <v>0.4432014494362044</v>
       </c>
       <c r="AO14">
-        <v>0.3385631450730674</v>
+        <v>0.4432014494362044</v>
       </c>
       <c r="AP14">
-        <v>0.3100974099839506</v>
+        <v>0.4432014494362044</v>
       </c>
       <c r="AQ14">
-        <v>0.3100974099839506</v>
+        <v>0.4432014494362044</v>
       </c>
       <c r="AR14">
-        <v>0.3100974099839506</v>
+        <v>0.4432014494362106</v>
       </c>
       <c r="AS14">
-        <v>0.3100974099839506</v>
+        <v>0.4432014494362106</v>
       </c>
       <c r="AT14">
-        <v>0.3100974099839506</v>
+        <v>0.4432014494362106</v>
       </c>
       <c r="AU14">
-        <v>0.3100974099839506</v>
+        <v>0.4432014494362106</v>
       </c>
       <c r="AV14">
-        <v>0.3100974099839506</v>
+        <v>0.4432014494362106</v>
       </c>
       <c r="AW14">
-        <v>0.3100974099839506</v>
+        <v>0.4432014494362081</v>
       </c>
       <c r="AX14">
-        <v>0.3100974099839506</v>
+        <v>0.4432014494362086</v>
       </c>
       <c r="AY14">
-        <v>0.3100974099839506</v>
+        <v>0.4432014494362094</v>
       </c>
       <c r="AZ14">
-        <v>0.3100974099839506</v>
+        <v>0.44320144943621</v>
       </c>
       <c r="BA14">
-        <v>0.3100974099839506</v>
+        <v>0.4432014494362108</v>
       </c>
       <c r="BB14">
-        <v>0.3100974099839506</v>
+        <v>0.4432014494362115</v>
       </c>
       <c r="BC14">
-        <v>0.3100974099839506</v>
+        <v>0.4432014494362123</v>
       </c>
       <c r="BD14">
-        <v>0.3100974099839506</v>
+        <v>0.443201449436213</v>
       </c>
       <c r="BE14">
-        <v>0.3100974099839506</v>
+        <v>0.4432014494362138</v>
       </c>
       <c r="BF14">
-        <v>0.3100974099839506</v>
+        <v>0.4432014494362145</v>
       </c>
       <c r="BG14">
-        <v>0.3100974099839506</v>
+        <v>0.4432014494362151</v>
       </c>
       <c r="BH14">
-        <v>0.3100974099839506</v>
+        <v>0.3737299852751597</v>
       </c>
       <c r="BI14">
-        <v>0.3100974099839506</v>
+        <v>0.3042585211141043</v>
       </c>
       <c r="BJ14">
-        <v>0.3100974099839506</v>
+        <v>0.2347870569530488</v>
       </c>
       <c r="BK14">
-        <v>0.3100974099839506</v>
+        <v>0.2347870569530491</v>
       </c>
       <c r="BL14">
-        <v>0.3100974099839506</v>
+        <v>0.2347870569530497</v>
       </c>
       <c r="BM14">
-        <v>0.2937823180503031</v>
+        <v>0.2347870569530503</v>
       </c>
       <c r="BN14">
-        <v>0.2774672261166555</v>
+        <v>0.2347870569530542</v>
       </c>
       <c r="BO14">
-        <v>0.2774672261166555</v>
+        <v>0.234787056953058</v>
       </c>
       <c r="BP14">
-        <v>0.2774672261166555</v>
+        <v>0.2347870569530594</v>
       </c>
       <c r="BQ14">
-        <v>0.2774672261166555</v>
+        <v>0.2347870569530618</v>
       </c>
       <c r="BR14">
-        <v>0.2774672261166555</v>
+        <v>0.2347870569530618</v>
       </c>
       <c r="BS14">
-        <v>0.2774672261166555</v>
+        <v>0.2347870569530659</v>
       </c>
       <c r="BT14">
-        <v>0.2774672261166555</v>
+        <v>0.2347870569530659</v>
       </c>
       <c r="BU14">
-        <v>0.2774672261166555</v>
+        <v>0.2347870569530659</v>
       </c>
       <c r="BV14">
-        <v>0.2774672261166555</v>
+        <v>0.2347870569530659</v>
       </c>
       <c r="BW14">
-        <v>0.2774672261166555</v>
+        <v>0.2347870569530684</v>
       </c>
       <c r="BX14">
-        <v>0.2454414793173712</v>
+        <v>0.2347870569530684</v>
       </c>
       <c r="BY14">
-        <v>0.2134157325180868</v>
+        <v>0.2347870569530684</v>
       </c>
       <c r="BZ14">
-        <v>0.210684378425173</v>
+        <v>0.2347870569530724</v>
       </c>
       <c r="CA14">
-        <v>0.2079530243322591</v>
+        <v>0.2347870569530763</v>
       </c>
       <c r="CB14">
-        <v>0.2079530243322591</v>
+        <v>0.2347870569530802</v>
       </c>
       <c r="CC14">
-        <v>0.2079530243322591</v>
+        <v>0.2008320093804018</v>
       </c>
       <c r="CD14">
-        <v>0.2079530243322591</v>
+        <v>0.2008320093804018</v>
       </c>
       <c r="CE14">
-        <v>0.2679530243322591</v>
+        <v>0.2008320093804018</v>
       </c>
       <c r="CF14">
-        <v>0.2351766982002106</v>
+        <v>0.2008320093804018</v>
       </c>
       <c r="CG14">
-        <v>0.202400372068162</v>
+        <v>0.2008320093804018</v>
       </c>
       <c r="CH14">
-        <v>0.202400372068162</v>
+        <v>0.2008320093804018</v>
       </c>
       <c r="CI14">
-        <v>0.202400372068162</v>
+        <v>0.2008320093804018</v>
       </c>
       <c r="CJ14">
-        <v>0.202400372068162</v>
+        <v>0.2008320093804018</v>
       </c>
       <c r="CK14">
-        <v>0.202400372068162</v>
+        <v>0.2008320093804018</v>
       </c>
       <c r="CL14">
-        <v>0.202400372068162</v>
+        <v>0.2008320093804018</v>
       </c>
       <c r="CM14">
-        <v>0.202400372068162</v>
+        <v>0.2008320093804018</v>
       </c>
       <c r="CN14">
-        <v>0.202400372068162</v>
+        <v>0.2008320093804018</v>
       </c>
       <c r="CO14">
-        <v>0.202400372068162</v>
+        <v>0.2008320093804018</v>
       </c>
       <c r="CP14">
-        <v>0.202400372068162</v>
+        <v>0.2008320093804018</v>
       </c>
       <c r="CQ14">
-        <v>0.202400372068162</v>
+        <v>0.2008320093804018</v>
       </c>
       <c r="CR14">
-        <v>0.202400372068162</v>
+        <v>0.2008320093804018</v>
       </c>
       <c r="CS14">
-        <v>0.202400372068162</v>
+        <v>0.2008320093804018</v>
       </c>
     </row>
     <row r="15" spans="1:97">
       <c r="A15" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B15">
         <v>0.2</v>
       </c>
       <c r="C15">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="D15">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="E15">
-        <v>0.32</v>
+        <v>0.2</v>
       </c>
       <c r="F15">
-        <v>0.32</v>
+        <v>0.2</v>
       </c>
       <c r="G15">
-        <v>0.32</v>
+        <v>0.2</v>
       </c>
       <c r="H15">
-        <v>0.32</v>
+        <v>0.2</v>
       </c>
       <c r="I15">
-        <v>0.32</v>
+        <v>0.2</v>
       </c>
       <c r="J15">
-        <v>0.32</v>
+        <v>0.2</v>
       </c>
       <c r="K15">
-        <v>0.38</v>
+        <v>0.2</v>
       </c>
       <c r="L15">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="M15">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="N15">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="O15">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="P15">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="Q15">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="R15">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="S15">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="T15">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="U15">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="V15">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="W15">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="X15">
-        <v>0.5400912170101594</v>
+        <v>0.8</v>
       </c>
       <c r="Y15">
-        <v>0.5201824340203188</v>
+        <v>0.8</v>
       </c>
       <c r="Z15">
-        <v>0.5002736510304783</v>
+        <v>0.8</v>
       </c>
       <c r="AA15">
-        <v>0.4803648680406377</v>
+        <v>0.8</v>
       </c>
       <c r="AB15">
-        <v>0.460456085050797</v>
+        <v>0.8</v>
       </c>
       <c r="AC15">
-        <v>0.520456085050797</v>
+        <v>0.7634848474177378</v>
       </c>
       <c r="AD15">
-        <v>0.5053219061024492</v>
+        <v>0.7269696948354755</v>
       </c>
       <c r="AE15">
-        <v>0.4901877271541014</v>
+        <v>0.6904545422532133</v>
       </c>
       <c r="AF15">
-        <v>0.4750535482057535</v>
+        <v>0.6539393896709511</v>
       </c>
       <c r="AG15">
-        <v>0.4599193692574056</v>
+        <v>0.6159902981255851</v>
       </c>
       <c r="AH15">
-        <v>0.4447851903090577</v>
+        <v>0.5780412065802191</v>
       </c>
       <c r="AI15">
-        <v>0.4296510113607098</v>
+        <v>0.5415206536547638</v>
       </c>
       <c r="AJ15">
-        <v>0.4296510113607098</v>
+        <v>0.5050001007293083</v>
       </c>
       <c r="AK15">
-        <v>0.4296510113607098</v>
+        <v>0.4684795478038529</v>
       </c>
       <c r="AL15">
-        <v>0.42965101136071</v>
+        <v>0.4319589948783975</v>
       </c>
       <c r="AM15">
-        <v>0.42965101136071</v>
+        <v>0.395438441952942</v>
       </c>
       <c r="AN15">
-        <v>0.42965101136071</v>
+        <v>0.395438441952942</v>
       </c>
       <c r="AO15">
-        <v>0.42965101136071</v>
+        <v>0.395438441952942</v>
       </c>
       <c r="AP15">
-        <v>0.42965101136071</v>
+        <v>0.395438441952942</v>
       </c>
       <c r="AQ15">
-        <v>0.42965101136071</v>
+        <v>0.395438441952942</v>
       </c>
       <c r="AR15">
-        <v>0.42965101136071</v>
+        <v>0.395438441952942</v>
       </c>
       <c r="AS15">
-        <v>0.42965101136071</v>
+        <v>0.395438441952942</v>
       </c>
       <c r="AT15">
-        <v>0.42965101136071</v>
+        <v>0.395438441952942</v>
       </c>
       <c r="AU15">
-        <v>0.42965101136071</v>
+        <v>0.395438441952942</v>
       </c>
       <c r="AV15">
-        <v>0.42965101136071</v>
+        <v>0.395438441952942</v>
       </c>
       <c r="AW15">
-        <v>0.42965101136071</v>
+        <v>0.395438441952942</v>
       </c>
       <c r="AX15">
-        <v>0.42965101136071</v>
+        <v>0.395438441952942</v>
       </c>
       <c r="AY15">
-        <v>0.42965101136071</v>
+        <v>0.395438441952942</v>
       </c>
       <c r="AZ15">
-        <v>0.42965101136071</v>
+        <v>0.395438441952942</v>
       </c>
       <c r="BA15">
-        <v>0.4081552407644353</v>
+        <v>0.395438441952942</v>
       </c>
       <c r="BB15">
-        <v>0.3866594701681606</v>
+        <v>0.395438441952942</v>
       </c>
       <c r="BC15">
-        <v>0.3866594701681606</v>
+        <v>0.395438441952942</v>
       </c>
       <c r="BD15">
-        <v>0.3866594701681606</v>
+        <v>0.395438441952942</v>
       </c>
       <c r="BE15">
-        <v>0.3590982651866109</v>
+        <v>0.395438441952942</v>
       </c>
       <c r="BF15">
-        <v>0.3315370602050611</v>
+        <v>0.395438441952942</v>
       </c>
       <c r="BG15">
-        <v>0.3315370602050611</v>
+        <v>0.395438441952942</v>
       </c>
       <c r="BH15">
-        <v>0.3315370602050611</v>
+        <v>0.395438441952942</v>
       </c>
       <c r="BI15">
-        <v>0.3315370602050611</v>
+        <v>0.395438441952942</v>
       </c>
       <c r="BJ15">
-        <v>0.3315370602050611</v>
+        <v>0.395438441952942</v>
       </c>
       <c r="BK15">
-        <v>0.3315370602050611</v>
+        <v>0.395438441952942</v>
       </c>
       <c r="BL15">
-        <v>0.3315370602050611</v>
+        <v>0.395438441952942</v>
       </c>
       <c r="BM15">
-        <v>0.3315370602050611</v>
+        <v>0.3208293072455948</v>
       </c>
       <c r="BN15">
-        <v>0.3315370602050611</v>
+        <v>0.2462201725382477</v>
       </c>
       <c r="BO15">
-        <v>0.3315370602050611</v>
+        <v>0.2462201725382477</v>
       </c>
       <c r="BP15">
-        <v>0.3315370602050611</v>
+        <v>0.2462201725382477</v>
       </c>
       <c r="BQ15">
-        <v>0.3315370602050611</v>
+        <v>0.2462201725382477</v>
       </c>
       <c r="BR15">
-        <v>0.3315370602050611</v>
+        <v>0.2462201725382477</v>
       </c>
       <c r="BS15">
-        <v>0.3315370602050611</v>
+        <v>0.201769762780359</v>
       </c>
       <c r="BT15">
-        <v>0.3315370602050611</v>
+        <v>0.201769762780359</v>
       </c>
       <c r="BU15">
-        <v>0.2958492082358995</v>
+        <v>0.201769762780359</v>
       </c>
       <c r="BV15">
-        <v>0.2601613562667379</v>
+        <v>0.201769762780359</v>
       </c>
       <c r="BW15">
-        <v>0.2601613562667379</v>
+        <v>0.201769762780359</v>
       </c>
       <c r="BX15">
-        <v>0.2601613562667379</v>
+        <v>0.201769762780359</v>
       </c>
       <c r="BY15">
-        <v>0.2601613562667379</v>
+        <v>0.201769762780359</v>
       </c>
       <c r="BZ15">
-        <v>0.2601613562667379</v>
+        <v>0.201769762780359</v>
       </c>
       <c r="CA15">
-        <v>0.2601613562667378</v>
+        <v>0.201769762780359</v>
       </c>
       <c r="CB15">
-        <v>0.230118729819394</v>
+        <v>0.201769762780359</v>
       </c>
       <c r="CC15">
-        <v>0.2000761033720501</v>
+        <v>0.201769762780359</v>
       </c>
       <c r="CD15">
-        <v>0.2000761033720501</v>
+        <v>0.201769762780359</v>
       </c>
       <c r="CE15">
-        <v>0.2000761033720501</v>
+        <v>0.201769762780359</v>
       </c>
       <c r="CF15">
-        <v>0.2000761033720501</v>
+        <v>0.201769762780359</v>
       </c>
       <c r="CG15">
-        <v>0.2000761033720501</v>
+        <v>0.201769762780359</v>
       </c>
       <c r="CH15">
-        <v>0.2000761033720501</v>
+        <v>0.201769762780359</v>
       </c>
       <c r="CI15">
-        <v>0.2000761033720501</v>
+        <v>0.201769762780359</v>
       </c>
       <c r="CJ15">
-        <v>0.2000761033720501</v>
+        <v>0.201769762780359</v>
       </c>
       <c r="CK15">
-        <v>0.2000761033720501</v>
+        <v>0.201769762780359</v>
       </c>
       <c r="CL15">
-        <v>0.2000761033720501</v>
+        <v>0.201769762780359</v>
       </c>
       <c r="CM15">
-        <v>0.2000761033720501</v>
+        <v>0.201769762780359</v>
       </c>
       <c r="CN15">
-        <v>0.2000761033720501</v>
+        <v>0.201769762780359</v>
       </c>
       <c r="CO15">
-        <v>0.2000761033720501</v>
+        <v>0.201769762780359</v>
       </c>
       <c r="CP15">
-        <v>0.2000761033720501</v>
+        <v>0.201769762780359</v>
       </c>
       <c r="CQ15">
-        <v>0.2000761033720501</v>
+        <v>0.201769762780359</v>
       </c>
       <c r="CR15">
-        <v>0.2000761033720501</v>
+        <v>0.201769762780359</v>
       </c>
       <c r="CS15">
-        <v>0.2000761033720501</v>
+        <v>0.201769762780359</v>
       </c>
     </row>
     <row r="16" spans="1:97">
       <c r="A16" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B16">
         <v>0.2</v>
@@ -6059,276 +5908,276 @@
         <v>0.2</v>
       </c>
       <c r="I16">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="J16">
-        <v>0.26</v>
+        <v>0.8</v>
       </c>
       <c r="K16">
-        <v>0.26</v>
+        <v>0.8</v>
       </c>
       <c r="L16">
-        <v>0.26</v>
+        <v>0.8</v>
       </c>
       <c r="M16">
-        <v>0.26</v>
+        <v>0.8</v>
       </c>
       <c r="N16">
-        <v>0.32</v>
+        <v>0.8</v>
       </c>
       <c r="O16">
-        <v>0.32</v>
+        <v>0.8</v>
       </c>
       <c r="P16">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="Q16">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="R16">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="S16">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="T16">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="U16">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="V16">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="W16">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="X16">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="Y16">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="Z16">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="AA16">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="AB16">
-        <v>0.5600000000000001</v>
+        <v>0.7575536384386758</v>
       </c>
       <c r="AC16">
-        <v>0.62</v>
+        <v>0.7151072768773514</v>
       </c>
       <c r="AD16">
-        <v>0.62</v>
+        <v>0.6726609153160271</v>
       </c>
       <c r="AE16">
-        <v>0.6046813109020445</v>
+        <v>0.6726609153160271</v>
       </c>
       <c r="AF16">
-        <v>0.5893626218040892</v>
+        <v>0.672660915316027</v>
       </c>
       <c r="AG16">
-        <v>0.5740439327061337</v>
+        <v>0.672660915316027</v>
       </c>
       <c r="AH16">
-        <v>0.5587252436081783</v>
+        <v>0.6321928449887801</v>
       </c>
       <c r="AI16">
-        <v>0.5434065545102229</v>
+        <v>0.5917247746615332</v>
       </c>
       <c r="AJ16">
-        <v>0.5253396266456015</v>
+        <v>0.5512567043342864</v>
       </c>
       <c r="AK16">
-        <v>0.5072726987809802</v>
+        <v>0.5512567043342864</v>
       </c>
       <c r="AL16">
-        <v>0.4892057709163589</v>
+        <v>0.5512567043342864</v>
       </c>
       <c r="AM16">
-        <v>0.4711388430517376</v>
+        <v>0.5512567043342864</v>
       </c>
       <c r="AN16">
-        <v>0.4530719151871163</v>
+        <v>0.5512567043342864</v>
       </c>
       <c r="AO16">
-        <v>0.4530719151871163</v>
+        <v>0.5512567043342864</v>
       </c>
       <c r="AP16">
-        <v>0.4530719151871163</v>
+        <v>0.5512567043342864</v>
       </c>
       <c r="AQ16">
-        <v>0.4530719151871163</v>
+        <v>0.5512567043342864</v>
       </c>
       <c r="AR16">
-        <v>0.4530719151871163</v>
+        <v>0.5512567043342864</v>
       </c>
       <c r="AS16">
-        <v>0.4530719151871163</v>
+        <v>0.5512567043342864</v>
       </c>
       <c r="AT16">
-        <v>0.4530719151871163</v>
+        <v>0.5512567043342864</v>
       </c>
       <c r="AU16">
-        <v>0.4530719151871163</v>
+        <v>0.5512567043342864</v>
       </c>
       <c r="AV16">
-        <v>0.4530719151871163</v>
+        <v>0.5512567043342864</v>
       </c>
       <c r="AW16">
-        <v>0.4530719151871163</v>
+        <v>0.5512567043342864</v>
       </c>
       <c r="AX16">
-        <v>0.4530719151871163</v>
+        <v>0.5512567043342864</v>
       </c>
       <c r="AY16">
-        <v>0.4530719151871163</v>
+        <v>0.5512567043342864</v>
       </c>
       <c r="AZ16">
-        <v>0.4530719151871163</v>
+        <v>0.5512567043342864</v>
       </c>
       <c r="BA16">
-        <v>0.4530719151871163</v>
+        <v>0.5512567043342864</v>
       </c>
       <c r="BB16">
-        <v>0.4530719151871163</v>
+        <v>0.5512567043342864</v>
       </c>
       <c r="BC16">
-        <v>0.4530719151871163</v>
+        <v>0.5512567043342864</v>
       </c>
       <c r="BD16">
-        <v>0.4204789825749758</v>
+        <v>0.5512567043342864</v>
       </c>
       <c r="BE16">
-        <v>0.3878860499628353</v>
+        <v>0.5512567043342864</v>
       </c>
       <c r="BF16">
-        <v>0.3552931173506948</v>
+        <v>0.5045589469956459</v>
       </c>
       <c r="BG16">
-        <v>0.3552931173506948</v>
+        <v>0.4578611896570053</v>
       </c>
       <c r="BH16">
-        <v>0.3552931173506948</v>
+        <v>0.4578611896570053</v>
       </c>
       <c r="BI16">
-        <v>0.3552931173506948</v>
+        <v>0.4578611896570053</v>
       </c>
       <c r="BJ16">
-        <v>0.3208484650103637</v>
+        <v>0.4173294204952437</v>
       </c>
       <c r="BK16">
-        <v>0.2864038126700325</v>
+        <v>0.3767976513334822</v>
       </c>
       <c r="BL16">
-        <v>0.2864038126700325</v>
+        <v>0.3767976513334822</v>
       </c>
       <c r="BM16">
-        <v>0.2864038126700325</v>
+        <v>0.3767976513334822</v>
       </c>
       <c r="BN16">
-        <v>0.2864038126700325</v>
+        <v>0.3767976513334822</v>
       </c>
       <c r="BO16">
-        <v>0.2864038126700325</v>
+        <v>0.3767976513334822</v>
       </c>
       <c r="BP16">
-        <v>0.2864038126700325</v>
+        <v>0.3767976513334822</v>
       </c>
       <c r="BQ16">
-        <v>0.2864038126700325</v>
+        <v>0.3767976513334822</v>
       </c>
       <c r="BR16">
-        <v>0.2864038126700325</v>
+        <v>0.3767976513334822</v>
       </c>
       <c r="BS16">
-        <v>0.2864038126700325</v>
+        <v>0.3767976513334822</v>
       </c>
       <c r="BT16">
-        <v>0.2864038126700325</v>
+        <v>0.3767976513334822</v>
       </c>
       <c r="BU16">
-        <v>0.2864038126700325</v>
+        <v>0.3767976513334822</v>
       </c>
       <c r="BV16">
-        <v>0.2864038126700325</v>
+        <v>0.3767976513334822</v>
       </c>
       <c r="BW16">
-        <v>0.2864038126700325</v>
+        <v>0.3767976513334822</v>
       </c>
       <c r="BX16">
-        <v>0.2864038126700325</v>
+        <v>0.3198715616270147</v>
       </c>
       <c r="BY16">
-        <v>0.2864038126700325</v>
+        <v>0.2629454719205471</v>
       </c>
       <c r="BZ16">
-        <v>0.2864038126700325</v>
+        <v>0.2060193822140796</v>
       </c>
       <c r="CA16">
-        <v>0.2864038126700325</v>
+        <v>0.2060193822140796</v>
       </c>
       <c r="CB16">
-        <v>0.2864038126700325</v>
+        <v>0.2060193822140796</v>
       </c>
       <c r="CC16">
-        <v>0.2694262888836933</v>
+        <v>0.2060193822140796</v>
       </c>
       <c r="CD16">
-        <v>0.2694262888836933</v>
+        <v>0.2060193822140796</v>
       </c>
       <c r="CE16">
-        <v>0.2694262888836933</v>
+        <v>0.2060193822140796</v>
       </c>
       <c r="CF16">
-        <v>0.2694262888836933</v>
+        <v>0.2060193822140796</v>
       </c>
       <c r="CG16">
-        <v>0.2694262888836933</v>
+        <v>0.2060193822140796</v>
       </c>
       <c r="CH16">
-        <v>0.2694262888836933</v>
+        <v>0.2060193822140796</v>
       </c>
       <c r="CI16">
-        <v>0.2694262888836933</v>
+        <v>0.2060193822140796</v>
       </c>
       <c r="CJ16">
-        <v>0.2694262888836933</v>
+        <v>0.2060193822140796</v>
       </c>
       <c r="CK16">
-        <v>0.2694262888836933</v>
+        <v>0.2060193822140796</v>
       </c>
       <c r="CL16">
-        <v>0.2694262888836933</v>
+        <v>0.2060193822140796</v>
       </c>
       <c r="CM16">
-        <v>0.2694262888836933</v>
+        <v>0.2060193822140796</v>
       </c>
       <c r="CN16">
-        <v>0.2364837213166586</v>
+        <v>0.2060193822140796</v>
       </c>
       <c r="CO16">
-        <v>0.2035411537496239</v>
+        <v>0.2060193822140796</v>
       </c>
       <c r="CP16">
-        <v>0.2035411537496239</v>
+        <v>0.2060193822140796</v>
       </c>
       <c r="CQ16">
-        <v>0.2035411537496239</v>
+        <v>0.2060193822140796</v>
       </c>
       <c r="CR16">
-        <v>0.2035411537496239</v>
+        <v>0.2060193822140796</v>
       </c>
       <c r="CS16">
-        <v>0.2035411537496239</v>
+        <v>0.2060193822140796</v>
       </c>
     </row>
     <row r="17" spans="1:97">
       <c r="A17" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B17">
         <v>0.2</v>
@@ -6340,288 +6189,288 @@
         <v>0.2</v>
       </c>
       <c r="E17">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="F17">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="G17">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="H17">
-        <v>0.26</v>
+        <v>0.8</v>
       </c>
       <c r="I17">
-        <v>0.32</v>
+        <v>0.8</v>
       </c>
       <c r="J17">
-        <v>0.32</v>
+        <v>0.8</v>
       </c>
       <c r="K17">
-        <v>0.32</v>
+        <v>0.8</v>
       </c>
       <c r="L17">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="M17">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="N17">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="O17">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="P17">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="Q17">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="R17">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="S17">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="T17">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="U17">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="V17">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="W17">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="X17">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="Y17">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="Z17">
-        <v>0.62</v>
+        <v>0.8</v>
       </c>
       <c r="AA17">
-        <v>0.6011761303758711</v>
+        <v>0.8</v>
       </c>
       <c r="AB17">
-        <v>0.5823522607517451</v>
+        <v>0.8</v>
       </c>
       <c r="AC17">
-        <v>0.563528391127619</v>
+        <v>0.8</v>
       </c>
       <c r="AD17">
-        <v>0.5447045215034929</v>
+        <v>0.8</v>
       </c>
       <c r="AE17">
-        <v>0.5447045215034928</v>
+        <v>0.7606998481046733</v>
       </c>
       <c r="AF17">
-        <v>0.5191623041544099</v>
+        <v>0.7213996962093364</v>
       </c>
       <c r="AG17">
-        <v>0.493620086805327</v>
+        <v>0.6820995443139997</v>
       </c>
       <c r="AH17">
-        <v>0.4742318243372201</v>
+        <v>0.6820995443139997</v>
       </c>
       <c r="AI17">
-        <v>0.4548435618691133</v>
+        <v>0.6820995443139997</v>
       </c>
       <c r="AJ17">
-        <v>0.4548435618691133</v>
+        <v>0.6820995443139997</v>
       </c>
       <c r="AK17">
-        <v>0.4548435618691133</v>
+        <v>0.6820995443139997</v>
       </c>
       <c r="AL17">
-        <v>0.4548435618691133</v>
+        <v>0.6820995443139997</v>
       </c>
       <c r="AM17">
-        <v>0.4548435618691133</v>
+        <v>0.6820995443139997</v>
       </c>
       <c r="AN17">
-        <v>0.4548435618691133</v>
+        <v>0.6820995443139997</v>
       </c>
       <c r="AO17">
-        <v>0.4548435618691133</v>
+        <v>0.6820995443139997</v>
       </c>
       <c r="AP17">
-        <v>0.4548435618691133</v>
+        <v>0.6820995443139997</v>
       </c>
       <c r="AQ17">
-        <v>0.4548435618691133</v>
+        <v>0.6820995443139997</v>
       </c>
       <c r="AR17">
-        <v>0.4548435618691133</v>
+        <v>0.6820995443139997</v>
       </c>
       <c r="AS17">
-        <v>0.4548435618691133</v>
+        <v>0.6722008549638386</v>
       </c>
       <c r="AT17">
-        <v>0.4548435618691133</v>
+        <v>0.6623021656136775</v>
       </c>
       <c r="AU17">
-        <v>0.4548435618691133</v>
+        <v>0.6524034762635164</v>
       </c>
       <c r="AV17">
-        <v>0.4276709833764629</v>
+        <v>0.6425047869133553</v>
       </c>
       <c r="AW17">
-        <v>0.4004984048838123</v>
+        <v>0.6326060975631942</v>
       </c>
       <c r="AX17">
-        <v>0.3733258263911619</v>
+        <v>0.6326060975631942</v>
       </c>
       <c r="AY17">
-        <v>0.3733258263911619</v>
+        <v>0.6326060975631942</v>
       </c>
       <c r="AZ17">
-        <v>0.3733258263911619</v>
+        <v>0.5695445570474469</v>
       </c>
       <c r="BA17">
-        <v>0.3733258263911619</v>
+        <v>0.5695445570474469</v>
       </c>
       <c r="BB17">
-        <v>0.3733258263911619</v>
+        <v>0.5259741991010449</v>
       </c>
       <c r="BC17">
-        <v>0.3495156528716125</v>
+        <v>0.4824038411546429</v>
       </c>
       <c r="BD17">
-        <v>0.3257054793520632</v>
+        <v>0.4172179759303619</v>
       </c>
       <c r="BE17">
-        <v>0.3257054793520632</v>
+        <v>0.3520321107060809</v>
       </c>
       <c r="BF17">
-        <v>0.3257054793520632</v>
+        <v>0.2868462454817999</v>
       </c>
       <c r="BG17">
-        <v>0.3257054793520632</v>
+        <v>0.2868462454817999</v>
       </c>
       <c r="BH17">
-        <v>0.3257054793520632</v>
+        <v>0.2868462454817999</v>
       </c>
       <c r="BI17">
-        <v>0.3257054793520632</v>
+        <v>0.2868462454817999</v>
       </c>
       <c r="BJ17">
-        <v>0.3257054793520632</v>
+        <v>0.2868462454817999</v>
       </c>
       <c r="BK17">
-        <v>0.3257054793520632</v>
+        <v>0.2868462454817999</v>
       </c>
       <c r="BL17">
-        <v>0.2944792429091727</v>
+        <v>0.2868462454817999</v>
       </c>
       <c r="BM17">
-        <v>0.2632530064662821</v>
+        <v>0.2868462454817999</v>
       </c>
       <c r="BN17">
-        <v>0.2632530064662821</v>
+        <v>0.2868462454817999</v>
       </c>
       <c r="BO17">
-        <v>0.2632530064662821</v>
+        <v>0.2610369181238767</v>
       </c>
       <c r="BP17">
-        <v>0.2632530064662821</v>
+        <v>0.2352275907659536</v>
       </c>
       <c r="BQ17">
-        <v>0.2632530064662821</v>
+        <v>0.2094182634080304</v>
       </c>
       <c r="BR17">
-        <v>0.2632530064662821</v>
+        <v>0.2094182634080304</v>
       </c>
       <c r="BS17">
-        <v>0.2632530064662821</v>
+        <v>0.2094182634080304</v>
       </c>
       <c r="BT17">
-        <v>0.2632530064662821</v>
+        <v>0.2094182634080304</v>
       </c>
       <c r="BU17">
-        <v>0.2632530064662821</v>
+        <v>0.2094182634080304</v>
       </c>
       <c r="BV17">
-        <v>0.2345495217037307</v>
+        <v>0.2094182634080304</v>
       </c>
       <c r="BW17">
-        <v>0.2058460369411793</v>
+        <v>0.2094182634080304</v>
       </c>
       <c r="BX17">
-        <v>0.2058460369411793</v>
+        <v>0.2094182634080304</v>
       </c>
       <c r="BY17">
-        <v>0.2058460369411793</v>
+        <v>0.2094182634080304</v>
       </c>
       <c r="BZ17">
-        <v>0.2058460369411793</v>
+        <v>0.2094182634080304</v>
       </c>
       <c r="CA17">
-        <v>0.2058460369411793</v>
+        <v>0.2094182634080304</v>
       </c>
       <c r="CB17">
-        <v>0.2058460369411793</v>
+        <v>0.2094182634080304</v>
       </c>
       <c r="CC17">
-        <v>0.2058460369411793</v>
+        <v>0.2094182634080304</v>
       </c>
       <c r="CD17">
-        <v>0.2031146828482654</v>
+        <v>0.2094182634080304</v>
       </c>
       <c r="CE17">
-        <v>0.2003833287553516</v>
+        <v>0.2094182634080304</v>
       </c>
       <c r="CF17">
-        <v>0.2003833287553516</v>
+        <v>0.2094182634080304</v>
       </c>
       <c r="CG17">
-        <v>0.2003833287553516</v>
+        <v>0.2094182634080304</v>
       </c>
       <c r="CH17">
-        <v>0.2003833287553516</v>
+        <v>0.2094182634080304</v>
       </c>
       <c r="CI17">
-        <v>0.2003833287553516</v>
+        <v>0.2094182634080304</v>
       </c>
       <c r="CJ17">
-        <v>0.2003833287553516</v>
+        <v>0.2094182634080304</v>
       </c>
       <c r="CK17">
-        <v>0.2003833287553516</v>
+        <v>0.2094182634080304</v>
       </c>
       <c r="CL17">
-        <v>0.2003833287553516</v>
+        <v>0.2094182634080304</v>
       </c>
       <c r="CM17">
-        <v>0.2003833287553516</v>
+        <v>0.2094182634080304</v>
       </c>
       <c r="CN17">
-        <v>0.2003833287553516</v>
+        <v>0.2094182634080304</v>
       </c>
       <c r="CO17">
-        <v>0.2003833287553516</v>
+        <v>0.2094182634080304</v>
       </c>
       <c r="CP17">
-        <v>0.2003833287553516</v>
+        <v>0.2094182634080304</v>
       </c>
       <c r="CQ17">
-        <v>0.2003833287553516</v>
+        <v>0.2094182634080304</v>
       </c>
       <c r="CR17">
-        <v>0.2003833287553516</v>
+        <v>0.2094182634080304</v>
       </c>
       <c r="CS17">
-        <v>0.2003833287553516</v>
+        <v>0.2094182634080304</v>
       </c>
     </row>
     <row r="18" spans="1:97">
       <c r="A18" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B18">
         <v>0.2</v>
@@ -6645,276 +6494,276 @@
         <v>0.2</v>
       </c>
       <c r="I18">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="J18">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="K18">
-        <v>0.32</v>
+        <v>0.2</v>
       </c>
       <c r="L18">
-        <v>0.32</v>
+        <v>0.2</v>
       </c>
       <c r="M18">
-        <v>0.32</v>
+        <v>0.2</v>
       </c>
       <c r="N18">
-        <v>0.32</v>
+        <v>0.2</v>
       </c>
       <c r="O18">
-        <v>0.32</v>
+        <v>0.2</v>
       </c>
       <c r="P18">
-        <v>0.32</v>
+        <v>0.8</v>
       </c>
       <c r="Q18">
-        <v>0.32</v>
+        <v>0.8</v>
       </c>
       <c r="R18">
-        <v>0.32</v>
+        <v>0.8</v>
       </c>
       <c r="S18">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="T18">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="U18">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="V18">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="W18">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="X18">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="Y18">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="Z18">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="AA18">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AB18">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AC18">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AD18">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AE18">
-        <v>0.5429309994750059</v>
+        <v>0.8</v>
       </c>
       <c r="AF18">
-        <v>0.5258619989500116</v>
+        <v>0.7489155653018726</v>
       </c>
       <c r="AG18">
-        <v>0.5064074025989824</v>
+        <v>0.6978311306037127</v>
       </c>
       <c r="AH18">
-        <v>0.4869528062479533</v>
+        <v>0.6590546056675051</v>
       </c>
       <c r="AI18">
-        <v>0.4674982098969241</v>
+        <v>0.6202780807312978</v>
       </c>
       <c r="AJ18">
-        <v>0.4674982098969241</v>
+        <v>0.6202780807313026</v>
       </c>
       <c r="AK18">
-        <v>0.4674982098969241</v>
+        <v>0.6202780807313026</v>
       </c>
       <c r="AL18">
-        <v>0.4674982098969241</v>
+        <v>0.6202780807313026</v>
       </c>
       <c r="AM18">
-        <v>0.4674982098969241</v>
+        <v>0.6202780807313026</v>
       </c>
       <c r="AN18">
-        <v>0.4423578078497066</v>
+        <v>0.5699972766368677</v>
       </c>
       <c r="AO18">
-        <v>0.4172174058024892</v>
+        <v>0.5197164725424327</v>
       </c>
       <c r="AP18">
-        <v>0.4172174058024892</v>
+        <v>0.5197164725424327</v>
       </c>
       <c r="AQ18">
-        <v>0.4172174058024892</v>
+        <v>0.5197164725424327</v>
       </c>
       <c r="AR18">
-        <v>0.4172174058024892</v>
+        <v>0.5197164725424327</v>
       </c>
       <c r="AS18">
-        <v>0.4172174058024892</v>
+        <v>0.5197164725424327</v>
       </c>
       <c r="AT18">
-        <v>0.4172174058024892</v>
+        <v>0.5197164725424327</v>
       </c>
       <c r="AU18">
-        <v>0.4172174058024892</v>
+        <v>0.5197164725424327</v>
       </c>
       <c r="AV18">
-        <v>0.4172174058024892</v>
+        <v>0.4653713155571317</v>
       </c>
       <c r="AW18">
-        <v>0.4172174058024892</v>
+        <v>0.4110261585718307</v>
       </c>
       <c r="AX18">
-        <v>0.4172174058024892</v>
+        <v>0.3566810015865297</v>
       </c>
       <c r="AY18">
-        <v>0.4172174058024892</v>
+        <v>0.3566810015865297</v>
       </c>
       <c r="AZ18">
-        <v>0.4172174058024892</v>
+        <v>0.3566810015865297</v>
       </c>
       <c r="BA18">
-        <v>0.4172174058024892</v>
+        <v>0.3566810015865297</v>
       </c>
       <c r="BB18">
-        <v>0.4172174058024892</v>
+        <v>0.3566810015865297</v>
       </c>
       <c r="BC18">
-        <v>0.3844577268558471</v>
+        <v>0.3566810015865297</v>
       </c>
       <c r="BD18">
-        <v>0.3516980479092051</v>
+        <v>0.3566810015865297</v>
       </c>
       <c r="BE18">
-        <v>0.3516980479092051</v>
+        <v>0.3566810015865297</v>
       </c>
       <c r="BF18">
-        <v>0.3283491692398849</v>
+        <v>0.3566810015865297</v>
       </c>
       <c r="BG18">
-        <v>0.3050002905705647</v>
+        <v>0.3032410158045629</v>
       </c>
       <c r="BH18">
-        <v>0.3050002905705647</v>
+        <v>0.249801030022596</v>
       </c>
       <c r="BI18">
-        <v>0.3050002905705647</v>
+        <v>0.249801030022596</v>
       </c>
       <c r="BJ18">
-        <v>0.3050002905705647</v>
+        <v>0.249801030022596</v>
       </c>
       <c r="BK18">
-        <v>0.2891620345653793</v>
+        <v>0.249801030022596</v>
       </c>
       <c r="BL18">
-        <v>0.2733237785601938</v>
+        <v>0.249801030022596</v>
       </c>
       <c r="BM18">
-        <v>0.2733237785601938</v>
+        <v>0.249801030022596</v>
       </c>
       <c r="BN18">
-        <v>0.2733237785601938</v>
+        <v>0.249801030022596</v>
       </c>
       <c r="BO18">
-        <v>0.2733237785601938</v>
+        <v>0.249801030022596</v>
       </c>
       <c r="BP18">
-        <v>0.2023229577494269</v>
+        <v>0.249801030022596</v>
       </c>
       <c r="BQ18">
-        <v>0.2023229577494269</v>
+        <v>0.249801030022596</v>
       </c>
       <c r="BR18">
-        <v>0.2023229577494269</v>
+        <v>0.2436791158762629</v>
       </c>
       <c r="BS18">
-        <v>0.2023229577494269</v>
+        <v>0.2436791158762629</v>
       </c>
       <c r="BT18">
-        <v>0.2023229577494269</v>
+        <v>0.2436791158762629</v>
       </c>
       <c r="BU18">
-        <v>0.2023229577494269</v>
+        <v>0.2024679482932747</v>
       </c>
       <c r="BV18">
-        <v>0.2023229577494269</v>
+        <v>0.2024679482932747</v>
       </c>
       <c r="BW18">
-        <v>0.2023229577494269</v>
+        <v>0.2024679482932747</v>
       </c>
       <c r="BX18">
-        <v>0.2023229577494269</v>
+        <v>0.2024679482932747</v>
       </c>
       <c r="BY18">
-        <v>0.2023229577494269</v>
+        <v>0.2024679482932747</v>
       </c>
       <c r="BZ18">
-        <v>0.2023229577494269</v>
+        <v>0.2024679482932747</v>
       </c>
       <c r="CA18">
-        <v>0.2023229577494269</v>
+        <v>0.2024679482932747</v>
       </c>
       <c r="CB18">
-        <v>0.2023229577494269</v>
+        <v>0.2024679482932747</v>
       </c>
       <c r="CC18">
-        <v>0.2023229577494269</v>
+        <v>0.2024679482932747</v>
       </c>
       <c r="CD18">
-        <v>0.2023229577494269</v>
+        <v>0.2024679482932747</v>
       </c>
       <c r="CE18">
-        <v>0.2023229577494269</v>
+        <v>0.2024679482932747</v>
       </c>
       <c r="CF18">
-        <v>0.2023229577494269</v>
+        <v>0.2024679482932747</v>
       </c>
       <c r="CG18">
-        <v>0.2023229577494269</v>
+        <v>0.2024679482932747</v>
       </c>
       <c r="CH18">
-        <v>0.2023229577494269</v>
+        <v>0.2024679482932747</v>
       </c>
       <c r="CI18">
-        <v>0.2023229577494269</v>
+        <v>0.2024679482932747</v>
       </c>
       <c r="CJ18">
-        <v>0.2023229577494269</v>
+        <v>0.2024679482932747</v>
       </c>
       <c r="CK18">
-        <v>0.2023229577494269</v>
+        <v>0.2024679482932747</v>
       </c>
       <c r="CL18">
-        <v>0.2023229577494269</v>
+        <v>0.2024679482932747</v>
       </c>
       <c r="CM18">
-        <v>0.2023229577494269</v>
+        <v>0.2024679482932747</v>
       </c>
       <c r="CN18">
-        <v>0.2023229577494269</v>
+        <v>0.2024679482932747</v>
       </c>
       <c r="CO18">
-        <v>0.2023229577494269</v>
+        <v>0.2024679482932747</v>
       </c>
       <c r="CP18">
-        <v>0.2023229577494269</v>
+        <v>0.2024679482932747</v>
       </c>
       <c r="CQ18">
-        <v>0.2023229577494269</v>
+        <v>0.2024679482932747</v>
       </c>
       <c r="CR18">
-        <v>0.2023229577494269</v>
+        <v>0.2024679482932747</v>
       </c>
       <c r="CS18">
-        <v>0.2023229577494269</v>
+        <v>0.2024679482932747</v>
       </c>
     </row>
     <row r="19" spans="1:97">
       <c r="A19" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B19">
         <v>0.2</v>
@@ -6926,288 +6775,288 @@
         <v>0.2</v>
       </c>
       <c r="E19">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="F19">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="G19">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="H19">
-        <v>0.26</v>
+        <v>0.8</v>
       </c>
       <c r="I19">
-        <v>0.26</v>
+        <v>0.8</v>
       </c>
       <c r="J19">
-        <v>0.26</v>
+        <v>0.8</v>
       </c>
       <c r="K19">
-        <v>0.26</v>
+        <v>0.8</v>
       </c>
       <c r="L19">
-        <v>0.32</v>
+        <v>0.8</v>
       </c>
       <c r="M19">
-        <v>0.32</v>
+        <v>0.8</v>
       </c>
       <c r="N19">
-        <v>0.32</v>
+        <v>0.8</v>
       </c>
       <c r="O19">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="P19">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="Q19">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="R19">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="S19">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="T19">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="U19">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="V19">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="W19">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="X19">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="Y19">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="Z19">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AA19">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AB19">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AC19">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AD19">
-        <v>0.5600000000000001</v>
+        <v>0.7626038517839512</v>
       </c>
       <c r="AE19">
-        <v>0.5403499240523313</v>
+        <v>0.725207703567902</v>
       </c>
       <c r="AF19">
-        <v>0.5206998481046626</v>
+        <v>0.6878115553518527</v>
       </c>
       <c r="AG19">
-        <v>0.501049772156994</v>
+        <v>0.6504154071358034</v>
       </c>
       <c r="AH19">
-        <v>0.501049772156994</v>
+        <v>0.6504154071358034</v>
       </c>
       <c r="AI19">
-        <v>0.501049772156994</v>
+        <v>0.6504154071358034</v>
       </c>
       <c r="AJ19">
-        <v>0.501049772156994</v>
+        <v>0.6504154071358034</v>
       </c>
       <c r="AK19">
-        <v>0.501049772156994</v>
+        <v>0.6504154071358034</v>
       </c>
       <c r="AL19">
-        <v>0.501049772156994</v>
+        <v>0.6504154071358034</v>
       </c>
       <c r="AM19">
-        <v>0.501049772156994</v>
+        <v>0.6504154071358034</v>
       </c>
       <c r="AN19">
-        <v>0.501049772156994</v>
+        <v>0.6504154071358034</v>
       </c>
       <c r="AO19">
-        <v>0.501049772156994</v>
+        <v>0.6504154071358034</v>
       </c>
       <c r="AP19">
-        <v>0.501049772156994</v>
+        <v>0.6504154071358034</v>
       </c>
       <c r="AQ19">
-        <v>0.501049772156994</v>
+        <v>0.6504154071358034</v>
       </c>
       <c r="AR19">
-        <v>0.501049772156994</v>
+        <v>0.6504154071358034</v>
       </c>
       <c r="AS19">
-        <v>0.501049772156994</v>
+        <v>0.6504154071358034</v>
       </c>
       <c r="AT19">
-        <v>0.501049772156994</v>
+        <v>0.6504154071358034</v>
       </c>
       <c r="AU19">
-        <v>0.501049772156994</v>
+        <v>0.6504154071358034</v>
       </c>
       <c r="AV19">
-        <v>0.501049772156994</v>
+        <v>0.6504154071358034</v>
       </c>
       <c r="AW19">
-        <v>0.4804612554239331</v>
+        <v>0.6504154071358034</v>
       </c>
       <c r="AX19">
-        <v>0.4598727386908721</v>
+        <v>0.6504154071358034</v>
       </c>
       <c r="AY19">
-        <v>0.4365554612956538</v>
+        <v>0.6504154071358034</v>
       </c>
       <c r="AZ19">
-        <v>0.4132381839004355</v>
+        <v>0.6504154071358034</v>
       </c>
       <c r="BA19">
-        <v>0.4132381839004355</v>
+        <v>0.6504154071358034</v>
       </c>
       <c r="BB19">
-        <v>0.4132381839004355</v>
+        <v>0.6504154071358034</v>
       </c>
       <c r="BC19">
-        <v>0.4132381839004355</v>
+        <v>0.6504154071358034</v>
       </c>
       <c r="BD19">
-        <v>0.4132381839004355</v>
+        <v>0.5886022640188794</v>
       </c>
       <c r="BE19">
-        <v>0.4132381839004355</v>
+        <v>0.5886022640188794</v>
       </c>
       <c r="BF19">
-        <v>0.4132381839004355</v>
+        <v>0.5886022640188794</v>
       </c>
       <c r="BG19">
-        <v>0.4132381839004355</v>
+        <v>0.5886022640188794</v>
       </c>
       <c r="BH19">
-        <v>0.4132381839004355</v>
+        <v>0.5886022640188794</v>
       </c>
       <c r="BI19">
-        <v>0.375747040566687</v>
+        <v>0.5886022640188794</v>
       </c>
       <c r="BJ19">
-        <v>0.3382558972329385</v>
+        <v>0.5886022640188794</v>
       </c>
       <c r="BK19">
-        <v>0.3382558972329385</v>
+        <v>0.558780409370042</v>
       </c>
       <c r="BL19">
-        <v>0.3382558972329385</v>
+        <v>0.5107590069795395</v>
       </c>
       <c r="BM19">
-        <v>0.3382558972329385</v>
+        <v>0.4627376045890367</v>
       </c>
       <c r="BN19">
-        <v>0.3124893841574347</v>
+        <v>0.4147162021985341</v>
       </c>
       <c r="BO19">
-        <v>0.2867228710819311</v>
+        <v>0.4147162021985341</v>
       </c>
       <c r="BP19">
-        <v>0.2867228710819311</v>
+        <v>0.3691119608687251</v>
       </c>
       <c r="BQ19">
-        <v>0.2867228710819311</v>
+        <v>0.3235077195389159</v>
       </c>
       <c r="BR19">
-        <v>0.2867228710819311</v>
+        <v>0.3235077195389159</v>
       </c>
       <c r="BS19">
-        <v>0.286722871081931</v>
+        <v>0.3235077195389159</v>
       </c>
       <c r="BT19">
-        <v>0.286722871081931</v>
+        <v>0.266202714501715</v>
       </c>
       <c r="BU19">
-        <v>0.286722871081931</v>
+        <v>0.208897709464514</v>
       </c>
       <c r="BV19">
-        <v>0.286722871081931</v>
+        <v>0.208897709464514</v>
       </c>
       <c r="BW19">
-        <v>0.286722871081931</v>
+        <v>0.208897709464514</v>
       </c>
       <c r="BX19">
-        <v>0.2582598262286972</v>
+        <v>0.208897709464514</v>
       </c>
       <c r="BY19">
-        <v>0.2297967813754635</v>
+        <v>0.208897709464514</v>
       </c>
       <c r="BZ19">
-        <v>0.2013337365222297</v>
+        <v>0.208897709464514</v>
       </c>
       <c r="CA19">
-        <v>0.2013337365222297</v>
+        <v>0.208897709464514</v>
       </c>
       <c r="CB19">
-        <v>0.2013337365222297</v>
+        <v>0.208897709464514</v>
       </c>
       <c r="CC19">
-        <v>0.2013337365222297</v>
+        <v>0.208897709464514</v>
       </c>
       <c r="CD19">
-        <v>0.2013337365222297</v>
+        <v>0.208897709464514</v>
       </c>
       <c r="CE19">
-        <v>0.2013337365222297</v>
+        <v>0.208897709464514</v>
       </c>
       <c r="CF19">
-        <v>0.2013337365222297</v>
+        <v>0.208897709464514</v>
       </c>
       <c r="CG19">
-        <v>0.2013337365222297</v>
+        <v>0.208897709464514</v>
       </c>
       <c r="CH19">
-        <v>0.2013337365222297</v>
+        <v>0.208897709464514</v>
       </c>
       <c r="CI19">
-        <v>0.2013337365222297</v>
+        <v>0.208897709464514</v>
       </c>
       <c r="CJ19">
-        <v>0.2013337365222297</v>
+        <v>0.208897709464514</v>
       </c>
       <c r="CK19">
-        <v>0.2013337365222297</v>
+        <v>0.208897709464514</v>
       </c>
       <c r="CL19">
-        <v>0.2013337365222297</v>
+        <v>0.208897709464514</v>
       </c>
       <c r="CM19">
-        <v>0.2013337365222297</v>
+        <v>0.208897709464514</v>
       </c>
       <c r="CN19">
-        <v>0.2013337365222297</v>
+        <v>0.208897709464514</v>
       </c>
       <c r="CO19">
-        <v>0.2013337365222297</v>
+        <v>0.208897709464514</v>
       </c>
       <c r="CP19">
-        <v>0.2013337365222297</v>
+        <v>0.208897709464514</v>
       </c>
       <c r="CQ19">
-        <v>0.2013337365222297</v>
+        <v>0.208897709464514</v>
       </c>
       <c r="CR19">
-        <v>0.2013337365222297</v>
+        <v>0.208897709464514</v>
       </c>
       <c r="CS19">
-        <v>0.2013337365222297</v>
+        <v>0.208897709464514</v>
       </c>
     </row>
     <row r="20" spans="1:97">
       <c r="A20" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B20">
         <v>0.2</v>
@@ -7222,573 +7071,1452 @@
         <v>0.2</v>
       </c>
       <c r="F20">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="G20">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="H20">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="I20">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="J20">
-        <v>0.32</v>
+        <v>0.2</v>
       </c>
       <c r="K20">
-        <v>0.32</v>
+        <v>0.8</v>
       </c>
       <c r="L20">
-        <v>0.32</v>
+        <v>0.8</v>
       </c>
       <c r="M20">
-        <v>0.32</v>
+        <v>0.8</v>
       </c>
       <c r="N20">
-        <v>0.32</v>
+        <v>0.8</v>
       </c>
       <c r="O20">
-        <v>0.32</v>
+        <v>0.8</v>
       </c>
       <c r="P20">
-        <v>0.38</v>
+        <v>0.8</v>
       </c>
       <c r="Q20">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="R20">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="S20">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="T20">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="U20">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="V20">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="W20">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="X20">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="Y20">
-        <v>0.5</v>
+        <v>0.7566730662603922</v>
       </c>
       <c r="Z20">
-        <v>0.5</v>
+        <v>0.7133461325207886</v>
       </c>
       <c r="AA20">
-        <v>0.5</v>
+        <v>0.6700191987811844</v>
       </c>
       <c r="AB20">
-        <v>0.5600000000000001</v>
+        <v>0.6266922650415784</v>
       </c>
       <c r="AC20">
-        <v>0.5600000000000001</v>
+        <v>0.5911531083848234</v>
       </c>
       <c r="AD20">
-        <v>0.5380117751607617</v>
+        <v>0.5556139517280683</v>
       </c>
       <c r="AE20">
-        <v>0.5160235503215234</v>
+        <v>0.5200747950713134</v>
       </c>
       <c r="AF20">
-        <v>0.4940353254822851</v>
+        <v>0.4845356384145583</v>
       </c>
       <c r="AG20">
-        <v>0.4940353254822851</v>
+        <v>0.4489964817578032</v>
       </c>
       <c r="AH20">
-        <v>0.4940353254822851</v>
+        <v>0.4489964817578032</v>
       </c>
       <c r="AI20">
-        <v>0.4806394595781864</v>
+        <v>0.4489964817578032</v>
       </c>
       <c r="AJ20">
-        <v>0.4672435936740876</v>
+        <v>0.4489964817578032</v>
       </c>
       <c r="AK20">
-        <v>0.4538477277699889</v>
+        <v>0.4489964817578032</v>
       </c>
       <c r="AL20">
-        <v>0.4404518618658901</v>
+        <v>0.4489964817578032</v>
       </c>
       <c r="AM20">
-        <v>0.4404518618658901</v>
+        <v>0.4489964817578032</v>
       </c>
       <c r="AN20">
-        <v>0.4404518618658901</v>
+        <v>0.4489964817578032</v>
       </c>
       <c r="AO20">
-        <v>0.4404518618658901</v>
+        <v>0.4489964817578032</v>
       </c>
       <c r="AP20">
-        <v>0.4404518618658901</v>
+        <v>0.4489964817578032</v>
       </c>
       <c r="AQ20">
-        <v>0.4404518618658901</v>
+        <v>0.4489964817578032</v>
       </c>
       <c r="AR20">
-        <v>0.4404518618658901</v>
+        <v>0.4489964817578032</v>
       </c>
       <c r="AS20">
-        <v>0.4404518618658901</v>
+        <v>0.4489964817578032</v>
       </c>
       <c r="AT20">
-        <v>0.4404518618658901</v>
+        <v>0.4489964817578032</v>
       </c>
       <c r="AU20">
-        <v>0.4404518618658901</v>
+        <v>0.4489964817578032</v>
       </c>
       <c r="AV20">
-        <v>0.4110331577409419</v>
+        <v>0.4489964817578032</v>
       </c>
       <c r="AW20">
-        <v>0.3816144536159936</v>
+        <v>0.4489964817578032</v>
       </c>
       <c r="AX20">
-        <v>0.3816144536159936</v>
+        <v>0.4489964817578032</v>
       </c>
       <c r="AY20">
-        <v>0.3816144536159936</v>
+        <v>0.4489964817578032</v>
       </c>
       <c r="AZ20">
-        <v>0.3816144536159936</v>
+        <v>0.4035245712129785</v>
       </c>
       <c r="BA20">
-        <v>0.3816144536159936</v>
+        <v>0.3580526606681538</v>
       </c>
       <c r="BB20">
-        <v>0.3816144536159936</v>
+        <v>0.3580526606681538</v>
       </c>
       <c r="BC20">
-        <v>0.3816144536159936</v>
+        <v>0.3580526606681538</v>
       </c>
       <c r="BD20">
-        <v>0.3816144536159936</v>
+        <v>0.3580526606681538</v>
       </c>
       <c r="BE20">
-        <v>0.3816144536159936</v>
+        <v>0.2925333027748698</v>
       </c>
       <c r="BF20">
-        <v>0.3816144536159936</v>
+        <v>0.2270139448815858</v>
       </c>
       <c r="BG20">
-        <v>0.3816144536159936</v>
+        <v>0.2270139448815858</v>
       </c>
       <c r="BH20">
-        <v>0.3816144536159936</v>
+        <v>0.2270139448815858</v>
       </c>
       <c r="BI20">
-        <v>0.3630243022929953</v>
+        <v>0.2270139448815858</v>
       </c>
       <c r="BJ20">
-        <v>0.344434150969997</v>
+        <v>0.2270139448815858</v>
       </c>
       <c r="BK20">
-        <v>0.344434150969997</v>
+        <v>0.2270139448815858</v>
       </c>
       <c r="BL20">
-        <v>0.344434150969997</v>
+        <v>0.2270139448815858</v>
       </c>
       <c r="BM20">
-        <v>0.344434150969997</v>
+        <v>0.2270139448815858</v>
       </c>
       <c r="BN20">
-        <v>0.344434150969997</v>
+        <v>0.2270139448815858</v>
       </c>
       <c r="BO20">
-        <v>0.344434150969997</v>
+        <v>0.2270139448815858</v>
       </c>
       <c r="BP20">
-        <v>0.344434150969997</v>
+        <v>0.2270139448815858</v>
       </c>
       <c r="BQ20">
-        <v>0.3444341509699969</v>
+        <v>0.2270139448815858</v>
       </c>
       <c r="BR20">
-        <v>0.3444341509699969</v>
+        <v>0.2270139448815858</v>
       </c>
       <c r="BS20">
-        <v>0.3444341509699969</v>
+        <v>0.2270139448815858</v>
       </c>
       <c r="BT20">
-        <v>0.3066178097125205</v>
+        <v>0.2270139448815858</v>
       </c>
       <c r="BU20">
-        <v>0.268801468455044</v>
+        <v>0.2270139448815858</v>
       </c>
       <c r="BV20">
-        <v>0.268801468455044</v>
+        <v>0.2270139448815858</v>
       </c>
       <c r="BW20">
-        <v>0.268801468455044</v>
+        <v>0.2270139448815858</v>
       </c>
       <c r="BX20">
-        <v>0.268801468455044</v>
+        <v>0.2270139448815858</v>
       </c>
       <c r="BY20">
-        <v>0.268801468455044</v>
+        <v>0.2270139448815858</v>
       </c>
       <c r="BZ20">
-        <v>0.2688014684550448</v>
+        <v>0.2270139448815858</v>
       </c>
       <c r="CA20">
-        <v>0.2477465776541888</v>
+        <v>0.2270139448815858</v>
       </c>
       <c r="CB20">
-        <v>0.2266916868533327</v>
+        <v>0.2270139448815858</v>
       </c>
       <c r="CC20">
-        <v>0.2266916868533327</v>
+        <v>0.2270139448815858</v>
       </c>
       <c r="CD20">
-        <v>0.2266916868533327</v>
+        <v>0.2270139448815858</v>
       </c>
       <c r="CE20">
-        <v>0.2056044610207043</v>
+        <v>0.2270139448815858</v>
       </c>
       <c r="CF20">
-        <v>0.2056044610207043</v>
+        <v>0.2270139448815858</v>
       </c>
       <c r="CG20">
-        <v>0.2056044610207043</v>
+        <v>0.2270139448815858</v>
       </c>
       <c r="CH20">
-        <v>0.2028429678077509</v>
+        <v>0.2270139448815858</v>
       </c>
       <c r="CI20">
-        <v>0.2000814745947975</v>
+        <v>0.2270139448815858</v>
       </c>
       <c r="CJ20">
-        <v>0.2000814745947975</v>
+        <v>0.2270139448815858</v>
       </c>
       <c r="CK20">
-        <v>0.2000814745947975</v>
+        <v>0.2270139448815858</v>
       </c>
       <c r="CL20">
-        <v>0.2000814745947975</v>
+        <v>0.2270139448815858</v>
       </c>
       <c r="CM20">
-        <v>0.2000814745947975</v>
+        <v>0.2270139448815858</v>
       </c>
       <c r="CN20">
-        <v>0.2000814745947975</v>
+        <v>0.2270139448815858</v>
       </c>
       <c r="CO20">
-        <v>0.2000814745947975</v>
+        <v>0.2270139448815858</v>
       </c>
       <c r="CP20">
-        <v>0.2000814745947975</v>
+        <v>0.2270139448815858</v>
       </c>
       <c r="CQ20">
-        <v>0.2000814745947975</v>
+        <v>0.2270139448815858</v>
       </c>
       <c r="CR20">
-        <v>0.2000814745947975</v>
+        <v>0.2270139448815858</v>
       </c>
       <c r="CS20">
-        <v>0.2000814745947975</v>
+        <v>0.2270139448815858</v>
       </c>
     </row>
     <row r="21" spans="1:97">
       <c r="A21" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B21">
+        <v>0.2</v>
+      </c>
+      <c r="C21">
+        <v>0.2</v>
+      </c>
+      <c r="D21">
+        <v>0.2</v>
+      </c>
+      <c r="E21">
+        <v>0.2</v>
+      </c>
+      <c r="F21">
+        <v>0.2</v>
+      </c>
+      <c r="G21">
+        <v>0.2</v>
+      </c>
+      <c r="H21">
+        <v>0.2</v>
+      </c>
+      <c r="I21">
+        <v>0.2</v>
+      </c>
+      <c r="J21">
+        <v>0.2</v>
+      </c>
+      <c r="K21">
+        <v>0.2</v>
+      </c>
+      <c r="L21">
+        <v>0.2</v>
+      </c>
+      <c r="M21">
+        <v>0.2</v>
+      </c>
+      <c r="N21">
+        <v>0.2</v>
+      </c>
+      <c r="O21">
+        <v>0.2</v>
+      </c>
+      <c r="P21">
+        <v>0.2</v>
+      </c>
+      <c r="Q21">
+        <v>0.8</v>
+      </c>
+      <c r="R21">
+        <v>0.8</v>
+      </c>
+      <c r="S21">
+        <v>0.8</v>
+      </c>
+      <c r="T21">
+        <v>0.8</v>
+      </c>
+      <c r="U21">
+        <v>0.8</v>
+      </c>
+      <c r="V21">
+        <v>0.8</v>
+      </c>
+      <c r="W21">
+        <v>0.8</v>
+      </c>
+      <c r="X21">
+        <v>0.8</v>
+      </c>
+      <c r="Y21">
+        <v>0.8</v>
+      </c>
+      <c r="Z21">
+        <v>0.8</v>
+      </c>
+      <c r="AA21">
+        <v>0.7623522607517587</v>
+      </c>
+      <c r="AB21">
+        <v>0.7247045215035066</v>
+      </c>
+      <c r="AC21">
+        <v>0.6870567822552546</v>
+      </c>
+      <c r="AD21">
+        <v>0.6494090430070023</v>
+      </c>
+      <c r="AE21">
+        <v>0.6494090430070023</v>
+      </c>
+      <c r="AF21">
+        <v>0.6023690802196565</v>
+      </c>
+      <c r="AG21">
+        <v>0.5553291174323107</v>
+      </c>
+      <c r="AH21">
+        <v>0.5082891546449648</v>
+      </c>
+      <c r="AI21">
+        <v>0.5082891546449648</v>
+      </c>
+      <c r="AJ21">
+        <v>0.5082891546449648</v>
+      </c>
+      <c r="AK21">
+        <v>0.5082891546449648</v>
+      </c>
+      <c r="AL21">
+        <v>0.5082891546449648</v>
+      </c>
+      <c r="AM21">
+        <v>0.5082891546449648</v>
+      </c>
+      <c r="AN21">
+        <v>0.5082891546449648</v>
+      </c>
+      <c r="AO21">
+        <v>0.5082891546449648</v>
+      </c>
+      <c r="AP21">
+        <v>0.5082891546449648</v>
+      </c>
+      <c r="AQ21">
+        <v>0.5082891546449648</v>
+      </c>
+      <c r="AR21">
+        <v>0.5082891546449648</v>
+      </c>
+      <c r="AS21">
+        <v>0.5082891546449648</v>
+      </c>
+      <c r="AT21">
+        <v>0.5082891546449648</v>
+      </c>
+      <c r="AU21">
+        <v>0.5082891546449648</v>
+      </c>
+      <c r="AV21">
+        <v>0.5082891546449648</v>
+      </c>
+      <c r="AW21">
+        <v>0.5082891546449648</v>
+      </c>
+      <c r="AX21">
+        <v>0.5082891546449648</v>
+      </c>
+      <c r="AY21">
+        <v>0.5082891546449648</v>
+      </c>
+      <c r="AZ21">
+        <v>0.5082891546449648</v>
+      </c>
+      <c r="BA21">
+        <v>0.5082891546449648</v>
+      </c>
+      <c r="BB21">
+        <v>0.5082891546449648</v>
+      </c>
+      <c r="BC21">
+        <v>0.5082891546449648</v>
+      </c>
+      <c r="BD21">
+        <v>0.5082891546449648</v>
+      </c>
+      <c r="BE21">
+        <v>0.5082891546449648</v>
+      </c>
+      <c r="BF21">
+        <v>0.5082891546449648</v>
+      </c>
+      <c r="BG21">
+        <v>0.5082891546449648</v>
+      </c>
+      <c r="BH21">
+        <v>0.5082891546449648</v>
+      </c>
+      <c r="BI21">
+        <v>0.4333068679774677</v>
+      </c>
+      <c r="BJ21">
+        <v>0.3583245813099705</v>
+      </c>
+      <c r="BK21">
+        <v>0.3266480692995996</v>
+      </c>
+      <c r="BL21">
+        <v>0.2949715572892287</v>
+      </c>
+      <c r="BM21">
+        <v>0.2578090588318514</v>
+      </c>
+      <c r="BN21">
+        <v>0.2578090588318514</v>
+      </c>
+      <c r="BO21">
+        <v>0.2578090588318514</v>
+      </c>
+      <c r="BP21">
+        <v>0.2578090588318514</v>
+      </c>
+      <c r="BQ21">
+        <v>0.2578090588318514</v>
+      </c>
+      <c r="BR21">
+        <v>0.2578090588318514</v>
+      </c>
+      <c r="BS21">
+        <v>0.2578090588318514</v>
+      </c>
+      <c r="BT21">
+        <v>0.2578090588318514</v>
+      </c>
+      <c r="BU21">
+        <v>0.2578090588318514</v>
+      </c>
+      <c r="BV21">
+        <v>0.2578090588318514</v>
+      </c>
+      <c r="BW21">
+        <v>0.2578090588318514</v>
+      </c>
+      <c r="BX21">
+        <v>0.2578090588318514</v>
+      </c>
+      <c r="BY21">
+        <v>0.2087001210009659</v>
+      </c>
+      <c r="BZ21">
+        <v>0.8087001210009659</v>
+      </c>
+      <c r="CA21">
+        <v>0.7665903393992538</v>
+      </c>
+      <c r="CB21">
+        <v>0.7244805577975418</v>
+      </c>
+      <c r="CC21">
+        <v>0.7244805577975418</v>
+      </c>
+      <c r="CD21">
+        <v>0.7190178496117141</v>
+      </c>
+      <c r="CE21">
+        <v>0.7135551414258864</v>
+      </c>
+      <c r="CF21">
+        <v>0.7135551414258864</v>
+      </c>
+      <c r="CG21">
+        <v>0.7135551414258864</v>
+      </c>
+      <c r="CH21">
+        <v>0.7135551414258864</v>
+      </c>
+      <c r="CI21">
+        <v>0.7135551414258864</v>
+      </c>
+      <c r="CJ21">
+        <v>0.6513403625803545</v>
+      </c>
+      <c r="CK21">
+        <v>0.5891255837348229</v>
+      </c>
+      <c r="CL21">
+        <v>0.5891255837348229</v>
+      </c>
+      <c r="CM21">
+        <v>0.5891255837348229</v>
+      </c>
+      <c r="CN21">
+        <v>0.5891255837348229</v>
+      </c>
+      <c r="CO21">
+        <v>0.5891255837348229</v>
+      </c>
+      <c r="CP21">
+        <v>0.5891255837348229</v>
+      </c>
+      <c r="CQ21">
+        <v>0.5891255837348229</v>
+      </c>
+      <c r="CR21">
+        <v>0.5891255837348229</v>
+      </c>
+      <c r="CS21">
+        <v>0.5891255837348229</v>
+      </c>
+    </row>
+    <row r="22" spans="1:97">
+      <c r="A22" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B22">
+        <v>0.2</v>
+      </c>
+      <c r="C22">
+        <v>0.2</v>
+      </c>
+      <c r="D22">
+        <v>0.2</v>
+      </c>
+      <c r="E22">
+        <v>0.2</v>
+      </c>
+      <c r="F22">
+        <v>0.2</v>
+      </c>
+      <c r="G22">
+        <v>0.2</v>
+      </c>
+      <c r="H22">
+        <v>0.2</v>
+      </c>
+      <c r="I22">
+        <v>0.2</v>
+      </c>
+      <c r="J22">
+        <v>0.2</v>
+      </c>
+      <c r="K22">
+        <v>0.2</v>
+      </c>
+      <c r="L22">
+        <v>0.2</v>
+      </c>
+      <c r="M22">
+        <v>0.2</v>
+      </c>
+      <c r="N22">
+        <v>0.8</v>
+      </c>
+      <c r="O22">
+        <v>0.8</v>
+      </c>
+      <c r="P22">
+        <v>0.8</v>
+      </c>
+      <c r="Q22">
+        <v>0.8</v>
+      </c>
+      <c r="R22">
+        <v>0.8</v>
+      </c>
+      <c r="S22">
+        <v>0.8</v>
+      </c>
+      <c r="T22">
+        <v>0.8</v>
+      </c>
+      <c r="U22">
+        <v>0.8</v>
+      </c>
+      <c r="V22">
+        <v>0.8</v>
+      </c>
+      <c r="W22">
+        <v>0.8</v>
+      </c>
+      <c r="X22">
+        <v>0.8</v>
+      </c>
+      <c r="Y22">
+        <v>0.8</v>
+      </c>
+      <c r="Z22">
+        <v>0.8</v>
+      </c>
+      <c r="AA22">
+        <v>0.8</v>
+      </c>
+      <c r="AB22">
+        <v>0.8</v>
+      </c>
+      <c r="AC22">
+        <v>0.8</v>
+      </c>
+      <c r="AD22">
+        <v>0.8</v>
+      </c>
+      <c r="AE22">
+        <v>0.8</v>
+      </c>
+      <c r="AF22">
+        <v>0.7679131390980103</v>
+      </c>
+      <c r="AG22">
+        <v>0.7358262781960089</v>
+      </c>
+      <c r="AH22">
+        <v>0.7037394172940061</v>
+      </c>
+      <c r="AI22">
+        <v>0.6716525563920052</v>
+      </c>
+      <c r="AJ22">
+        <v>0.6395656954900025</v>
+      </c>
+      <c r="AK22">
+        <v>0.6395656954900093</v>
+      </c>
+      <c r="AL22">
+        <v>0.6020321115901663</v>
+      </c>
+      <c r="AM22">
+        <v>0.5644985276903248</v>
+      </c>
+      <c r="AN22">
+        <v>0.5269649437904828</v>
+      </c>
+      <c r="AO22">
+        <v>0.4894313598906406</v>
+      </c>
+      <c r="AP22">
+        <v>0.4894313598906458</v>
+      </c>
+      <c r="AQ22">
+        <v>0.4894313598906458</v>
+      </c>
+      <c r="AR22">
+        <v>0.4894313598906458</v>
+      </c>
+      <c r="AS22">
+        <v>0.4894313598906458</v>
+      </c>
+      <c r="AT22">
+        <v>0.4894313598906458</v>
+      </c>
+      <c r="AU22">
+        <v>0.4894313598906458</v>
+      </c>
+      <c r="AV22">
+        <v>0.4894313598906458</v>
+      </c>
+      <c r="AW22">
+        <v>0.4894313598906458</v>
+      </c>
+      <c r="AX22">
+        <v>0.4894313598906458</v>
+      </c>
+      <c r="AY22">
+        <v>0.4894313598906458</v>
+      </c>
+      <c r="AZ22">
+        <v>0.4335140259921836</v>
+      </c>
+      <c r="BA22">
+        <v>0.3775966920937212</v>
+      </c>
+      <c r="BB22">
+        <v>0.3216793581952588</v>
+      </c>
+      <c r="BC22">
+        <v>0.3216793581952588</v>
+      </c>
+      <c r="BD22">
+        <v>0.3216793581952588</v>
+      </c>
+      <c r="BE22">
+        <v>0.3216793581952588</v>
+      </c>
+      <c r="BF22">
+        <v>0.3216793581952588</v>
+      </c>
+      <c r="BG22">
+        <v>0.3216793581952588</v>
+      </c>
+      <c r="BH22">
+        <v>0.2645779156343875</v>
+      </c>
+      <c r="BI22">
+        <v>0.2074764730735163</v>
+      </c>
+      <c r="BJ22">
+        <v>0.2074764730735163</v>
+      </c>
+      <c r="BK22">
+        <v>0.2074764730735163</v>
+      </c>
+      <c r="BL22">
+        <v>0.2074764730735163</v>
+      </c>
+      <c r="BM22">
+        <v>0.2074764730735163</v>
+      </c>
+      <c r="BN22">
+        <v>0.2074764730735163</v>
+      </c>
+      <c r="BO22">
+        <v>0.2074764730735163</v>
+      </c>
+      <c r="BP22">
+        <v>0.2074764730735163</v>
+      </c>
+      <c r="BQ22">
+        <v>0.2074764730735163</v>
+      </c>
+      <c r="BR22">
+        <v>0.2074764730735163</v>
+      </c>
+      <c r="BS22">
+        <v>0.2074764730735163</v>
+      </c>
+      <c r="BT22">
+        <v>0.2074764730735163</v>
+      </c>
+      <c r="BU22">
+        <v>0.2074764730735163</v>
+      </c>
+      <c r="BV22">
+        <v>0.2074764730735163</v>
+      </c>
+      <c r="BW22">
+        <v>0.2074764730735163</v>
+      </c>
+      <c r="BX22">
+        <v>0.2074764730735163</v>
+      </c>
+      <c r="BY22">
+        <v>0.2074764730735163</v>
+      </c>
+      <c r="BZ22">
+        <v>0.2074764730735163</v>
+      </c>
+      <c r="CA22">
+        <v>0.2074764730735163</v>
+      </c>
+      <c r="CB22">
+        <v>0.2074764730735163</v>
+      </c>
+      <c r="CC22">
+        <v>0.2074764730735163</v>
+      </c>
+      <c r="CD22">
+        <v>0.2074764730735163</v>
+      </c>
+      <c r="CE22">
+        <v>0.2074764730735163</v>
+      </c>
+      <c r="CF22">
+        <v>0.2074764730735163</v>
+      </c>
+      <c r="CG22">
+        <v>0.2074764730735163</v>
+      </c>
+      <c r="CH22">
+        <v>0.2074764730735163</v>
+      </c>
+      <c r="CI22">
+        <v>0.2074764730735163</v>
+      </c>
+      <c r="CJ22">
+        <v>0.2074764730735163</v>
+      </c>
+      <c r="CK22">
+        <v>0.2074764730735163</v>
+      </c>
+      <c r="CL22">
+        <v>0.2074764730735163</v>
+      </c>
+      <c r="CM22">
+        <v>0.2074764730735163</v>
+      </c>
+      <c r="CN22">
+        <v>0.2074764730735163</v>
+      </c>
+      <c r="CO22">
+        <v>0.2074764730735163</v>
+      </c>
+      <c r="CP22">
+        <v>0.2074764730735163</v>
+      </c>
+      <c r="CQ22">
+        <v>0.2074764730735163</v>
+      </c>
+      <c r="CR22">
+        <v>0.2074764730735163</v>
+      </c>
+      <c r="CS22">
+        <v>0.2074764730735163</v>
+      </c>
+    </row>
+    <row r="23" spans="1:97">
+      <c r="A23" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B21">
-        <v>0.2</v>
-      </c>
-      <c r="C21">
-        <v>0.26</v>
-      </c>
-      <c r="D21">
-        <v>0.26</v>
-      </c>
-      <c r="E21">
-        <v>0.26</v>
-      </c>
-      <c r="F21">
-        <v>0.26</v>
-      </c>
-      <c r="G21">
-        <v>0.26</v>
-      </c>
-      <c r="H21">
-        <v>0.26</v>
-      </c>
-      <c r="I21">
-        <v>0.26</v>
-      </c>
-      <c r="J21">
-        <v>0.32</v>
-      </c>
-      <c r="K21">
-        <v>0.32</v>
-      </c>
-      <c r="L21">
-        <v>0.32</v>
-      </c>
-      <c r="M21">
-        <v>0.38</v>
-      </c>
-      <c r="N21">
-        <v>0.38</v>
-      </c>
-      <c r="O21">
-        <v>0.38</v>
-      </c>
-      <c r="P21">
-        <v>0.44</v>
-      </c>
-      <c r="Q21">
-        <v>0.44</v>
-      </c>
-      <c r="R21">
-        <v>0.44</v>
-      </c>
-      <c r="S21">
-        <v>0.5</v>
-      </c>
-      <c r="T21">
-        <v>0.5</v>
-      </c>
-      <c r="U21">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="V21">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="W21">
-        <v>0.5378754765360211</v>
-      </c>
-      <c r="X21">
-        <v>0.5157509530720421</v>
-      </c>
-      <c r="Y21">
-        <v>0.4936264296080631</v>
-      </c>
-      <c r="Z21">
-        <v>0.4715019061440842</v>
-      </c>
-      <c r="AA21">
-        <v>0.5315019061440842</v>
-      </c>
-      <c r="AB21">
-        <v>0.5915019061440842</v>
-      </c>
-      <c r="AC21">
-        <v>0.591501906144084</v>
-      </c>
-      <c r="AD21">
-        <v>0.591501906144084</v>
-      </c>
-      <c r="AE21">
-        <v>0.591501906144084</v>
-      </c>
-      <c r="AF21">
-        <v>0.5733845400460664</v>
-      </c>
-      <c r="AG21">
-        <v>0.5552671739480487</v>
-      </c>
-      <c r="AH21">
-        <v>0.537149807850031</v>
-      </c>
-      <c r="AI21">
-        <v>0.537149807850031</v>
-      </c>
-      <c r="AJ21">
-        <v>0.537149807850031</v>
-      </c>
-      <c r="AK21">
-        <v>0.537149807850031</v>
-      </c>
-      <c r="AL21">
-        <v>0.537149807850031</v>
-      </c>
-      <c r="AM21">
-        <v>0.537149807850031</v>
-      </c>
-      <c r="AN21">
-        <v>0.537149807850031</v>
-      </c>
-      <c r="AO21">
-        <v>0.537149807850031</v>
-      </c>
-      <c r="AP21">
-        <v>0.537149807850031</v>
-      </c>
-      <c r="AQ21">
-        <v>0.537149807850031</v>
-      </c>
-      <c r="AR21">
-        <v>0.5092916610123439</v>
-      </c>
-      <c r="AS21">
-        <v>0.4814335141746569</v>
-      </c>
-      <c r="AT21">
-        <v>0.45357536733697</v>
-      </c>
-      <c r="AU21">
-        <v>0.45357536733697</v>
-      </c>
-      <c r="AV21">
-        <v>0.45357536733697</v>
-      </c>
-      <c r="AW21">
-        <v>0.45357536733697</v>
-      </c>
-      <c r="AX21">
-        <v>0.4350654690952911</v>
-      </c>
-      <c r="AY21">
-        <v>0.4350654690952911</v>
-      </c>
-      <c r="AZ21">
-        <v>0.4350654690952911</v>
-      </c>
-      <c r="BA21">
-        <v>0.4350654690952911</v>
-      </c>
-      <c r="BB21">
-        <v>0.4132802901220901</v>
-      </c>
-      <c r="BC21">
-        <v>0.3914951111488891</v>
-      </c>
-      <c r="BD21">
-        <v>0.3605885395904271</v>
-      </c>
-      <c r="BE21">
-        <v>0.3605885395904271</v>
-      </c>
-      <c r="BF21">
-        <v>0.3605885395904271</v>
-      </c>
-      <c r="BG21">
-        <v>0.3605885395904271</v>
-      </c>
-      <c r="BH21">
-        <v>0.3320378183099915</v>
-      </c>
-      <c r="BI21">
-        <v>0.3034870970295558</v>
-      </c>
-      <c r="BJ21">
-        <v>0.3034870970295558</v>
-      </c>
-      <c r="BK21">
-        <v>0.3034870970295558</v>
-      </c>
-      <c r="BL21">
-        <v>0.3034870970295558</v>
-      </c>
-      <c r="BM21">
-        <v>0.3034870970295558</v>
-      </c>
-      <c r="BN21">
-        <v>0.3034870970295558</v>
-      </c>
-      <c r="BO21">
-        <v>0.3034870970295558</v>
-      </c>
-      <c r="BP21">
-        <v>0.3034870970295558</v>
-      </c>
-      <c r="BQ21">
-        <v>0.2674569308724929</v>
-      </c>
-      <c r="BR21">
-        <v>0.2314267647154299</v>
-      </c>
-      <c r="BS21">
-        <v>0.2314267647154299</v>
-      </c>
-      <c r="BT21">
-        <v>0.2314267647154299</v>
-      </c>
-      <c r="BU21">
-        <v>0.2314267647154299</v>
-      </c>
-      <c r="BV21">
-        <v>0.2314267647154299</v>
-      </c>
-      <c r="BW21">
-        <v>0.2314267647154299</v>
-      </c>
-      <c r="BX21">
-        <v>0.2314267647154299</v>
-      </c>
-      <c r="BY21">
-        <v>0.2314267647154299</v>
-      </c>
-      <c r="BZ21">
-        <v>0.2314267647154299</v>
-      </c>
-      <c r="CA21">
-        <v>0.2036561184270317</v>
-      </c>
-      <c r="CB21">
-        <v>0.2036561184270317</v>
-      </c>
-      <c r="CC21">
-        <v>0.2036561184270317</v>
-      </c>
-      <c r="CD21">
-        <v>0.2036561184270317</v>
-      </c>
-      <c r="CE21">
-        <v>0.2036561184270317</v>
-      </c>
-      <c r="CF21">
-        <v>0.2036561184270317</v>
-      </c>
-      <c r="CG21">
-        <v>0.2036561184270317</v>
-      </c>
-      <c r="CH21">
-        <v>0.2036561184270317</v>
-      </c>
-      <c r="CI21">
-        <v>0.2036561184270317</v>
-      </c>
-      <c r="CJ21">
-        <v>0.2036561184270317</v>
-      </c>
-      <c r="CK21">
-        <v>0.2036561184270317</v>
-      </c>
-      <c r="CL21">
-        <v>0.2036561184270317</v>
-      </c>
-      <c r="CM21">
-        <v>0.2036561184270317</v>
-      </c>
-      <c r="CN21">
-        <v>0.2036561184270317</v>
-      </c>
-      <c r="CO21">
-        <v>0.2036561184270317</v>
-      </c>
-      <c r="CP21">
-        <v>0.2036561184270317</v>
-      </c>
-      <c r="CQ21">
-        <v>0.2036561184270317</v>
-      </c>
-      <c r="CR21">
-        <v>0.2036561184270317</v>
-      </c>
-      <c r="CS21">
-        <v>0.2036561184270317</v>
+      <c r="B23">
+        <v>0.2</v>
+      </c>
+      <c r="C23">
+        <v>0.2</v>
+      </c>
+      <c r="D23">
+        <v>0.2</v>
+      </c>
+      <c r="E23">
+        <v>0.2</v>
+      </c>
+      <c r="F23">
+        <v>0.2</v>
+      </c>
+      <c r="G23">
+        <v>0.2</v>
+      </c>
+      <c r="H23">
+        <v>0.2</v>
+      </c>
+      <c r="I23">
+        <v>0.2</v>
+      </c>
+      <c r="J23">
+        <v>0.2</v>
+      </c>
+      <c r="K23">
+        <v>0.2</v>
+      </c>
+      <c r="L23">
+        <v>0.2</v>
+      </c>
+      <c r="M23">
+        <v>0.2</v>
+      </c>
+      <c r="N23">
+        <v>0.2</v>
+      </c>
+      <c r="O23">
+        <v>0.2</v>
+      </c>
+      <c r="P23">
+        <v>0.2</v>
+      </c>
+      <c r="Q23">
+        <v>0.8</v>
+      </c>
+      <c r="R23">
+        <v>0.8</v>
+      </c>
+      <c r="S23">
+        <v>0.8</v>
+      </c>
+      <c r="T23">
+        <v>0.8</v>
+      </c>
+      <c r="U23">
+        <v>0.8</v>
+      </c>
+      <c r="V23">
+        <v>0.8</v>
+      </c>
+      <c r="W23">
+        <v>0.8</v>
+      </c>
+      <c r="X23">
+        <v>0.8</v>
+      </c>
+      <c r="Y23">
+        <v>0.8</v>
+      </c>
+      <c r="Z23">
+        <v>0.8</v>
+      </c>
+      <c r="AA23">
+        <v>0.8</v>
+      </c>
+      <c r="AB23">
+        <v>0.8</v>
+      </c>
+      <c r="AC23">
+        <v>0.8</v>
+      </c>
+      <c r="AD23">
+        <v>0.8</v>
+      </c>
+      <c r="AE23">
+        <v>0.7693626218040892</v>
+      </c>
+      <c r="AF23">
+        <v>0.7387252436081785</v>
+      </c>
+      <c r="AG23">
+        <v>0.7080878654122676</v>
+      </c>
+      <c r="AH23">
+        <v>0.6774504872163569</v>
+      </c>
+      <c r="AI23">
+        <v>0.6468131090204461</v>
+      </c>
+      <c r="AJ23">
+        <v>0.6468131090204461</v>
+      </c>
+      <c r="AK23">
+        <v>0.6468131090204461</v>
+      </c>
+      <c r="AL23">
+        <v>0.6468131090204461</v>
+      </c>
+      <c r="AM23">
+        <v>0.6468131090204461</v>
+      </c>
+      <c r="AN23">
+        <v>0.6468131090204461</v>
+      </c>
+      <c r="AO23">
+        <v>0.6468131090204461</v>
+      </c>
+      <c r="AP23">
+        <v>0.6468131090204461</v>
+      </c>
+      <c r="AQ23">
+        <v>0.6468131090204461</v>
+      </c>
+      <c r="AR23">
+        <v>0.6468131090204461</v>
+      </c>
+      <c r="AS23">
+        <v>0.6468131090204461</v>
+      </c>
+      <c r="AT23">
+        <v>0.6468131090204461</v>
+      </c>
+      <c r="AU23">
+        <v>0.6468131090204461</v>
+      </c>
+      <c r="AV23">
+        <v>0.6468131090204461</v>
+      </c>
+      <c r="AW23">
+        <v>0.6468131090204461</v>
+      </c>
+      <c r="AX23">
+        <v>0.6468131090204461</v>
+      </c>
+      <c r="AY23">
+        <v>0.6468131090204461</v>
+      </c>
+      <c r="AZ23">
+        <v>0.6468131090204461</v>
+      </c>
+      <c r="BA23">
+        <v>0.6468131090204461</v>
+      </c>
+      <c r="BB23">
+        <v>0.6468131090204461</v>
+      </c>
+      <c r="BC23">
+        <v>0.6468131090204461</v>
+      </c>
+      <c r="BD23">
+        <v>0.6468131090204461</v>
+      </c>
+      <c r="BE23">
+        <v>0.6468131090204461</v>
+      </c>
+      <c r="BF23">
+        <v>0.6468131090204461</v>
+      </c>
+      <c r="BG23">
+        <v>0.6468131090204461</v>
+      </c>
+      <c r="BH23">
+        <v>0.6468131090204461</v>
+      </c>
+      <c r="BI23">
+        <v>0.6468131090204461</v>
+      </c>
+      <c r="BJ23">
+        <v>0.6468131090204461</v>
+      </c>
+      <c r="BK23">
+        <v>0.6468131090204461</v>
+      </c>
+      <c r="BL23">
+        <v>0.646813109020446</v>
+      </c>
+      <c r="BM23">
+        <v>0.6188443310445441</v>
+      </c>
+      <c r="BN23">
+        <v>0.5908755530686421</v>
+      </c>
+      <c r="BO23">
+        <v>0.5629067750927402</v>
+      </c>
+      <c r="BP23">
+        <v>0.5629067750927402</v>
+      </c>
+      <c r="BQ23">
+        <v>0.4908464427786144</v>
+      </c>
+      <c r="BR23">
+        <v>0.4187861104644885</v>
+      </c>
+      <c r="BS23">
+        <v>0.4187861104644885</v>
+      </c>
+      <c r="BT23">
+        <v>0.3431534279495356</v>
+      </c>
+      <c r="BU23">
+        <v>0.2675207454345828</v>
+      </c>
+      <c r="BV23">
+        <v>0.2675207454345828</v>
+      </c>
+      <c r="BW23">
+        <v>0.2675207454345828</v>
+      </c>
+      <c r="BX23">
+        <v>0.2675207454345828</v>
+      </c>
+      <c r="BY23">
+        <v>0.2675207454345828</v>
+      </c>
+      <c r="BZ23">
+        <v>0.2675207454345828</v>
+      </c>
+      <c r="CA23">
+        <v>0.2675207454345828</v>
+      </c>
+      <c r="CB23">
+        <v>0.2675207454345828</v>
+      </c>
+      <c r="CC23">
+        <v>0.2675207454345828</v>
+      </c>
+      <c r="CD23">
+        <v>0.2675207454345828</v>
+      </c>
+      <c r="CE23">
+        <v>0.2675207454345828</v>
+      </c>
+      <c r="CF23">
+        <v>0.2675207454345828</v>
+      </c>
+      <c r="CG23">
+        <v>0.2192155943307338</v>
+      </c>
+      <c r="CH23">
+        <v>0.2192155943307338</v>
+      </c>
+      <c r="CI23">
+        <v>0.2192155943307338</v>
+      </c>
+      <c r="CJ23">
+        <v>0.2192155943307338</v>
+      </c>
+      <c r="CK23">
+        <v>0.2192155943307338</v>
+      </c>
+      <c r="CL23">
+        <v>0.2137751526476299</v>
+      </c>
+      <c r="CM23">
+        <v>0.2083347109645261</v>
+      </c>
+      <c r="CN23">
+        <v>0.2083347109645261</v>
+      </c>
+      <c r="CO23">
+        <v>0.2083347109645261</v>
+      </c>
+      <c r="CP23">
+        <v>0.2083347109645261</v>
+      </c>
+      <c r="CQ23">
+        <v>0.2083347109645261</v>
+      </c>
+      <c r="CR23">
+        <v>0.2083347109645261</v>
+      </c>
+      <c r="CS23">
+        <v>0.2083347109645261</v>
+      </c>
+    </row>
+    <row r="24" spans="1:97">
+      <c r="A24" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B24">
+        <v>0.2</v>
+      </c>
+      <c r="C24">
+        <v>0.2</v>
+      </c>
+      <c r="D24">
+        <v>0.2</v>
+      </c>
+      <c r="E24">
+        <v>0.2</v>
+      </c>
+      <c r="F24">
+        <v>0.8</v>
+      </c>
+      <c r="G24">
+        <v>0.8</v>
+      </c>
+      <c r="H24">
+        <v>0.8</v>
+      </c>
+      <c r="I24">
+        <v>0.8</v>
+      </c>
+      <c r="J24">
+        <v>0.8</v>
+      </c>
+      <c r="K24">
+        <v>0.8</v>
+      </c>
+      <c r="L24">
+        <v>0.8</v>
+      </c>
+      <c r="M24">
+        <v>0.8</v>
+      </c>
+      <c r="N24">
+        <v>0.8</v>
+      </c>
+      <c r="O24">
+        <v>0.8</v>
+      </c>
+      <c r="P24">
+        <v>0.8</v>
+      </c>
+      <c r="Q24">
+        <v>0.8</v>
+      </c>
+      <c r="R24">
+        <v>0.8</v>
+      </c>
+      <c r="S24">
+        <v>0.8</v>
+      </c>
+      <c r="T24">
+        <v>0.8</v>
+      </c>
+      <c r="U24">
+        <v>0.8</v>
+      </c>
+      <c r="V24">
+        <v>0.8</v>
+      </c>
+      <c r="W24">
+        <v>0.8</v>
+      </c>
+      <c r="X24">
+        <v>0.8</v>
+      </c>
+      <c r="Y24">
+        <v>0.8</v>
+      </c>
+      <c r="Z24">
+        <v>0.8</v>
+      </c>
+      <c r="AA24">
+        <v>0.8</v>
+      </c>
+      <c r="AB24">
+        <v>0.7550577101412291</v>
+      </c>
+      <c r="AC24">
+        <v>0.7101154202824582</v>
+      </c>
+      <c r="AD24">
+        <v>0.6651731304236873</v>
+      </c>
+      <c r="AE24">
+        <v>0.6651731304236873</v>
+      </c>
+      <c r="AF24">
+        <v>0.6286377676146073</v>
+      </c>
+      <c r="AG24">
+        <v>0.5921024048055273</v>
+      </c>
+      <c r="AH24">
+        <v>0.5921024048055273</v>
+      </c>
+      <c r="AI24">
+        <v>0.5514446004492221</v>
+      </c>
+      <c r="AJ24">
+        <v>0.5107867960929168</v>
+      </c>
+      <c r="AK24">
+        <v>0.4701289917366115</v>
+      </c>
+      <c r="AL24">
+        <v>0.4294711873803062</v>
+      </c>
+      <c r="AM24">
+        <v>0.4294711873803062</v>
+      </c>
+      <c r="AN24">
+        <v>0.4294711873803062</v>
+      </c>
+      <c r="AO24">
+        <v>0.4294711873803062</v>
+      </c>
+      <c r="AP24">
+        <v>0.4294711873803062</v>
+      </c>
+      <c r="AQ24">
+        <v>0.4294711873803062</v>
+      </c>
+      <c r="AR24">
+        <v>0.4294711873803062</v>
+      </c>
+      <c r="AS24">
+        <v>0.4294711873803062</v>
+      </c>
+      <c r="AT24">
+        <v>0.4294711873803062</v>
+      </c>
+      <c r="AU24">
+        <v>0.4227094636694624</v>
+      </c>
+      <c r="AV24">
+        <v>0.4159477399586186</v>
+      </c>
+      <c r="AW24">
+        <v>0.4091860162477747</v>
+      </c>
+      <c r="AX24">
+        <v>0.402424292536931</v>
+      </c>
+      <c r="AY24">
+        <v>0.3956625688260871</v>
+      </c>
+      <c r="AZ24">
+        <v>0.3889008451152433</v>
+      </c>
+      <c r="BA24">
+        <v>0.3821391214043995</v>
+      </c>
+      <c r="BB24">
+        <v>0.3821391214043995</v>
+      </c>
+      <c r="BC24">
+        <v>0.3821391214043995</v>
+      </c>
+      <c r="BD24">
+        <v>0.3821391214043995</v>
+      </c>
+      <c r="BE24">
+        <v>0.334631175908228</v>
+      </c>
+      <c r="BF24">
+        <v>0.2871232304120565</v>
+      </c>
+      <c r="BG24">
+        <v>0.2871232304120565</v>
+      </c>
+      <c r="BH24">
+        <v>0.2871232304120565</v>
+      </c>
+      <c r="BI24">
+        <v>0.2871232304120565</v>
+      </c>
+      <c r="BJ24">
+        <v>0.2871232304120565</v>
+      </c>
+      <c r="BK24">
+        <v>0.2871232304120565</v>
+      </c>
+      <c r="BL24">
+        <v>0.2871232304120565</v>
+      </c>
+      <c r="BM24">
+        <v>0.2871232304120565</v>
+      </c>
+      <c r="BN24">
+        <v>0.2871232304120565</v>
+      </c>
+      <c r="BO24">
+        <v>0.2871232304120565</v>
+      </c>
+      <c r="BP24">
+        <v>0.2871232304120565</v>
+      </c>
+      <c r="BQ24">
+        <v>0.2871232304120565</v>
+      </c>
+      <c r="BR24">
+        <v>0.2871232304120565</v>
+      </c>
+      <c r="BS24">
+        <v>0.2871232304120565</v>
+      </c>
+      <c r="BT24">
+        <v>0.2871232304120565</v>
+      </c>
+      <c r="BU24">
+        <v>0.2871232304120565</v>
+      </c>
+      <c r="BV24">
+        <v>0.2871232304120565</v>
+      </c>
+      <c r="BW24">
+        <v>0.2450134488103445</v>
+      </c>
+      <c r="BX24">
+        <v>0.2029036672086324</v>
+      </c>
+      <c r="BY24">
+        <v>0.2029036672086324</v>
+      </c>
+      <c r="BZ24">
+        <v>0.2029036672086324</v>
+      </c>
+      <c r="CA24">
+        <v>0.2029036672086324</v>
+      </c>
+      <c r="CB24">
+        <v>0.2029036672086324</v>
+      </c>
+      <c r="CC24">
+        <v>0.2029036672086324</v>
+      </c>
+      <c r="CD24">
+        <v>0.2029036672086324</v>
+      </c>
+      <c r="CE24">
+        <v>0.2029036672086324</v>
+      </c>
+      <c r="CF24">
+        <v>0.2029036672086324</v>
+      </c>
+      <c r="CG24">
+        <v>0.2029036672086324</v>
+      </c>
+      <c r="CH24">
+        <v>0.2029036672086324</v>
+      </c>
+      <c r="CI24">
+        <v>0.2029036672086324</v>
+      </c>
+      <c r="CJ24">
+        <v>0.2029036672086324</v>
+      </c>
+      <c r="CK24">
+        <v>0.2029036672086324</v>
+      </c>
+      <c r="CL24">
+        <v>0.2029036672086324</v>
+      </c>
+      <c r="CM24">
+        <v>0.2029036672086324</v>
+      </c>
+      <c r="CN24">
+        <v>0.2029036672086324</v>
+      </c>
+      <c r="CO24">
+        <v>0.2029036672086324</v>
+      </c>
+      <c r="CP24">
+        <v>0.2029036672086324</v>
+      </c>
+      <c r="CQ24">
+        <v>0.2029036672086324</v>
+      </c>
+      <c r="CR24">
+        <v>0.2029036672086324</v>
+      </c>
+      <c r="CS24">
+        <v>0.2029036672086324</v>
       </c>
     </row>
   </sheetData>
